--- a/Гарааны_үнэлгээ/2_нас_гарааны_үнэлгээ_А79.xlsx
+++ b/Гарааны_үнэлгээ/2_нас_гарааны_үнэлгээ_А79.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -946,21 +946,41 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1">
+    <row r="18" ht="134" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>Багш, цэцэрлэгийн гүйцэтгэлийн үнэлгээ (А/27)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Хүүхдийн цэцэрлэгийн бага, дунд бүлгийн багшийн гүйцэтгэлийн «1.1. Сургалт, үйл ажиллагааны үр дүн» үзүүлэлтийг багшийн сургалт, үйл ажиллагааны явцад бүрдүүлсэн баримт нотолгоонд үндэслэн тооцно (журам 2.10). Иймд гарааны үнэлгээний ажиглалт, тэмдэглэл, хувийн хавтас нь багшийн гүйцэтгэлийн нотолгоо болно. Цэцэрлэгийн гүйцэтгэлийн 3-р шалгуур «Суралцагчийн хөгжил хамгаалал» (20 оноо)-д «хүүхдийн хөгжлийн ахиц өөрчлөлтийг бодитой үнэлж, баримт нотолгоо бүрдүүлж буй байдал» багтана (2-р хавсралт). Үнэлгээний баг баримт нотолгоог хуурамчаар үйлдсэн бол үнэлгээг хүчингүйд тооцно (2.12). Үр дүнгийн мэдээллийг журамд заасныг бусад зорилгоор ашиглахыг хориглоно (4.2).</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Боловсролын сайдын 2026.04.27-ны А/27 «СӨ болон ЕБ-ын сургалтын байгууллага, багшийн ажлын гүйцэтгэлийн үнэлгээ зохион байгуулах журам», 2-р хавсралт (А/115-ыг хүчингүй болгосон)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Бөглөх заавар</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>1) «Нэгтгэл» шийтийн B баганад хүүхдийн нэрийг нэг удаа бичнэ; бусад шийтэд автоматаар гарна. 2) Шалгуур бүрийн «Чадна» эсвэл «Чадахгүй» нүдэнд 1 гэж бичнэ. 3) Тоо, хувь, түвшин, мэдлэг/чадвар/төлөвшлийн хувь автоматаар бодогдоно. 4) Шийт бүр A4-д хэвлэхэд тааруулсан.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Гарааны_үнэлгээ/2_нас_гарааны_үнэлгээ_А79.xlsx
+++ b/Гарааны_үнэлгээ/2_нас_гарааны_үнэлгээ_А79.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -966,21 +966,41 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="64" customHeight="1">
+    <row r="19" ht="120" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>Хуулийн 10.5-ын 4 чиглэл</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Хуулийн тайлбараар гурав хүртэлх насны хүүхдийн цогц хөгжлийг дэмжих хөтөлбөр нь эрүүл мэнд, өсөлт, хэл яриа, танин мэдэхүйн хөгжлийг дэмжинэ. Хөтөлбөрийн бичвэр нийтэд олдоогүй тул А/79-ийн 37 шалгуурыг эдгээр 4 чиглэлд багш хуваарилсан (шалгуурын толгойд «10.5: ...» гэж заасан): Эрүүл мэнд — 1, 2, 17, 18, 35, 36, 37; Өсөлт (бие бялдар, их ба нарийн хөдөлгөөн) — 12–16, 26, 28–30; Хэл яриа — 3, 11, 19–22, 31; Танин мэдэхүй — үлдсэн 14 шалгуур. Нэгтгэл шийтэд 4 чиглэл тус бүрийн хувь бодогдоно. Хөтөлбөр батлагдаж нийтлэгдвэл хуваарилалтыг тулгаж засна.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Сургуулийн өмнөх болон ерөнхий боловсролын тухай хуулийн 10.5 ба түүний тайлбар; А/79 журам 2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>Бөглөх заавар</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>1) «Нэгтгэл» шийтийн B баганад хүүхдийн нэрийг нэг удаа бичнэ; бусад шийтэд автоматаар гарна. 2) Шалгуур бүрийн «Чадна» эсвэл «Чадахгүй» нүдэнд 1 гэж бичнэ. 3) Тоо, хувь, түвшин, мэдлэг/чадвар/төлөвшлийн хувь автоматаар бодогдоно. 4) Шийт бүр A4-д хэвлэхэд тааруулсан.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -998,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -1009,9 +1029,13 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1049,17 +1073,21 @@
       <c r="F3" s="8" t="n"/>
       <c r="G3" s="8" t="n"/>
       <c r="H3" s="8" t="n"/>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Нийт чадна (37-аас)</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Нийт хувь</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Түвшин</t>
         </is>
@@ -1082,9 +1110,17 @@
       </c>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
-      <c r="I4" s="8" t="n"/>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Хуулийн 10.5-ын чиглэл (%)</t>
+        </is>
+      </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="8" t="n"/>
+      <c r="O4" s="8" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="8" t="n"/>
@@ -1119,9 +1155,29 @@
           <t>Төлөвшил</t>
         </is>
       </c>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="8" t="n"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Эрүүл мэнд</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Өсөлт</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Хэл яриа</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Танин мэдэхүй</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -1156,9 +1212,29 @@
           <t>4 шалгуур</t>
         </is>
       </c>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>7 шалгуур</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>9 шалгуур</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>7 шалгуур</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>14 шалгуур</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="12" t="n">
@@ -1189,16 +1265,32 @@
         <f>IF(('Бие бялдар'!V10+'Бие бялдар'!X10+'Танин мэдэхүй'!AP10+'Танин мэдэхүй'!AR10+'Нийгэмшил'!V10+'Нийгэмшил'!X10)=0,"",ROUND((N('Нийгэмшил'!N10)+N('Нийгэмшил'!P10)+N('Нийгэмшил'!R10)+N('Нийгэмшил'!T10))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="12">
+        <f>IF(('Бие бялдар'!V10+'Бие бялдар'!X10+'Танин мэдэхүй'!AP10+'Танин мэдэхүй'!AR10+'Нийгэмшил'!V10+'Нийгэмшил'!X10)=0,"",ROUND((N('Бие бялдар'!D10)+N('Бие бялдар'!F10)+N('Бие бялдар'!R10)+N('Бие бялдар'!T10)+N('Нийгэмшил'!P10)+N('Нийгэмшил'!R10)+N('Нийгэмшил'!T10))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>IF(('Бие бялдар'!V10+'Бие бялдар'!X10+'Танин мэдэхүй'!AP10+'Танин мэдэхүй'!AR10+'Нийгэмшил'!V10+'Нийгэмшил'!X10)=0,"",ROUND((N('Бие бялдар'!H10)+N('Бие бялдар'!J10)+N('Бие бялдар'!L10)+N('Бие бялдар'!N10)+N('Бие бялдар'!P10)+N('Танин мэдэхүй'!AD10)+N('Танин мэдэхүй'!AF10)+N('Танин мэдэхүй'!AH10)+N('Танин мэдэхүй'!AJ10))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>IF(('Бие бялдар'!V10+'Бие бялдар'!X10+'Танин мэдэхүй'!AP10+'Танин мэдэхүй'!AR10+'Нийгэмшил'!V10+'Нийгэмшил'!X10)=0,"",ROUND((N('Танин мэдэхүй'!D10)+N('Нийгэмшил'!H10)+N('Танин мэдэхүй'!P10)+N('Танин мэдэхүй'!R10)+N('Танин мэдэхүй'!T10)+N('Танин мэдэхүй'!V10)+N('Нийгэмшил'!L10))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L7" s="12">
+        <f>IF(('Бие бялдар'!V10+'Бие бялдар'!X10+'Танин мэдэхүй'!AP10+'Танин мэдэхүй'!AR10+'Нийгэмшил'!V10+'Нийгэмшил'!X10)=0,"",ROUND((N('Танин мэдэхүй'!F10)+N('Танин мэдэхүй'!H10)+N('Танин мэдэхүй'!J10)+N('Нийгэмшил'!D10)+N('Танин мэдэхүй'!L10)+N('Танин мэдэхүй'!N10)+N('Нийгэмшил'!F10)+N('Танин мэдэхүй'!X10)+N('Танин мэдэхүй'!Z10)+N('Танин мэдэхүй'!AB10)+N('Нийгэмшил'!J10)+N('Танин мэдэхүй'!AL10)+N('Танин мэдэхүй'!AN10)+N('Нийгэмшил'!N10))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M7" s="14">
         <f>'Бие бялдар'!V10+'Танин мэдэхүй'!AP10+'Нийгэмшил'!V10</f>
         <v/>
       </c>
-      <c r="J7" s="12">
-        <f>IF(('Бие бялдар'!V10+'Бие бялдар'!X10+'Танин мэдэхүй'!AP10+'Танин мэдэхүй'!AR10+'Нийгэмшил'!V10+'Нийгэмшил'!X10)=0,"",ROUND(I7/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K7" s="15">
-        <f>IF(J7="","",IF(J7&gt;=80,"Хангалттай эзэмшиж байна",IF(J7&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N7" s="12">
+        <f>IF(('Бие бялдар'!V10+'Бие бялдар'!X10+'Танин мэдэхүй'!AP10+'Танин мэдэхүй'!AR10+'Нийгэмшил'!V10+'Нийгэмшил'!X10)=0,"",ROUND(M7/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O7" s="15">
+        <f>IF(N7="","",IF(N7&gt;=80,"Хангалттай эзэмшиж байна",IF(N7&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1231,16 +1323,32 @@
         <f>IF(('Бие бялдар'!V11+'Бие бялдар'!X11+'Танин мэдэхүй'!AP11+'Танин мэдэхүй'!AR11+'Нийгэмшил'!V11+'Нийгэмшил'!X11)=0,"",ROUND((N('Нийгэмшил'!N11)+N('Нийгэмшил'!P11)+N('Нийгэмшил'!R11)+N('Нийгэмшил'!T11))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="12">
+        <f>IF(('Бие бялдар'!V11+'Бие бялдар'!X11+'Танин мэдэхүй'!AP11+'Танин мэдэхүй'!AR11+'Нийгэмшил'!V11+'Нийгэмшил'!X11)=0,"",ROUND((N('Бие бялдар'!D11)+N('Бие бялдар'!F11)+N('Бие бялдар'!R11)+N('Бие бялдар'!T11)+N('Нийгэмшил'!P11)+N('Нийгэмшил'!R11)+N('Нийгэмшил'!T11))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>IF(('Бие бялдар'!V11+'Бие бялдар'!X11+'Танин мэдэхүй'!AP11+'Танин мэдэхүй'!AR11+'Нийгэмшил'!V11+'Нийгэмшил'!X11)=0,"",ROUND((N('Бие бялдар'!H11)+N('Бие бялдар'!J11)+N('Бие бялдар'!L11)+N('Бие бялдар'!N11)+N('Бие бялдар'!P11)+N('Танин мэдэхүй'!AD11)+N('Танин мэдэхүй'!AF11)+N('Танин мэдэхүй'!AH11)+N('Танин мэдэхүй'!AJ11))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>IF(('Бие бялдар'!V11+'Бие бялдар'!X11+'Танин мэдэхүй'!AP11+'Танин мэдэхүй'!AR11+'Нийгэмшил'!V11+'Нийгэмшил'!X11)=0,"",ROUND((N('Танин мэдэхүй'!D11)+N('Нийгэмшил'!H11)+N('Танин мэдэхүй'!P11)+N('Танин мэдэхүй'!R11)+N('Танин мэдэхүй'!T11)+N('Танин мэдэхүй'!V11)+N('Нийгэмшил'!L11))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>IF(('Бие бялдар'!V11+'Бие бялдар'!X11+'Танин мэдэхүй'!AP11+'Танин мэдэхүй'!AR11+'Нийгэмшил'!V11+'Нийгэмшил'!X11)=0,"",ROUND((N('Танин мэдэхүй'!F11)+N('Танин мэдэхүй'!H11)+N('Танин мэдэхүй'!J11)+N('Нийгэмшил'!D11)+N('Танин мэдэхүй'!L11)+N('Танин мэдэхүй'!N11)+N('Нийгэмшил'!F11)+N('Танин мэдэхүй'!X11)+N('Танин мэдэхүй'!Z11)+N('Танин мэдэхүй'!AB11)+N('Нийгэмшил'!J11)+N('Танин мэдэхүй'!AL11)+N('Танин мэдэхүй'!AN11)+N('Нийгэмшил'!N11))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M8" s="14">
         <f>'Бие бялдар'!V11+'Танин мэдэхүй'!AP11+'Нийгэмшил'!V11</f>
         <v/>
       </c>
-      <c r="J8" s="12">
-        <f>IF(('Бие бялдар'!V11+'Бие бялдар'!X11+'Танин мэдэхүй'!AP11+'Танин мэдэхүй'!AR11+'Нийгэмшил'!V11+'Нийгэмшил'!X11)=0,"",ROUND(I8/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K8" s="15">
-        <f>IF(J8="","",IF(J8&gt;=80,"Хангалттай эзэмшиж байна",IF(J8&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N8" s="12">
+        <f>IF(('Бие бялдар'!V11+'Бие бялдар'!X11+'Танин мэдэхүй'!AP11+'Танин мэдэхүй'!AR11+'Нийгэмшил'!V11+'Нийгэмшил'!X11)=0,"",ROUND(M8/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O8" s="15">
+        <f>IF(N8="","",IF(N8&gt;=80,"Хангалттай эзэмшиж байна",IF(N8&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1273,16 +1381,32 @@
         <f>IF(('Бие бялдар'!V12+'Бие бялдар'!X12+'Танин мэдэхүй'!AP12+'Танин мэдэхүй'!AR12+'Нийгэмшил'!V12+'Нийгэмшил'!X12)=0,"",ROUND((N('Нийгэмшил'!N12)+N('Нийгэмшил'!P12)+N('Нийгэмшил'!R12)+N('Нийгэмшил'!T12))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="12">
+        <f>IF(('Бие бялдар'!V12+'Бие бялдар'!X12+'Танин мэдэхүй'!AP12+'Танин мэдэхүй'!AR12+'Нийгэмшил'!V12+'Нийгэмшил'!X12)=0,"",ROUND((N('Бие бялдар'!D12)+N('Бие бялдар'!F12)+N('Бие бялдар'!R12)+N('Бие бялдар'!T12)+N('Нийгэмшил'!P12)+N('Нийгэмшил'!R12)+N('Нийгэмшил'!T12))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J9" s="12">
+        <f>IF(('Бие бялдар'!V12+'Бие бялдар'!X12+'Танин мэдэхүй'!AP12+'Танин мэдэхүй'!AR12+'Нийгэмшил'!V12+'Нийгэмшил'!X12)=0,"",ROUND((N('Бие бялдар'!H12)+N('Бие бялдар'!J12)+N('Бие бялдар'!L12)+N('Бие бялдар'!N12)+N('Бие бялдар'!P12)+N('Танин мэдэхүй'!AD12)+N('Танин мэдэхүй'!AF12)+N('Танин мэдэхүй'!AH12)+N('Танин мэдэхүй'!AJ12))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K9" s="12">
+        <f>IF(('Бие бялдар'!V12+'Бие бялдар'!X12+'Танин мэдэхүй'!AP12+'Танин мэдэхүй'!AR12+'Нийгэмшил'!V12+'Нийгэмшил'!X12)=0,"",ROUND((N('Танин мэдэхүй'!D12)+N('Нийгэмшил'!H12)+N('Танин мэдэхүй'!P12)+N('Танин мэдэхүй'!R12)+N('Танин мэдэхүй'!T12)+N('Танин мэдэхүй'!V12)+N('Нийгэмшил'!L12))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L9" s="12">
+        <f>IF(('Бие бялдар'!V12+'Бие бялдар'!X12+'Танин мэдэхүй'!AP12+'Танин мэдэхүй'!AR12+'Нийгэмшил'!V12+'Нийгэмшил'!X12)=0,"",ROUND((N('Танин мэдэхүй'!F12)+N('Танин мэдэхүй'!H12)+N('Танин мэдэхүй'!J12)+N('Нийгэмшил'!D12)+N('Танин мэдэхүй'!L12)+N('Танин мэдэхүй'!N12)+N('Нийгэмшил'!F12)+N('Танин мэдэхүй'!X12)+N('Танин мэдэхүй'!Z12)+N('Танин мэдэхүй'!AB12)+N('Нийгэмшил'!J12)+N('Танин мэдэхүй'!AL12)+N('Танин мэдэхүй'!AN12)+N('Нийгэмшил'!N12))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M9" s="14">
         <f>'Бие бялдар'!V12+'Танин мэдэхүй'!AP12+'Нийгэмшил'!V12</f>
         <v/>
       </c>
-      <c r="J9" s="12">
-        <f>IF(('Бие бялдар'!V12+'Бие бялдар'!X12+'Танин мэдэхүй'!AP12+'Танин мэдэхүй'!AR12+'Нийгэмшил'!V12+'Нийгэмшил'!X12)=0,"",ROUND(I9/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K9" s="15">
-        <f>IF(J9="","",IF(J9&gt;=80,"Хангалттай эзэмшиж байна",IF(J9&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N9" s="12">
+        <f>IF(('Бие бялдар'!V12+'Бие бялдар'!X12+'Танин мэдэхүй'!AP12+'Танин мэдэхүй'!AR12+'Нийгэмшил'!V12+'Нийгэмшил'!X12)=0,"",ROUND(M9/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O9" s="15">
+        <f>IF(N9="","",IF(N9&gt;=80,"Хангалттай эзэмшиж байна",IF(N9&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1315,16 +1439,32 @@
         <f>IF(('Бие бялдар'!V13+'Бие бялдар'!X13+'Танин мэдэхүй'!AP13+'Танин мэдэхүй'!AR13+'Нийгэмшил'!V13+'Нийгэмшил'!X13)=0,"",ROUND((N('Нийгэмшил'!N13)+N('Нийгэмшил'!P13)+N('Нийгэмшил'!R13)+N('Нийгэмшил'!T13))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="12">
+        <f>IF(('Бие бялдар'!V13+'Бие бялдар'!X13+'Танин мэдэхүй'!AP13+'Танин мэдэхүй'!AR13+'Нийгэмшил'!V13+'Нийгэмшил'!X13)=0,"",ROUND((N('Бие бялдар'!D13)+N('Бие бялдар'!F13)+N('Бие бялдар'!R13)+N('Бие бялдар'!T13)+N('Нийгэмшил'!P13)+N('Нийгэмшил'!R13)+N('Нийгэмшил'!T13))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J10" s="12">
+        <f>IF(('Бие бялдар'!V13+'Бие бялдар'!X13+'Танин мэдэхүй'!AP13+'Танин мэдэхүй'!AR13+'Нийгэмшил'!V13+'Нийгэмшил'!X13)=0,"",ROUND((N('Бие бялдар'!H13)+N('Бие бялдар'!J13)+N('Бие бялдар'!L13)+N('Бие бялдар'!N13)+N('Бие бялдар'!P13)+N('Танин мэдэхүй'!AD13)+N('Танин мэдэхүй'!AF13)+N('Танин мэдэхүй'!AH13)+N('Танин мэдэхүй'!AJ13))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K10" s="12">
+        <f>IF(('Бие бялдар'!V13+'Бие бялдар'!X13+'Танин мэдэхүй'!AP13+'Танин мэдэхүй'!AR13+'Нийгэмшил'!V13+'Нийгэмшил'!X13)=0,"",ROUND((N('Танин мэдэхүй'!D13)+N('Нийгэмшил'!H13)+N('Танин мэдэхүй'!P13)+N('Танин мэдэхүй'!R13)+N('Танин мэдэхүй'!T13)+N('Танин мэдэхүй'!V13)+N('Нийгэмшил'!L13))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L10" s="12">
+        <f>IF(('Бие бялдар'!V13+'Бие бялдар'!X13+'Танин мэдэхүй'!AP13+'Танин мэдэхүй'!AR13+'Нийгэмшил'!V13+'Нийгэмшил'!X13)=0,"",ROUND((N('Танин мэдэхүй'!F13)+N('Танин мэдэхүй'!H13)+N('Танин мэдэхүй'!J13)+N('Нийгэмшил'!D13)+N('Танин мэдэхүй'!L13)+N('Танин мэдэхүй'!N13)+N('Нийгэмшил'!F13)+N('Танин мэдэхүй'!X13)+N('Танин мэдэхүй'!Z13)+N('Танин мэдэхүй'!AB13)+N('Нийгэмшил'!J13)+N('Танин мэдэхүй'!AL13)+N('Танин мэдэхүй'!AN13)+N('Нийгэмшил'!N13))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M10" s="14">
         <f>'Бие бялдар'!V13+'Танин мэдэхүй'!AP13+'Нийгэмшил'!V13</f>
         <v/>
       </c>
-      <c r="J10" s="12">
-        <f>IF(('Бие бялдар'!V13+'Бие бялдар'!X13+'Танин мэдэхүй'!AP13+'Танин мэдэхүй'!AR13+'Нийгэмшил'!V13+'Нийгэмшил'!X13)=0,"",ROUND(I10/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K10" s="15">
-        <f>IF(J10="","",IF(J10&gt;=80,"Хангалттай эзэмшиж байна",IF(J10&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N10" s="12">
+        <f>IF(('Бие бялдар'!V13+'Бие бялдар'!X13+'Танин мэдэхүй'!AP13+'Танин мэдэхүй'!AR13+'Нийгэмшил'!V13+'Нийгэмшил'!X13)=0,"",ROUND(M10/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O10" s="15">
+        <f>IF(N10="","",IF(N10&gt;=80,"Хангалттай эзэмшиж байна",IF(N10&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1357,16 +1497,32 @@
         <f>IF(('Бие бялдар'!V14+'Бие бялдар'!X14+'Танин мэдэхүй'!AP14+'Танин мэдэхүй'!AR14+'Нийгэмшил'!V14+'Нийгэмшил'!X14)=0,"",ROUND((N('Нийгэмшил'!N14)+N('Нийгэмшил'!P14)+N('Нийгэмшил'!R14)+N('Нийгэмшил'!T14))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="12">
+        <f>IF(('Бие бялдар'!V14+'Бие бялдар'!X14+'Танин мэдэхүй'!AP14+'Танин мэдэхүй'!AR14+'Нийгэмшил'!V14+'Нийгэмшил'!X14)=0,"",ROUND((N('Бие бялдар'!D14)+N('Бие бялдар'!F14)+N('Бие бялдар'!R14)+N('Бие бялдар'!T14)+N('Нийгэмшил'!P14)+N('Нийгэмшил'!R14)+N('Нийгэмшил'!T14))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J11" s="12">
+        <f>IF(('Бие бялдар'!V14+'Бие бялдар'!X14+'Танин мэдэхүй'!AP14+'Танин мэдэхүй'!AR14+'Нийгэмшил'!V14+'Нийгэмшил'!X14)=0,"",ROUND((N('Бие бялдар'!H14)+N('Бие бялдар'!J14)+N('Бие бялдар'!L14)+N('Бие бялдар'!N14)+N('Бие бялдар'!P14)+N('Танин мэдэхүй'!AD14)+N('Танин мэдэхүй'!AF14)+N('Танин мэдэхүй'!AH14)+N('Танин мэдэхүй'!AJ14))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K11" s="12">
+        <f>IF(('Бие бялдар'!V14+'Бие бялдар'!X14+'Танин мэдэхүй'!AP14+'Танин мэдэхүй'!AR14+'Нийгэмшил'!V14+'Нийгэмшил'!X14)=0,"",ROUND((N('Танин мэдэхүй'!D14)+N('Нийгэмшил'!H14)+N('Танин мэдэхүй'!P14)+N('Танин мэдэхүй'!R14)+N('Танин мэдэхүй'!T14)+N('Танин мэдэхүй'!V14)+N('Нийгэмшил'!L14))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L11" s="12">
+        <f>IF(('Бие бялдар'!V14+'Бие бялдар'!X14+'Танин мэдэхүй'!AP14+'Танин мэдэхүй'!AR14+'Нийгэмшил'!V14+'Нийгэмшил'!X14)=0,"",ROUND((N('Танин мэдэхүй'!F14)+N('Танин мэдэхүй'!H14)+N('Танин мэдэхүй'!J14)+N('Нийгэмшил'!D14)+N('Танин мэдэхүй'!L14)+N('Танин мэдэхүй'!N14)+N('Нийгэмшил'!F14)+N('Танин мэдэхүй'!X14)+N('Танин мэдэхүй'!Z14)+N('Танин мэдэхүй'!AB14)+N('Нийгэмшил'!J14)+N('Танин мэдэхүй'!AL14)+N('Танин мэдэхүй'!AN14)+N('Нийгэмшил'!N14))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M11" s="14">
         <f>'Бие бялдар'!V14+'Танин мэдэхүй'!AP14+'Нийгэмшил'!V14</f>
         <v/>
       </c>
-      <c r="J11" s="12">
-        <f>IF(('Бие бялдар'!V14+'Бие бялдар'!X14+'Танин мэдэхүй'!AP14+'Танин мэдэхүй'!AR14+'Нийгэмшил'!V14+'Нийгэмшил'!X14)=0,"",ROUND(I11/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K11" s="15">
-        <f>IF(J11="","",IF(J11&gt;=80,"Хангалттай эзэмшиж байна",IF(J11&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N11" s="12">
+        <f>IF(('Бие бялдар'!V14+'Бие бялдар'!X14+'Танин мэдэхүй'!AP14+'Танин мэдэхүй'!AR14+'Нийгэмшил'!V14+'Нийгэмшил'!X14)=0,"",ROUND(M11/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O11" s="15">
+        <f>IF(N11="","",IF(N11&gt;=80,"Хангалттай эзэмшиж байна",IF(N11&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1399,16 +1555,32 @@
         <f>IF(('Бие бялдар'!V15+'Бие бялдар'!X15+'Танин мэдэхүй'!AP15+'Танин мэдэхүй'!AR15+'Нийгэмшил'!V15+'Нийгэмшил'!X15)=0,"",ROUND((N('Нийгэмшил'!N15)+N('Нийгэмшил'!P15)+N('Нийгэмшил'!R15)+N('Нийгэмшил'!T15))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="12">
+        <f>IF(('Бие бялдар'!V15+'Бие бялдар'!X15+'Танин мэдэхүй'!AP15+'Танин мэдэхүй'!AR15+'Нийгэмшил'!V15+'Нийгэмшил'!X15)=0,"",ROUND((N('Бие бялдар'!D15)+N('Бие бялдар'!F15)+N('Бие бялдар'!R15)+N('Бие бялдар'!T15)+N('Нийгэмшил'!P15)+N('Нийгэмшил'!R15)+N('Нийгэмшил'!T15))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J12" s="12">
+        <f>IF(('Бие бялдар'!V15+'Бие бялдар'!X15+'Танин мэдэхүй'!AP15+'Танин мэдэхүй'!AR15+'Нийгэмшил'!V15+'Нийгэмшил'!X15)=0,"",ROUND((N('Бие бялдар'!H15)+N('Бие бялдар'!J15)+N('Бие бялдар'!L15)+N('Бие бялдар'!N15)+N('Бие бялдар'!P15)+N('Танин мэдэхүй'!AD15)+N('Танин мэдэхүй'!AF15)+N('Танин мэдэхүй'!AH15)+N('Танин мэдэхүй'!AJ15))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K12" s="12">
+        <f>IF(('Бие бялдар'!V15+'Бие бялдар'!X15+'Танин мэдэхүй'!AP15+'Танин мэдэхүй'!AR15+'Нийгэмшил'!V15+'Нийгэмшил'!X15)=0,"",ROUND((N('Танин мэдэхүй'!D15)+N('Нийгэмшил'!H15)+N('Танин мэдэхүй'!P15)+N('Танин мэдэхүй'!R15)+N('Танин мэдэхүй'!T15)+N('Танин мэдэхүй'!V15)+N('Нийгэмшил'!L15))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L12" s="12">
+        <f>IF(('Бие бялдар'!V15+'Бие бялдар'!X15+'Танин мэдэхүй'!AP15+'Танин мэдэхүй'!AR15+'Нийгэмшил'!V15+'Нийгэмшил'!X15)=0,"",ROUND((N('Танин мэдэхүй'!F15)+N('Танин мэдэхүй'!H15)+N('Танин мэдэхүй'!J15)+N('Нийгэмшил'!D15)+N('Танин мэдэхүй'!L15)+N('Танин мэдэхүй'!N15)+N('Нийгэмшил'!F15)+N('Танин мэдэхүй'!X15)+N('Танин мэдэхүй'!Z15)+N('Танин мэдэхүй'!AB15)+N('Нийгэмшил'!J15)+N('Танин мэдэхүй'!AL15)+N('Танин мэдэхүй'!AN15)+N('Нийгэмшил'!N15))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M12" s="14">
         <f>'Бие бялдар'!V15+'Танин мэдэхүй'!AP15+'Нийгэмшил'!V15</f>
         <v/>
       </c>
-      <c r="J12" s="12">
-        <f>IF(('Бие бялдар'!V15+'Бие бялдар'!X15+'Танин мэдэхүй'!AP15+'Танин мэдэхүй'!AR15+'Нийгэмшил'!V15+'Нийгэмшил'!X15)=0,"",ROUND(I12/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K12" s="15">
-        <f>IF(J12="","",IF(J12&gt;=80,"Хангалттай эзэмшиж байна",IF(J12&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N12" s="12">
+        <f>IF(('Бие бялдар'!V15+'Бие бялдар'!X15+'Танин мэдэхүй'!AP15+'Танин мэдэхүй'!AR15+'Нийгэмшил'!V15+'Нийгэмшил'!X15)=0,"",ROUND(M12/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O12" s="15">
+        <f>IF(N12="","",IF(N12&gt;=80,"Хангалттай эзэмшиж байна",IF(N12&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1441,16 +1613,32 @@
         <f>IF(('Бие бялдар'!V16+'Бие бялдар'!X16+'Танин мэдэхүй'!AP16+'Танин мэдэхүй'!AR16+'Нийгэмшил'!V16+'Нийгэмшил'!X16)=0,"",ROUND((N('Нийгэмшил'!N16)+N('Нийгэмшил'!P16)+N('Нийгэмшил'!R16)+N('Нийгэмшил'!T16))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="12">
+        <f>IF(('Бие бялдар'!V16+'Бие бялдар'!X16+'Танин мэдэхүй'!AP16+'Танин мэдэхүй'!AR16+'Нийгэмшил'!V16+'Нийгэмшил'!X16)=0,"",ROUND((N('Бие бялдар'!D16)+N('Бие бялдар'!F16)+N('Бие бялдар'!R16)+N('Бие бялдар'!T16)+N('Нийгэмшил'!P16)+N('Нийгэмшил'!R16)+N('Нийгэмшил'!T16))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J13" s="12">
+        <f>IF(('Бие бялдар'!V16+'Бие бялдар'!X16+'Танин мэдэхүй'!AP16+'Танин мэдэхүй'!AR16+'Нийгэмшил'!V16+'Нийгэмшил'!X16)=0,"",ROUND((N('Бие бялдар'!H16)+N('Бие бялдар'!J16)+N('Бие бялдар'!L16)+N('Бие бялдар'!N16)+N('Бие бялдар'!P16)+N('Танин мэдэхүй'!AD16)+N('Танин мэдэхүй'!AF16)+N('Танин мэдэхүй'!AH16)+N('Танин мэдэхүй'!AJ16))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K13" s="12">
+        <f>IF(('Бие бялдар'!V16+'Бие бялдар'!X16+'Танин мэдэхүй'!AP16+'Танин мэдэхүй'!AR16+'Нийгэмшил'!V16+'Нийгэмшил'!X16)=0,"",ROUND((N('Танин мэдэхүй'!D16)+N('Нийгэмшил'!H16)+N('Танин мэдэхүй'!P16)+N('Танин мэдэхүй'!R16)+N('Танин мэдэхүй'!T16)+N('Танин мэдэхүй'!V16)+N('Нийгэмшил'!L16))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L13" s="12">
+        <f>IF(('Бие бялдар'!V16+'Бие бялдар'!X16+'Танин мэдэхүй'!AP16+'Танин мэдэхүй'!AR16+'Нийгэмшил'!V16+'Нийгэмшил'!X16)=0,"",ROUND((N('Танин мэдэхүй'!F16)+N('Танин мэдэхүй'!H16)+N('Танин мэдэхүй'!J16)+N('Нийгэмшил'!D16)+N('Танин мэдэхүй'!L16)+N('Танин мэдэхүй'!N16)+N('Нийгэмшил'!F16)+N('Танин мэдэхүй'!X16)+N('Танин мэдэхүй'!Z16)+N('Танин мэдэхүй'!AB16)+N('Нийгэмшил'!J16)+N('Танин мэдэхүй'!AL16)+N('Танин мэдэхүй'!AN16)+N('Нийгэмшил'!N16))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M13" s="14">
         <f>'Бие бялдар'!V16+'Танин мэдэхүй'!AP16+'Нийгэмшил'!V16</f>
         <v/>
       </c>
-      <c r="J13" s="12">
-        <f>IF(('Бие бялдар'!V16+'Бие бялдар'!X16+'Танин мэдэхүй'!AP16+'Танин мэдэхүй'!AR16+'Нийгэмшил'!V16+'Нийгэмшил'!X16)=0,"",ROUND(I13/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K13" s="15">
-        <f>IF(J13="","",IF(J13&gt;=80,"Хангалттай эзэмшиж байна",IF(J13&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N13" s="12">
+        <f>IF(('Бие бялдар'!V16+'Бие бялдар'!X16+'Танин мэдэхүй'!AP16+'Танин мэдэхүй'!AR16+'Нийгэмшил'!V16+'Нийгэмшил'!X16)=0,"",ROUND(M13/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O13" s="15">
+        <f>IF(N13="","",IF(N13&gt;=80,"Хангалттай эзэмшиж байна",IF(N13&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1483,16 +1671,32 @@
         <f>IF(('Бие бялдар'!V17+'Бие бялдар'!X17+'Танин мэдэхүй'!AP17+'Танин мэдэхүй'!AR17+'Нийгэмшил'!V17+'Нийгэмшил'!X17)=0,"",ROUND((N('Нийгэмшил'!N17)+N('Нийгэмшил'!P17)+N('Нийгэмшил'!R17)+N('Нийгэмшил'!T17))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="12">
+        <f>IF(('Бие бялдар'!V17+'Бие бялдар'!X17+'Танин мэдэхүй'!AP17+'Танин мэдэхүй'!AR17+'Нийгэмшил'!V17+'Нийгэмшил'!X17)=0,"",ROUND((N('Бие бялдар'!D17)+N('Бие бялдар'!F17)+N('Бие бялдар'!R17)+N('Бие бялдар'!T17)+N('Нийгэмшил'!P17)+N('Нийгэмшил'!R17)+N('Нийгэмшил'!T17))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J14" s="12">
+        <f>IF(('Бие бялдар'!V17+'Бие бялдар'!X17+'Танин мэдэхүй'!AP17+'Танин мэдэхүй'!AR17+'Нийгэмшил'!V17+'Нийгэмшил'!X17)=0,"",ROUND((N('Бие бялдар'!H17)+N('Бие бялдар'!J17)+N('Бие бялдар'!L17)+N('Бие бялдар'!N17)+N('Бие бялдар'!P17)+N('Танин мэдэхүй'!AD17)+N('Танин мэдэхүй'!AF17)+N('Танин мэдэхүй'!AH17)+N('Танин мэдэхүй'!AJ17))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K14" s="12">
+        <f>IF(('Бие бялдар'!V17+'Бие бялдар'!X17+'Танин мэдэхүй'!AP17+'Танин мэдэхүй'!AR17+'Нийгэмшил'!V17+'Нийгэмшил'!X17)=0,"",ROUND((N('Танин мэдэхүй'!D17)+N('Нийгэмшил'!H17)+N('Танин мэдэхүй'!P17)+N('Танин мэдэхүй'!R17)+N('Танин мэдэхүй'!T17)+N('Танин мэдэхүй'!V17)+N('Нийгэмшил'!L17))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L14" s="12">
+        <f>IF(('Бие бялдар'!V17+'Бие бялдар'!X17+'Танин мэдэхүй'!AP17+'Танин мэдэхүй'!AR17+'Нийгэмшил'!V17+'Нийгэмшил'!X17)=0,"",ROUND((N('Танин мэдэхүй'!F17)+N('Танин мэдэхүй'!H17)+N('Танин мэдэхүй'!J17)+N('Нийгэмшил'!D17)+N('Танин мэдэхүй'!L17)+N('Танин мэдэхүй'!N17)+N('Нийгэмшил'!F17)+N('Танин мэдэхүй'!X17)+N('Танин мэдэхүй'!Z17)+N('Танин мэдэхүй'!AB17)+N('Нийгэмшил'!J17)+N('Танин мэдэхүй'!AL17)+N('Танин мэдэхүй'!AN17)+N('Нийгэмшил'!N17))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M14" s="14">
         <f>'Бие бялдар'!V17+'Танин мэдэхүй'!AP17+'Нийгэмшил'!V17</f>
         <v/>
       </c>
-      <c r="J14" s="12">
-        <f>IF(('Бие бялдар'!V17+'Бие бялдар'!X17+'Танин мэдэхүй'!AP17+'Танин мэдэхүй'!AR17+'Нийгэмшил'!V17+'Нийгэмшил'!X17)=0,"",ROUND(I14/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K14" s="15">
-        <f>IF(J14="","",IF(J14&gt;=80,"Хангалттай эзэмшиж байна",IF(J14&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N14" s="12">
+        <f>IF(('Бие бялдар'!V17+'Бие бялдар'!X17+'Танин мэдэхүй'!AP17+'Танин мэдэхүй'!AR17+'Нийгэмшил'!V17+'Нийгэмшил'!X17)=0,"",ROUND(M14/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O14" s="15">
+        <f>IF(N14="","",IF(N14&gt;=80,"Хангалттай эзэмшиж байна",IF(N14&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1525,16 +1729,32 @@
         <f>IF(('Бие бялдар'!V18+'Бие бялдар'!X18+'Танин мэдэхүй'!AP18+'Танин мэдэхүй'!AR18+'Нийгэмшил'!V18+'Нийгэмшил'!X18)=0,"",ROUND((N('Нийгэмшил'!N18)+N('Нийгэмшил'!P18)+N('Нийгэмшил'!R18)+N('Нийгэмшил'!T18))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="12">
+        <f>IF(('Бие бялдар'!V18+'Бие бялдар'!X18+'Танин мэдэхүй'!AP18+'Танин мэдэхүй'!AR18+'Нийгэмшил'!V18+'Нийгэмшил'!X18)=0,"",ROUND((N('Бие бялдар'!D18)+N('Бие бялдар'!F18)+N('Бие бялдар'!R18)+N('Бие бялдар'!T18)+N('Нийгэмшил'!P18)+N('Нийгэмшил'!R18)+N('Нийгэмшил'!T18))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J15" s="12">
+        <f>IF(('Бие бялдар'!V18+'Бие бялдар'!X18+'Танин мэдэхүй'!AP18+'Танин мэдэхүй'!AR18+'Нийгэмшил'!V18+'Нийгэмшил'!X18)=0,"",ROUND((N('Бие бялдар'!H18)+N('Бие бялдар'!J18)+N('Бие бялдар'!L18)+N('Бие бялдар'!N18)+N('Бие бялдар'!P18)+N('Танин мэдэхүй'!AD18)+N('Танин мэдэхүй'!AF18)+N('Танин мэдэхүй'!AH18)+N('Танин мэдэхүй'!AJ18))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K15" s="12">
+        <f>IF(('Бие бялдар'!V18+'Бие бялдар'!X18+'Танин мэдэхүй'!AP18+'Танин мэдэхүй'!AR18+'Нийгэмшил'!V18+'Нийгэмшил'!X18)=0,"",ROUND((N('Танин мэдэхүй'!D18)+N('Нийгэмшил'!H18)+N('Танин мэдэхүй'!P18)+N('Танин мэдэхүй'!R18)+N('Танин мэдэхүй'!T18)+N('Танин мэдэхүй'!V18)+N('Нийгэмшил'!L18))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L15" s="12">
+        <f>IF(('Бие бялдар'!V18+'Бие бялдар'!X18+'Танин мэдэхүй'!AP18+'Танин мэдэхүй'!AR18+'Нийгэмшил'!V18+'Нийгэмшил'!X18)=0,"",ROUND((N('Танин мэдэхүй'!F18)+N('Танин мэдэхүй'!H18)+N('Танин мэдэхүй'!J18)+N('Нийгэмшил'!D18)+N('Танин мэдэхүй'!L18)+N('Танин мэдэхүй'!N18)+N('Нийгэмшил'!F18)+N('Танин мэдэхүй'!X18)+N('Танин мэдэхүй'!Z18)+N('Танин мэдэхүй'!AB18)+N('Нийгэмшил'!J18)+N('Танин мэдэхүй'!AL18)+N('Танин мэдэхүй'!AN18)+N('Нийгэмшил'!N18))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M15" s="14">
         <f>'Бие бялдар'!V18+'Танин мэдэхүй'!AP18+'Нийгэмшил'!V18</f>
         <v/>
       </c>
-      <c r="J15" s="12">
-        <f>IF(('Бие бялдар'!V18+'Бие бялдар'!X18+'Танин мэдэхүй'!AP18+'Танин мэдэхүй'!AR18+'Нийгэмшил'!V18+'Нийгэмшил'!X18)=0,"",ROUND(I15/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K15" s="15">
-        <f>IF(J15="","",IF(J15&gt;=80,"Хангалттай эзэмшиж байна",IF(J15&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N15" s="12">
+        <f>IF(('Бие бялдар'!V18+'Бие бялдар'!X18+'Танин мэдэхүй'!AP18+'Танин мэдэхүй'!AR18+'Нийгэмшил'!V18+'Нийгэмшил'!X18)=0,"",ROUND(M15/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O15" s="15">
+        <f>IF(N15="","",IF(N15&gt;=80,"Хангалттай эзэмшиж байна",IF(N15&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1567,16 +1787,32 @@
         <f>IF(('Бие бялдар'!V19+'Бие бялдар'!X19+'Танин мэдэхүй'!AP19+'Танин мэдэхүй'!AR19+'Нийгэмшил'!V19+'Нийгэмшил'!X19)=0,"",ROUND((N('Нийгэмшил'!N19)+N('Нийгэмшил'!P19)+N('Нийгэмшил'!R19)+N('Нийгэмшил'!T19))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="12">
+        <f>IF(('Бие бялдар'!V19+'Бие бялдар'!X19+'Танин мэдэхүй'!AP19+'Танин мэдэхүй'!AR19+'Нийгэмшил'!V19+'Нийгэмшил'!X19)=0,"",ROUND((N('Бие бялдар'!D19)+N('Бие бялдар'!F19)+N('Бие бялдар'!R19)+N('Бие бялдар'!T19)+N('Нийгэмшил'!P19)+N('Нийгэмшил'!R19)+N('Нийгэмшил'!T19))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J16" s="12">
+        <f>IF(('Бие бялдар'!V19+'Бие бялдар'!X19+'Танин мэдэхүй'!AP19+'Танин мэдэхүй'!AR19+'Нийгэмшил'!V19+'Нийгэмшил'!X19)=0,"",ROUND((N('Бие бялдар'!H19)+N('Бие бялдар'!J19)+N('Бие бялдар'!L19)+N('Бие бялдар'!N19)+N('Бие бялдар'!P19)+N('Танин мэдэхүй'!AD19)+N('Танин мэдэхүй'!AF19)+N('Танин мэдэхүй'!AH19)+N('Танин мэдэхүй'!AJ19))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K16" s="12">
+        <f>IF(('Бие бялдар'!V19+'Бие бялдар'!X19+'Танин мэдэхүй'!AP19+'Танин мэдэхүй'!AR19+'Нийгэмшил'!V19+'Нийгэмшил'!X19)=0,"",ROUND((N('Танин мэдэхүй'!D19)+N('Нийгэмшил'!H19)+N('Танин мэдэхүй'!P19)+N('Танин мэдэхүй'!R19)+N('Танин мэдэхүй'!T19)+N('Танин мэдэхүй'!V19)+N('Нийгэмшил'!L19))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L16" s="12">
+        <f>IF(('Бие бялдар'!V19+'Бие бялдар'!X19+'Танин мэдэхүй'!AP19+'Танин мэдэхүй'!AR19+'Нийгэмшил'!V19+'Нийгэмшил'!X19)=0,"",ROUND((N('Танин мэдэхүй'!F19)+N('Танин мэдэхүй'!H19)+N('Танин мэдэхүй'!J19)+N('Нийгэмшил'!D19)+N('Танин мэдэхүй'!L19)+N('Танин мэдэхүй'!N19)+N('Нийгэмшил'!F19)+N('Танин мэдэхүй'!X19)+N('Танин мэдэхүй'!Z19)+N('Танин мэдэхүй'!AB19)+N('Нийгэмшил'!J19)+N('Танин мэдэхүй'!AL19)+N('Танин мэдэхүй'!AN19)+N('Нийгэмшил'!N19))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M16" s="14">
         <f>'Бие бялдар'!V19+'Танин мэдэхүй'!AP19+'Нийгэмшил'!V19</f>
         <v/>
       </c>
-      <c r="J16" s="12">
-        <f>IF(('Бие бялдар'!V19+'Бие бялдар'!X19+'Танин мэдэхүй'!AP19+'Танин мэдэхүй'!AR19+'Нийгэмшил'!V19+'Нийгэмшил'!X19)=0,"",ROUND(I16/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K16" s="15">
-        <f>IF(J16="","",IF(J16&gt;=80,"Хангалттай эзэмшиж байна",IF(J16&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N16" s="12">
+        <f>IF(('Бие бялдар'!V19+'Бие бялдар'!X19+'Танин мэдэхүй'!AP19+'Танин мэдэхүй'!AR19+'Нийгэмшил'!V19+'Нийгэмшил'!X19)=0,"",ROUND(M16/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O16" s="15">
+        <f>IF(N16="","",IF(N16&gt;=80,"Хангалттай эзэмшиж байна",IF(N16&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1609,16 +1845,32 @@
         <f>IF(('Бие бялдар'!V20+'Бие бялдар'!X20+'Танин мэдэхүй'!AP20+'Танин мэдэхүй'!AR20+'Нийгэмшил'!V20+'Нийгэмшил'!X20)=0,"",ROUND((N('Нийгэмшил'!N20)+N('Нийгэмшил'!P20)+N('Нийгэмшил'!R20)+N('Нийгэмшил'!T20))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="12">
+        <f>IF(('Бие бялдар'!V20+'Бие бялдар'!X20+'Танин мэдэхүй'!AP20+'Танин мэдэхүй'!AR20+'Нийгэмшил'!V20+'Нийгэмшил'!X20)=0,"",ROUND((N('Бие бялдар'!D20)+N('Бие бялдар'!F20)+N('Бие бялдар'!R20)+N('Бие бялдар'!T20)+N('Нийгэмшил'!P20)+N('Нийгэмшил'!R20)+N('Нийгэмшил'!T20))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J17" s="12">
+        <f>IF(('Бие бялдар'!V20+'Бие бялдар'!X20+'Танин мэдэхүй'!AP20+'Танин мэдэхүй'!AR20+'Нийгэмшил'!V20+'Нийгэмшил'!X20)=0,"",ROUND((N('Бие бялдар'!H20)+N('Бие бялдар'!J20)+N('Бие бялдар'!L20)+N('Бие бялдар'!N20)+N('Бие бялдар'!P20)+N('Танин мэдэхүй'!AD20)+N('Танин мэдэхүй'!AF20)+N('Танин мэдэхүй'!AH20)+N('Танин мэдэхүй'!AJ20))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K17" s="12">
+        <f>IF(('Бие бялдар'!V20+'Бие бялдар'!X20+'Танин мэдэхүй'!AP20+'Танин мэдэхүй'!AR20+'Нийгэмшил'!V20+'Нийгэмшил'!X20)=0,"",ROUND((N('Танин мэдэхүй'!D20)+N('Нийгэмшил'!H20)+N('Танин мэдэхүй'!P20)+N('Танин мэдэхүй'!R20)+N('Танин мэдэхүй'!T20)+N('Танин мэдэхүй'!V20)+N('Нийгэмшил'!L20))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L17" s="12">
+        <f>IF(('Бие бялдар'!V20+'Бие бялдар'!X20+'Танин мэдэхүй'!AP20+'Танин мэдэхүй'!AR20+'Нийгэмшил'!V20+'Нийгэмшил'!X20)=0,"",ROUND((N('Танин мэдэхүй'!F20)+N('Танин мэдэхүй'!H20)+N('Танин мэдэхүй'!J20)+N('Нийгэмшил'!D20)+N('Танин мэдэхүй'!L20)+N('Танин мэдэхүй'!N20)+N('Нийгэмшил'!F20)+N('Танин мэдэхүй'!X20)+N('Танин мэдэхүй'!Z20)+N('Танин мэдэхүй'!AB20)+N('Нийгэмшил'!J20)+N('Танин мэдэхүй'!AL20)+N('Танин мэдэхүй'!AN20)+N('Нийгэмшил'!N20))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M17" s="14">
         <f>'Бие бялдар'!V20+'Танин мэдэхүй'!AP20+'Нийгэмшил'!V20</f>
         <v/>
       </c>
-      <c r="J17" s="12">
-        <f>IF(('Бие бялдар'!V20+'Бие бялдар'!X20+'Танин мэдэхүй'!AP20+'Танин мэдэхүй'!AR20+'Нийгэмшил'!V20+'Нийгэмшил'!X20)=0,"",ROUND(I17/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K17" s="15">
-        <f>IF(J17="","",IF(J17&gt;=80,"Хангалттай эзэмшиж байна",IF(J17&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N17" s="12">
+        <f>IF(('Бие бялдар'!V20+'Бие бялдар'!X20+'Танин мэдэхүй'!AP20+'Танин мэдэхүй'!AR20+'Нийгэмшил'!V20+'Нийгэмшил'!X20)=0,"",ROUND(M17/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O17" s="15">
+        <f>IF(N17="","",IF(N17&gt;=80,"Хангалттай эзэмшиж байна",IF(N17&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1651,16 +1903,32 @@
         <f>IF(('Бие бялдар'!V21+'Бие бялдар'!X21+'Танин мэдэхүй'!AP21+'Танин мэдэхүй'!AR21+'Нийгэмшил'!V21+'Нийгэмшил'!X21)=0,"",ROUND((N('Нийгэмшил'!N21)+N('Нийгэмшил'!P21)+N('Нийгэмшил'!R21)+N('Нийгэмшил'!T21))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="12">
+        <f>IF(('Бие бялдар'!V21+'Бие бялдар'!X21+'Танин мэдэхүй'!AP21+'Танин мэдэхүй'!AR21+'Нийгэмшил'!V21+'Нийгэмшил'!X21)=0,"",ROUND((N('Бие бялдар'!D21)+N('Бие бялдар'!F21)+N('Бие бялдар'!R21)+N('Бие бялдар'!T21)+N('Нийгэмшил'!P21)+N('Нийгэмшил'!R21)+N('Нийгэмшил'!T21))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J18" s="12">
+        <f>IF(('Бие бялдар'!V21+'Бие бялдар'!X21+'Танин мэдэхүй'!AP21+'Танин мэдэхүй'!AR21+'Нийгэмшил'!V21+'Нийгэмшил'!X21)=0,"",ROUND((N('Бие бялдар'!H21)+N('Бие бялдар'!J21)+N('Бие бялдар'!L21)+N('Бие бялдар'!N21)+N('Бие бялдар'!P21)+N('Танин мэдэхүй'!AD21)+N('Танин мэдэхүй'!AF21)+N('Танин мэдэхүй'!AH21)+N('Танин мэдэхүй'!AJ21))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K18" s="12">
+        <f>IF(('Бие бялдар'!V21+'Бие бялдар'!X21+'Танин мэдэхүй'!AP21+'Танин мэдэхүй'!AR21+'Нийгэмшил'!V21+'Нийгэмшил'!X21)=0,"",ROUND((N('Танин мэдэхүй'!D21)+N('Нийгэмшил'!H21)+N('Танин мэдэхүй'!P21)+N('Танин мэдэхүй'!R21)+N('Танин мэдэхүй'!T21)+N('Танин мэдэхүй'!V21)+N('Нийгэмшил'!L21))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L18" s="12">
+        <f>IF(('Бие бялдар'!V21+'Бие бялдар'!X21+'Танин мэдэхүй'!AP21+'Танин мэдэхүй'!AR21+'Нийгэмшил'!V21+'Нийгэмшил'!X21)=0,"",ROUND((N('Танин мэдэхүй'!F21)+N('Танин мэдэхүй'!H21)+N('Танин мэдэхүй'!J21)+N('Нийгэмшил'!D21)+N('Танин мэдэхүй'!L21)+N('Танин мэдэхүй'!N21)+N('Нийгэмшил'!F21)+N('Танин мэдэхүй'!X21)+N('Танин мэдэхүй'!Z21)+N('Танин мэдэхүй'!AB21)+N('Нийгэмшил'!J21)+N('Танин мэдэхүй'!AL21)+N('Танин мэдэхүй'!AN21)+N('Нийгэмшил'!N21))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M18" s="14">
         <f>'Бие бялдар'!V21+'Танин мэдэхүй'!AP21+'Нийгэмшил'!V21</f>
         <v/>
       </c>
-      <c r="J18" s="12">
-        <f>IF(('Бие бялдар'!V21+'Бие бялдар'!X21+'Танин мэдэхүй'!AP21+'Танин мэдэхүй'!AR21+'Нийгэмшил'!V21+'Нийгэмшил'!X21)=0,"",ROUND(I18/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K18" s="15">
-        <f>IF(J18="","",IF(J18&gt;=80,"Хангалттай эзэмшиж байна",IF(J18&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N18" s="12">
+        <f>IF(('Бие бялдар'!V21+'Бие бялдар'!X21+'Танин мэдэхүй'!AP21+'Танин мэдэхүй'!AR21+'Нийгэмшил'!V21+'Нийгэмшил'!X21)=0,"",ROUND(M18/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O18" s="15">
+        <f>IF(N18="","",IF(N18&gt;=80,"Хангалттай эзэмшиж байна",IF(N18&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1693,16 +1961,32 @@
         <f>IF(('Бие бялдар'!V22+'Бие бялдар'!X22+'Танин мэдэхүй'!AP22+'Танин мэдэхүй'!AR22+'Нийгэмшил'!V22+'Нийгэмшил'!X22)=0,"",ROUND((N('Нийгэмшил'!N22)+N('Нийгэмшил'!P22)+N('Нийгэмшил'!R22)+N('Нийгэмшил'!T22))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="12">
+        <f>IF(('Бие бялдар'!V22+'Бие бялдар'!X22+'Танин мэдэхүй'!AP22+'Танин мэдэхүй'!AR22+'Нийгэмшил'!V22+'Нийгэмшил'!X22)=0,"",ROUND((N('Бие бялдар'!D22)+N('Бие бялдар'!F22)+N('Бие бялдар'!R22)+N('Бие бялдар'!T22)+N('Нийгэмшил'!P22)+N('Нийгэмшил'!R22)+N('Нийгэмшил'!T22))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J19" s="12">
+        <f>IF(('Бие бялдар'!V22+'Бие бялдар'!X22+'Танин мэдэхүй'!AP22+'Танин мэдэхүй'!AR22+'Нийгэмшил'!V22+'Нийгэмшил'!X22)=0,"",ROUND((N('Бие бялдар'!H22)+N('Бие бялдар'!J22)+N('Бие бялдар'!L22)+N('Бие бялдар'!N22)+N('Бие бялдар'!P22)+N('Танин мэдэхүй'!AD22)+N('Танин мэдэхүй'!AF22)+N('Танин мэдэхүй'!AH22)+N('Танин мэдэхүй'!AJ22))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K19" s="12">
+        <f>IF(('Бие бялдар'!V22+'Бие бялдар'!X22+'Танин мэдэхүй'!AP22+'Танин мэдэхүй'!AR22+'Нийгэмшил'!V22+'Нийгэмшил'!X22)=0,"",ROUND((N('Танин мэдэхүй'!D22)+N('Нийгэмшил'!H22)+N('Танин мэдэхүй'!P22)+N('Танин мэдэхүй'!R22)+N('Танин мэдэхүй'!T22)+N('Танин мэдэхүй'!V22)+N('Нийгэмшил'!L22))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L19" s="12">
+        <f>IF(('Бие бялдар'!V22+'Бие бялдар'!X22+'Танин мэдэхүй'!AP22+'Танин мэдэхүй'!AR22+'Нийгэмшил'!V22+'Нийгэмшил'!X22)=0,"",ROUND((N('Танин мэдэхүй'!F22)+N('Танин мэдэхүй'!H22)+N('Танин мэдэхүй'!J22)+N('Нийгэмшил'!D22)+N('Танин мэдэхүй'!L22)+N('Танин мэдэхүй'!N22)+N('Нийгэмшил'!F22)+N('Танин мэдэхүй'!X22)+N('Танин мэдэхүй'!Z22)+N('Танин мэдэхүй'!AB22)+N('Нийгэмшил'!J22)+N('Танин мэдэхүй'!AL22)+N('Танин мэдэхүй'!AN22)+N('Нийгэмшил'!N22))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M19" s="14">
         <f>'Бие бялдар'!V22+'Танин мэдэхүй'!AP22+'Нийгэмшил'!V22</f>
         <v/>
       </c>
-      <c r="J19" s="12">
-        <f>IF(('Бие бялдар'!V22+'Бие бялдар'!X22+'Танин мэдэхүй'!AP22+'Танин мэдэхүй'!AR22+'Нийгэмшил'!V22+'Нийгэмшил'!X22)=0,"",ROUND(I19/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K19" s="15">
-        <f>IF(J19="","",IF(J19&gt;=80,"Хангалттай эзэмшиж байна",IF(J19&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N19" s="12">
+        <f>IF(('Бие бялдар'!V22+'Бие бялдар'!X22+'Танин мэдэхүй'!AP22+'Танин мэдэхүй'!AR22+'Нийгэмшил'!V22+'Нийгэмшил'!X22)=0,"",ROUND(M19/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O19" s="15">
+        <f>IF(N19="","",IF(N19&gt;=80,"Хангалттай эзэмшиж байна",IF(N19&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1735,16 +2019,32 @@
         <f>IF(('Бие бялдар'!V23+'Бие бялдар'!X23+'Танин мэдэхүй'!AP23+'Танин мэдэхүй'!AR23+'Нийгэмшил'!V23+'Нийгэмшил'!X23)=0,"",ROUND((N('Нийгэмшил'!N23)+N('Нийгэмшил'!P23)+N('Нийгэмшил'!R23)+N('Нийгэмшил'!T23))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="12">
+        <f>IF(('Бие бялдар'!V23+'Бие бялдар'!X23+'Танин мэдэхүй'!AP23+'Танин мэдэхүй'!AR23+'Нийгэмшил'!V23+'Нийгэмшил'!X23)=0,"",ROUND((N('Бие бялдар'!D23)+N('Бие бялдар'!F23)+N('Бие бялдар'!R23)+N('Бие бялдар'!T23)+N('Нийгэмшил'!P23)+N('Нийгэмшил'!R23)+N('Нийгэмшил'!T23))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J20" s="12">
+        <f>IF(('Бие бялдар'!V23+'Бие бялдар'!X23+'Танин мэдэхүй'!AP23+'Танин мэдэхүй'!AR23+'Нийгэмшил'!V23+'Нийгэмшил'!X23)=0,"",ROUND((N('Бие бялдар'!H23)+N('Бие бялдар'!J23)+N('Бие бялдар'!L23)+N('Бие бялдар'!N23)+N('Бие бялдар'!P23)+N('Танин мэдэхүй'!AD23)+N('Танин мэдэхүй'!AF23)+N('Танин мэдэхүй'!AH23)+N('Танин мэдэхүй'!AJ23))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K20" s="12">
+        <f>IF(('Бие бялдар'!V23+'Бие бялдар'!X23+'Танин мэдэхүй'!AP23+'Танин мэдэхүй'!AR23+'Нийгэмшил'!V23+'Нийгэмшил'!X23)=0,"",ROUND((N('Танин мэдэхүй'!D23)+N('Нийгэмшил'!H23)+N('Танин мэдэхүй'!P23)+N('Танин мэдэхүй'!R23)+N('Танин мэдэхүй'!T23)+N('Танин мэдэхүй'!V23)+N('Нийгэмшил'!L23))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L20" s="12">
+        <f>IF(('Бие бялдар'!V23+'Бие бялдар'!X23+'Танин мэдэхүй'!AP23+'Танин мэдэхүй'!AR23+'Нийгэмшил'!V23+'Нийгэмшил'!X23)=0,"",ROUND((N('Танин мэдэхүй'!F23)+N('Танин мэдэхүй'!H23)+N('Танин мэдэхүй'!J23)+N('Нийгэмшил'!D23)+N('Танин мэдэхүй'!L23)+N('Танин мэдэхүй'!N23)+N('Нийгэмшил'!F23)+N('Танин мэдэхүй'!X23)+N('Танин мэдэхүй'!Z23)+N('Танин мэдэхүй'!AB23)+N('Нийгэмшил'!J23)+N('Танин мэдэхүй'!AL23)+N('Танин мэдэхүй'!AN23)+N('Нийгэмшил'!N23))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M20" s="14">
         <f>'Бие бялдар'!V23+'Танин мэдэхүй'!AP23+'Нийгэмшил'!V23</f>
         <v/>
       </c>
-      <c r="J20" s="12">
-        <f>IF(('Бие бялдар'!V23+'Бие бялдар'!X23+'Танин мэдэхүй'!AP23+'Танин мэдэхүй'!AR23+'Нийгэмшил'!V23+'Нийгэмшил'!X23)=0,"",ROUND(I20/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K20" s="15">
-        <f>IF(J20="","",IF(J20&gt;=80,"Хангалттай эзэмшиж байна",IF(J20&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N20" s="12">
+        <f>IF(('Бие бялдар'!V23+'Бие бялдар'!X23+'Танин мэдэхүй'!AP23+'Танин мэдэхүй'!AR23+'Нийгэмшил'!V23+'Нийгэмшил'!X23)=0,"",ROUND(M20/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O20" s="15">
+        <f>IF(N20="","",IF(N20&gt;=80,"Хангалттай эзэмшиж байна",IF(N20&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1777,16 +2077,32 @@
         <f>IF(('Бие бялдар'!V24+'Бие бялдар'!X24+'Танин мэдэхүй'!AP24+'Танин мэдэхүй'!AR24+'Нийгэмшил'!V24+'Нийгэмшил'!X24)=0,"",ROUND((N('Нийгэмшил'!N24)+N('Нийгэмшил'!P24)+N('Нийгэмшил'!R24)+N('Нийгэмшил'!T24))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="12">
+        <f>IF(('Бие бялдар'!V24+'Бие бялдар'!X24+'Танин мэдэхүй'!AP24+'Танин мэдэхүй'!AR24+'Нийгэмшил'!V24+'Нийгэмшил'!X24)=0,"",ROUND((N('Бие бялдар'!D24)+N('Бие бялдар'!F24)+N('Бие бялдар'!R24)+N('Бие бялдар'!T24)+N('Нийгэмшил'!P24)+N('Нийгэмшил'!R24)+N('Нийгэмшил'!T24))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J21" s="12">
+        <f>IF(('Бие бялдар'!V24+'Бие бялдар'!X24+'Танин мэдэхүй'!AP24+'Танин мэдэхүй'!AR24+'Нийгэмшил'!V24+'Нийгэмшил'!X24)=0,"",ROUND((N('Бие бялдар'!H24)+N('Бие бялдар'!J24)+N('Бие бялдар'!L24)+N('Бие бялдар'!N24)+N('Бие бялдар'!P24)+N('Танин мэдэхүй'!AD24)+N('Танин мэдэхүй'!AF24)+N('Танин мэдэхүй'!AH24)+N('Танин мэдэхүй'!AJ24))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K21" s="12">
+        <f>IF(('Бие бялдар'!V24+'Бие бялдар'!X24+'Танин мэдэхүй'!AP24+'Танин мэдэхүй'!AR24+'Нийгэмшил'!V24+'Нийгэмшил'!X24)=0,"",ROUND((N('Танин мэдэхүй'!D24)+N('Нийгэмшил'!H24)+N('Танин мэдэхүй'!P24)+N('Танин мэдэхүй'!R24)+N('Танин мэдэхүй'!T24)+N('Танин мэдэхүй'!V24)+N('Нийгэмшил'!L24))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L21" s="12">
+        <f>IF(('Бие бялдар'!V24+'Бие бялдар'!X24+'Танин мэдэхүй'!AP24+'Танин мэдэхүй'!AR24+'Нийгэмшил'!V24+'Нийгэмшил'!X24)=0,"",ROUND((N('Танин мэдэхүй'!F24)+N('Танин мэдэхүй'!H24)+N('Танин мэдэхүй'!J24)+N('Нийгэмшил'!D24)+N('Танин мэдэхүй'!L24)+N('Танин мэдэхүй'!N24)+N('Нийгэмшил'!F24)+N('Танин мэдэхүй'!X24)+N('Танин мэдэхүй'!Z24)+N('Танин мэдэхүй'!AB24)+N('Нийгэмшил'!J24)+N('Танин мэдэхүй'!AL24)+N('Танин мэдэхүй'!AN24)+N('Нийгэмшил'!N24))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M21" s="14">
         <f>'Бие бялдар'!V24+'Танин мэдэхүй'!AP24+'Нийгэмшил'!V24</f>
         <v/>
       </c>
-      <c r="J21" s="12">
-        <f>IF(('Бие бялдар'!V24+'Бие бялдар'!X24+'Танин мэдэхүй'!AP24+'Танин мэдэхүй'!AR24+'Нийгэмшил'!V24+'Нийгэмшил'!X24)=0,"",ROUND(I21/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K21" s="15">
-        <f>IF(J21="","",IF(J21&gt;=80,"Хангалттай эзэмшиж байна",IF(J21&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N21" s="12">
+        <f>IF(('Бие бялдар'!V24+'Бие бялдар'!X24+'Танин мэдэхүй'!AP24+'Танин мэдэхүй'!AR24+'Нийгэмшил'!V24+'Нийгэмшил'!X24)=0,"",ROUND(M21/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O21" s="15">
+        <f>IF(N21="","",IF(N21&gt;=80,"Хангалттай эзэмшиж байна",IF(N21&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1819,16 +2135,32 @@
         <f>IF(('Бие бялдар'!V25+'Бие бялдар'!X25+'Танин мэдэхүй'!AP25+'Танин мэдэхүй'!AR25+'Нийгэмшил'!V25+'Нийгэмшил'!X25)=0,"",ROUND((N('Нийгэмшил'!N25)+N('Нийгэмшил'!P25)+N('Нийгэмшил'!R25)+N('Нийгэмшил'!T25))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="12">
+        <f>IF(('Бие бялдар'!V25+'Бие бялдар'!X25+'Танин мэдэхүй'!AP25+'Танин мэдэхүй'!AR25+'Нийгэмшил'!V25+'Нийгэмшил'!X25)=0,"",ROUND((N('Бие бялдар'!D25)+N('Бие бялдар'!F25)+N('Бие бялдар'!R25)+N('Бие бялдар'!T25)+N('Нийгэмшил'!P25)+N('Нийгэмшил'!R25)+N('Нийгэмшил'!T25))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>IF(('Бие бялдар'!V25+'Бие бялдар'!X25+'Танин мэдэхүй'!AP25+'Танин мэдэхүй'!AR25+'Нийгэмшил'!V25+'Нийгэмшил'!X25)=0,"",ROUND((N('Бие бялдар'!H25)+N('Бие бялдар'!J25)+N('Бие бялдар'!L25)+N('Бие бялдар'!N25)+N('Бие бялдар'!P25)+N('Танин мэдэхүй'!AD25)+N('Танин мэдэхүй'!AF25)+N('Танин мэдэхүй'!AH25)+N('Танин мэдэхүй'!AJ25))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>IF(('Бие бялдар'!V25+'Бие бялдар'!X25+'Танин мэдэхүй'!AP25+'Танин мэдэхүй'!AR25+'Нийгэмшил'!V25+'Нийгэмшил'!X25)=0,"",ROUND((N('Танин мэдэхүй'!D25)+N('Нийгэмшил'!H25)+N('Танин мэдэхүй'!P25)+N('Танин мэдэхүй'!R25)+N('Танин мэдэхүй'!T25)+N('Танин мэдэхүй'!V25)+N('Нийгэмшил'!L25))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L22" s="12">
+        <f>IF(('Бие бялдар'!V25+'Бие бялдар'!X25+'Танин мэдэхүй'!AP25+'Танин мэдэхүй'!AR25+'Нийгэмшил'!V25+'Нийгэмшил'!X25)=0,"",ROUND((N('Танин мэдэхүй'!F25)+N('Танин мэдэхүй'!H25)+N('Танин мэдэхүй'!J25)+N('Нийгэмшил'!D25)+N('Танин мэдэхүй'!L25)+N('Танин мэдэхүй'!N25)+N('Нийгэмшил'!F25)+N('Танин мэдэхүй'!X25)+N('Танин мэдэхүй'!Z25)+N('Танин мэдэхүй'!AB25)+N('Нийгэмшил'!J25)+N('Танин мэдэхүй'!AL25)+N('Танин мэдэхүй'!AN25)+N('Нийгэмшил'!N25))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M22" s="14">
         <f>'Бие бялдар'!V25+'Танин мэдэхүй'!AP25+'Нийгэмшил'!V25</f>
         <v/>
       </c>
-      <c r="J22" s="12">
-        <f>IF(('Бие бялдар'!V25+'Бие бялдар'!X25+'Танин мэдэхүй'!AP25+'Танин мэдэхүй'!AR25+'Нийгэмшил'!V25+'Нийгэмшил'!X25)=0,"",ROUND(I22/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K22" s="15">
-        <f>IF(J22="","",IF(J22&gt;=80,"Хангалттай эзэмшиж байна",IF(J22&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N22" s="12">
+        <f>IF(('Бие бялдар'!V25+'Бие бялдар'!X25+'Танин мэдэхүй'!AP25+'Танин мэдэхүй'!AR25+'Нийгэмшил'!V25+'Нийгэмшил'!X25)=0,"",ROUND(M22/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O22" s="15">
+        <f>IF(N22="","",IF(N22&gt;=80,"Хангалттай эзэмшиж байна",IF(N22&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1861,16 +2193,32 @@
         <f>IF(('Бие бялдар'!V26+'Бие бялдар'!X26+'Танин мэдэхүй'!AP26+'Танин мэдэхүй'!AR26+'Нийгэмшил'!V26+'Нийгэмшил'!X26)=0,"",ROUND((N('Нийгэмшил'!N26)+N('Нийгэмшил'!P26)+N('Нийгэмшил'!R26)+N('Нийгэмшил'!T26))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="12">
+        <f>IF(('Бие бялдар'!V26+'Бие бялдар'!X26+'Танин мэдэхүй'!AP26+'Танин мэдэхүй'!AR26+'Нийгэмшил'!V26+'Нийгэмшил'!X26)=0,"",ROUND((N('Бие бялдар'!D26)+N('Бие бялдар'!F26)+N('Бие бялдар'!R26)+N('Бие бялдар'!T26)+N('Нийгэмшил'!P26)+N('Нийгэмшил'!R26)+N('Нийгэмшил'!T26))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J23" s="12">
+        <f>IF(('Бие бялдар'!V26+'Бие бялдар'!X26+'Танин мэдэхүй'!AP26+'Танин мэдэхүй'!AR26+'Нийгэмшил'!V26+'Нийгэмшил'!X26)=0,"",ROUND((N('Бие бялдар'!H26)+N('Бие бялдар'!J26)+N('Бие бялдар'!L26)+N('Бие бялдар'!N26)+N('Бие бялдар'!P26)+N('Танин мэдэхүй'!AD26)+N('Танин мэдэхүй'!AF26)+N('Танин мэдэхүй'!AH26)+N('Танин мэдэхүй'!AJ26))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K23" s="12">
+        <f>IF(('Бие бялдар'!V26+'Бие бялдар'!X26+'Танин мэдэхүй'!AP26+'Танин мэдэхүй'!AR26+'Нийгэмшил'!V26+'Нийгэмшил'!X26)=0,"",ROUND((N('Танин мэдэхүй'!D26)+N('Нийгэмшил'!H26)+N('Танин мэдэхүй'!P26)+N('Танин мэдэхүй'!R26)+N('Танин мэдэхүй'!T26)+N('Танин мэдэхүй'!V26)+N('Нийгэмшил'!L26))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L23" s="12">
+        <f>IF(('Бие бялдар'!V26+'Бие бялдар'!X26+'Танин мэдэхүй'!AP26+'Танин мэдэхүй'!AR26+'Нийгэмшил'!V26+'Нийгэмшил'!X26)=0,"",ROUND((N('Танин мэдэхүй'!F26)+N('Танин мэдэхүй'!H26)+N('Танин мэдэхүй'!J26)+N('Нийгэмшил'!D26)+N('Танин мэдэхүй'!L26)+N('Танин мэдэхүй'!N26)+N('Нийгэмшил'!F26)+N('Танин мэдэхүй'!X26)+N('Танин мэдэхүй'!Z26)+N('Танин мэдэхүй'!AB26)+N('Нийгэмшил'!J26)+N('Танин мэдэхүй'!AL26)+N('Танин мэдэхүй'!AN26)+N('Нийгэмшил'!N26))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M23" s="14">
         <f>'Бие бялдар'!V26+'Танин мэдэхүй'!AP26+'Нийгэмшил'!V26</f>
         <v/>
       </c>
-      <c r="J23" s="12">
-        <f>IF(('Бие бялдар'!V26+'Бие бялдар'!X26+'Танин мэдэхүй'!AP26+'Танин мэдэхүй'!AR26+'Нийгэмшил'!V26+'Нийгэмшил'!X26)=0,"",ROUND(I23/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K23" s="15">
-        <f>IF(J23="","",IF(J23&gt;=80,"Хангалттай эзэмшиж байна",IF(J23&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N23" s="12">
+        <f>IF(('Бие бялдар'!V26+'Бие бялдар'!X26+'Танин мэдэхүй'!AP26+'Танин мэдэхүй'!AR26+'Нийгэмшил'!V26+'Нийгэмшил'!X26)=0,"",ROUND(M23/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O23" s="15">
+        <f>IF(N23="","",IF(N23&gt;=80,"Хангалттай эзэмшиж байна",IF(N23&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1903,16 +2251,32 @@
         <f>IF(('Бие бялдар'!V27+'Бие бялдар'!X27+'Танин мэдэхүй'!AP27+'Танин мэдэхүй'!AR27+'Нийгэмшил'!V27+'Нийгэмшил'!X27)=0,"",ROUND((N('Нийгэмшил'!N27)+N('Нийгэмшил'!P27)+N('Нийгэмшил'!R27)+N('Нийгэмшил'!T27))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="12">
+        <f>IF(('Бие бялдар'!V27+'Бие бялдар'!X27+'Танин мэдэхүй'!AP27+'Танин мэдэхүй'!AR27+'Нийгэмшил'!V27+'Нийгэмшил'!X27)=0,"",ROUND((N('Бие бялдар'!D27)+N('Бие бялдар'!F27)+N('Бие бялдар'!R27)+N('Бие бялдар'!T27)+N('Нийгэмшил'!P27)+N('Нийгэмшил'!R27)+N('Нийгэмшил'!T27))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J24" s="12">
+        <f>IF(('Бие бялдар'!V27+'Бие бялдар'!X27+'Танин мэдэхүй'!AP27+'Танин мэдэхүй'!AR27+'Нийгэмшил'!V27+'Нийгэмшил'!X27)=0,"",ROUND((N('Бие бялдар'!H27)+N('Бие бялдар'!J27)+N('Бие бялдар'!L27)+N('Бие бялдар'!N27)+N('Бие бялдар'!P27)+N('Танин мэдэхүй'!AD27)+N('Танин мэдэхүй'!AF27)+N('Танин мэдэхүй'!AH27)+N('Танин мэдэхүй'!AJ27))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K24" s="12">
+        <f>IF(('Бие бялдар'!V27+'Бие бялдар'!X27+'Танин мэдэхүй'!AP27+'Танин мэдэхүй'!AR27+'Нийгэмшил'!V27+'Нийгэмшил'!X27)=0,"",ROUND((N('Танин мэдэхүй'!D27)+N('Нийгэмшил'!H27)+N('Танин мэдэхүй'!P27)+N('Танин мэдэхүй'!R27)+N('Танин мэдэхүй'!T27)+N('Танин мэдэхүй'!V27)+N('Нийгэмшил'!L27))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L24" s="12">
+        <f>IF(('Бие бялдар'!V27+'Бие бялдар'!X27+'Танин мэдэхүй'!AP27+'Танин мэдэхүй'!AR27+'Нийгэмшил'!V27+'Нийгэмшил'!X27)=0,"",ROUND((N('Танин мэдэхүй'!F27)+N('Танин мэдэхүй'!H27)+N('Танин мэдэхүй'!J27)+N('Нийгэмшил'!D27)+N('Танин мэдэхүй'!L27)+N('Танин мэдэхүй'!N27)+N('Нийгэмшил'!F27)+N('Танин мэдэхүй'!X27)+N('Танин мэдэхүй'!Z27)+N('Танин мэдэхүй'!AB27)+N('Нийгэмшил'!J27)+N('Танин мэдэхүй'!AL27)+N('Танин мэдэхүй'!AN27)+N('Нийгэмшил'!N27))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M24" s="14">
         <f>'Бие бялдар'!V27+'Танин мэдэхүй'!AP27+'Нийгэмшил'!V27</f>
         <v/>
       </c>
-      <c r="J24" s="12">
-        <f>IF(('Бие бялдар'!V27+'Бие бялдар'!X27+'Танин мэдэхүй'!AP27+'Танин мэдэхүй'!AR27+'Нийгэмшил'!V27+'Нийгэмшил'!X27)=0,"",ROUND(I24/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K24" s="15">
-        <f>IF(J24="","",IF(J24&gt;=80,"Хангалттай эзэмшиж байна",IF(J24&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N24" s="12">
+        <f>IF(('Бие бялдар'!V27+'Бие бялдар'!X27+'Танин мэдэхүй'!AP27+'Танин мэдэхүй'!AR27+'Нийгэмшил'!V27+'Нийгэмшил'!X27)=0,"",ROUND(M24/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O24" s="15">
+        <f>IF(N24="","",IF(N24&gt;=80,"Хангалттай эзэмшиж байна",IF(N24&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1945,16 +2309,32 @@
         <f>IF(('Бие бялдар'!V28+'Бие бялдар'!X28+'Танин мэдэхүй'!AP28+'Танин мэдэхүй'!AR28+'Нийгэмшил'!V28+'Нийгэмшил'!X28)=0,"",ROUND((N('Нийгэмшил'!N28)+N('Нийгэмшил'!P28)+N('Нийгэмшил'!R28)+N('Нийгэмшил'!T28))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="12">
+        <f>IF(('Бие бялдар'!V28+'Бие бялдар'!X28+'Танин мэдэхүй'!AP28+'Танин мэдэхүй'!AR28+'Нийгэмшил'!V28+'Нийгэмшил'!X28)=0,"",ROUND((N('Бие бялдар'!D28)+N('Бие бялдар'!F28)+N('Бие бялдар'!R28)+N('Бие бялдар'!T28)+N('Нийгэмшил'!P28)+N('Нийгэмшил'!R28)+N('Нийгэмшил'!T28))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>IF(('Бие бялдар'!V28+'Бие бялдар'!X28+'Танин мэдэхүй'!AP28+'Танин мэдэхүй'!AR28+'Нийгэмшил'!V28+'Нийгэмшил'!X28)=0,"",ROUND((N('Бие бялдар'!H28)+N('Бие бялдар'!J28)+N('Бие бялдар'!L28)+N('Бие бялдар'!N28)+N('Бие бялдар'!P28)+N('Танин мэдэхүй'!AD28)+N('Танин мэдэхүй'!AF28)+N('Танин мэдэхүй'!AH28)+N('Танин мэдэхүй'!AJ28))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K25" s="12">
+        <f>IF(('Бие бялдар'!V28+'Бие бялдар'!X28+'Танин мэдэхүй'!AP28+'Танин мэдэхүй'!AR28+'Нийгэмшил'!V28+'Нийгэмшил'!X28)=0,"",ROUND((N('Танин мэдэхүй'!D28)+N('Нийгэмшил'!H28)+N('Танин мэдэхүй'!P28)+N('Танин мэдэхүй'!R28)+N('Танин мэдэхүй'!T28)+N('Танин мэдэхүй'!V28)+N('Нийгэмшил'!L28))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L25" s="12">
+        <f>IF(('Бие бялдар'!V28+'Бие бялдар'!X28+'Танин мэдэхүй'!AP28+'Танин мэдэхүй'!AR28+'Нийгэмшил'!V28+'Нийгэмшил'!X28)=0,"",ROUND((N('Танин мэдэхүй'!F28)+N('Танин мэдэхүй'!H28)+N('Танин мэдэхүй'!J28)+N('Нийгэмшил'!D28)+N('Танин мэдэхүй'!L28)+N('Танин мэдэхүй'!N28)+N('Нийгэмшил'!F28)+N('Танин мэдэхүй'!X28)+N('Танин мэдэхүй'!Z28)+N('Танин мэдэхүй'!AB28)+N('Нийгэмшил'!J28)+N('Танин мэдэхүй'!AL28)+N('Танин мэдэхүй'!AN28)+N('Нийгэмшил'!N28))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M25" s="14">
         <f>'Бие бялдар'!V28+'Танин мэдэхүй'!AP28+'Нийгэмшил'!V28</f>
         <v/>
       </c>
-      <c r="J25" s="12">
-        <f>IF(('Бие бялдар'!V28+'Бие бялдар'!X28+'Танин мэдэхүй'!AP28+'Танин мэдэхүй'!AR28+'Нийгэмшил'!V28+'Нийгэмшил'!X28)=0,"",ROUND(I25/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K25" s="15">
-        <f>IF(J25="","",IF(J25&gt;=80,"Хангалттай эзэмшиж байна",IF(J25&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N25" s="12">
+        <f>IF(('Бие бялдар'!V28+'Бие бялдар'!X28+'Танин мэдэхүй'!AP28+'Танин мэдэхүй'!AR28+'Нийгэмшил'!V28+'Нийгэмшил'!X28)=0,"",ROUND(M25/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O25" s="15">
+        <f>IF(N25="","",IF(N25&gt;=80,"Хангалттай эзэмшиж байна",IF(N25&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -1987,16 +2367,32 @@
         <f>IF(('Бие бялдар'!V29+'Бие бялдар'!X29+'Танин мэдэхүй'!AP29+'Танин мэдэхүй'!AR29+'Нийгэмшил'!V29+'Нийгэмшил'!X29)=0,"",ROUND((N('Нийгэмшил'!N29)+N('Нийгэмшил'!P29)+N('Нийгэмшил'!R29)+N('Нийгэмшил'!T29))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="12">
+        <f>IF(('Бие бялдар'!V29+'Бие бялдар'!X29+'Танин мэдэхүй'!AP29+'Танин мэдэхүй'!AR29+'Нийгэмшил'!V29+'Нийгэмшил'!X29)=0,"",ROUND((N('Бие бялдар'!D29)+N('Бие бялдар'!F29)+N('Бие бялдар'!R29)+N('Бие бялдар'!T29)+N('Нийгэмшил'!P29)+N('Нийгэмшил'!R29)+N('Нийгэмшил'!T29))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J26" s="12">
+        <f>IF(('Бие бялдар'!V29+'Бие бялдар'!X29+'Танин мэдэхүй'!AP29+'Танин мэдэхүй'!AR29+'Нийгэмшил'!V29+'Нийгэмшил'!X29)=0,"",ROUND((N('Бие бялдар'!H29)+N('Бие бялдар'!J29)+N('Бие бялдар'!L29)+N('Бие бялдар'!N29)+N('Бие бялдар'!P29)+N('Танин мэдэхүй'!AD29)+N('Танин мэдэхүй'!AF29)+N('Танин мэдэхүй'!AH29)+N('Танин мэдэхүй'!AJ29))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K26" s="12">
+        <f>IF(('Бие бялдар'!V29+'Бие бялдар'!X29+'Танин мэдэхүй'!AP29+'Танин мэдэхүй'!AR29+'Нийгэмшил'!V29+'Нийгэмшил'!X29)=0,"",ROUND((N('Танин мэдэхүй'!D29)+N('Нийгэмшил'!H29)+N('Танин мэдэхүй'!P29)+N('Танин мэдэхүй'!R29)+N('Танин мэдэхүй'!T29)+N('Танин мэдэхүй'!V29)+N('Нийгэмшил'!L29))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L26" s="12">
+        <f>IF(('Бие бялдар'!V29+'Бие бялдар'!X29+'Танин мэдэхүй'!AP29+'Танин мэдэхүй'!AR29+'Нийгэмшил'!V29+'Нийгэмшил'!X29)=0,"",ROUND((N('Танин мэдэхүй'!F29)+N('Танин мэдэхүй'!H29)+N('Танин мэдэхүй'!J29)+N('Нийгэмшил'!D29)+N('Танин мэдэхүй'!L29)+N('Танин мэдэхүй'!N29)+N('Нийгэмшил'!F29)+N('Танин мэдэхүй'!X29)+N('Танин мэдэхүй'!Z29)+N('Танин мэдэхүй'!AB29)+N('Нийгэмшил'!J29)+N('Танин мэдэхүй'!AL29)+N('Танин мэдэхүй'!AN29)+N('Нийгэмшил'!N29))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M26" s="14">
         <f>'Бие бялдар'!V29+'Танин мэдэхүй'!AP29+'Нийгэмшил'!V29</f>
         <v/>
       </c>
-      <c r="J26" s="12">
-        <f>IF(('Бие бялдар'!V29+'Бие бялдар'!X29+'Танин мэдэхүй'!AP29+'Танин мэдэхүй'!AR29+'Нийгэмшил'!V29+'Нийгэмшил'!X29)=0,"",ROUND(I26/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K26" s="15">
-        <f>IF(J26="","",IF(J26&gt;=80,"Хангалттай эзэмшиж байна",IF(J26&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N26" s="12">
+        <f>IF(('Бие бялдар'!V29+'Бие бялдар'!X29+'Танин мэдэхүй'!AP29+'Танин мэдэхүй'!AR29+'Нийгэмшил'!V29+'Нийгэмшил'!X29)=0,"",ROUND(M26/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O26" s="15">
+        <f>IF(N26="","",IF(N26&gt;=80,"Хангалттай эзэмшиж байна",IF(N26&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2029,16 +2425,32 @@
         <f>IF(('Бие бялдар'!V30+'Бие бялдар'!X30+'Танин мэдэхүй'!AP30+'Танин мэдэхүй'!AR30+'Нийгэмшил'!V30+'Нийгэмшил'!X30)=0,"",ROUND((N('Нийгэмшил'!N30)+N('Нийгэмшил'!P30)+N('Нийгэмшил'!R30)+N('Нийгэмшил'!T30))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="12">
+        <f>IF(('Бие бялдар'!V30+'Бие бялдар'!X30+'Танин мэдэхүй'!AP30+'Танин мэдэхүй'!AR30+'Нийгэмшил'!V30+'Нийгэмшил'!X30)=0,"",ROUND((N('Бие бялдар'!D30)+N('Бие бялдар'!F30)+N('Бие бялдар'!R30)+N('Бие бялдар'!T30)+N('Нийгэмшил'!P30)+N('Нийгэмшил'!R30)+N('Нийгэмшил'!T30))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J27" s="12">
+        <f>IF(('Бие бялдар'!V30+'Бие бялдар'!X30+'Танин мэдэхүй'!AP30+'Танин мэдэхүй'!AR30+'Нийгэмшил'!V30+'Нийгэмшил'!X30)=0,"",ROUND((N('Бие бялдар'!H30)+N('Бие бялдар'!J30)+N('Бие бялдар'!L30)+N('Бие бялдар'!N30)+N('Бие бялдар'!P30)+N('Танин мэдэхүй'!AD30)+N('Танин мэдэхүй'!AF30)+N('Танин мэдэхүй'!AH30)+N('Танин мэдэхүй'!AJ30))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K27" s="12">
+        <f>IF(('Бие бялдар'!V30+'Бие бялдар'!X30+'Танин мэдэхүй'!AP30+'Танин мэдэхүй'!AR30+'Нийгэмшил'!V30+'Нийгэмшил'!X30)=0,"",ROUND((N('Танин мэдэхүй'!D30)+N('Нийгэмшил'!H30)+N('Танин мэдэхүй'!P30)+N('Танин мэдэхүй'!R30)+N('Танин мэдэхүй'!T30)+N('Танин мэдэхүй'!V30)+N('Нийгэмшил'!L30))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L27" s="12">
+        <f>IF(('Бие бялдар'!V30+'Бие бялдар'!X30+'Танин мэдэхүй'!AP30+'Танин мэдэхүй'!AR30+'Нийгэмшил'!V30+'Нийгэмшил'!X30)=0,"",ROUND((N('Танин мэдэхүй'!F30)+N('Танин мэдэхүй'!H30)+N('Танин мэдэхүй'!J30)+N('Нийгэмшил'!D30)+N('Танин мэдэхүй'!L30)+N('Танин мэдэхүй'!N30)+N('Нийгэмшил'!F30)+N('Танин мэдэхүй'!X30)+N('Танин мэдэхүй'!Z30)+N('Танин мэдэхүй'!AB30)+N('Нийгэмшил'!J30)+N('Танин мэдэхүй'!AL30)+N('Танин мэдэхүй'!AN30)+N('Нийгэмшил'!N30))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M27" s="14">
         <f>'Бие бялдар'!V30+'Танин мэдэхүй'!AP30+'Нийгэмшил'!V30</f>
         <v/>
       </c>
-      <c r="J27" s="12">
-        <f>IF(('Бие бялдар'!V30+'Бие бялдар'!X30+'Танин мэдэхүй'!AP30+'Танин мэдэхүй'!AR30+'Нийгэмшил'!V30+'Нийгэмшил'!X30)=0,"",ROUND(I27/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K27" s="15">
-        <f>IF(J27="","",IF(J27&gt;=80,"Хангалттай эзэмшиж байна",IF(J27&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N27" s="12">
+        <f>IF(('Бие бялдар'!V30+'Бие бялдар'!X30+'Танин мэдэхүй'!AP30+'Танин мэдэхүй'!AR30+'Нийгэмшил'!V30+'Нийгэмшил'!X30)=0,"",ROUND(M27/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O27" s="15">
+        <f>IF(N27="","",IF(N27&gt;=80,"Хангалттай эзэмшиж байна",IF(N27&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2071,16 +2483,32 @@
         <f>IF(('Бие бялдар'!V31+'Бие бялдар'!X31+'Танин мэдэхүй'!AP31+'Танин мэдэхүй'!AR31+'Нийгэмшил'!V31+'Нийгэмшил'!X31)=0,"",ROUND((N('Нийгэмшил'!N31)+N('Нийгэмшил'!P31)+N('Нийгэмшил'!R31)+N('Нийгэмшил'!T31))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="12">
+        <f>IF(('Бие бялдар'!V31+'Бие бялдар'!X31+'Танин мэдэхүй'!AP31+'Танин мэдэхүй'!AR31+'Нийгэмшил'!V31+'Нийгэмшил'!X31)=0,"",ROUND((N('Бие бялдар'!D31)+N('Бие бялдар'!F31)+N('Бие бялдар'!R31)+N('Бие бялдар'!T31)+N('Нийгэмшил'!P31)+N('Нийгэмшил'!R31)+N('Нийгэмшил'!T31))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J28" s="12">
+        <f>IF(('Бие бялдар'!V31+'Бие бялдар'!X31+'Танин мэдэхүй'!AP31+'Танин мэдэхүй'!AR31+'Нийгэмшил'!V31+'Нийгэмшил'!X31)=0,"",ROUND((N('Бие бялдар'!H31)+N('Бие бялдар'!J31)+N('Бие бялдар'!L31)+N('Бие бялдар'!N31)+N('Бие бялдар'!P31)+N('Танин мэдэхүй'!AD31)+N('Танин мэдэхүй'!AF31)+N('Танин мэдэхүй'!AH31)+N('Танин мэдэхүй'!AJ31))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K28" s="12">
+        <f>IF(('Бие бялдар'!V31+'Бие бялдар'!X31+'Танин мэдэхүй'!AP31+'Танин мэдэхүй'!AR31+'Нийгэмшил'!V31+'Нийгэмшил'!X31)=0,"",ROUND((N('Танин мэдэхүй'!D31)+N('Нийгэмшил'!H31)+N('Танин мэдэхүй'!P31)+N('Танин мэдэхүй'!R31)+N('Танин мэдэхүй'!T31)+N('Танин мэдэхүй'!V31)+N('Нийгэмшил'!L31))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L28" s="12">
+        <f>IF(('Бие бялдар'!V31+'Бие бялдар'!X31+'Танин мэдэхүй'!AP31+'Танин мэдэхүй'!AR31+'Нийгэмшил'!V31+'Нийгэмшил'!X31)=0,"",ROUND((N('Танин мэдэхүй'!F31)+N('Танин мэдэхүй'!H31)+N('Танин мэдэхүй'!J31)+N('Нийгэмшил'!D31)+N('Танин мэдэхүй'!L31)+N('Танин мэдэхүй'!N31)+N('Нийгэмшил'!F31)+N('Танин мэдэхүй'!X31)+N('Танин мэдэхүй'!Z31)+N('Танин мэдэхүй'!AB31)+N('Нийгэмшил'!J31)+N('Танин мэдэхүй'!AL31)+N('Танин мэдэхүй'!AN31)+N('Нийгэмшил'!N31))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M28" s="14">
         <f>'Бие бялдар'!V31+'Танин мэдэхүй'!AP31+'Нийгэмшил'!V31</f>
         <v/>
       </c>
-      <c r="J28" s="12">
-        <f>IF(('Бие бялдар'!V31+'Бие бялдар'!X31+'Танин мэдэхүй'!AP31+'Танин мэдэхүй'!AR31+'Нийгэмшил'!V31+'Нийгэмшил'!X31)=0,"",ROUND(I28/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K28" s="15">
-        <f>IF(J28="","",IF(J28&gt;=80,"Хангалттай эзэмшиж байна",IF(J28&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N28" s="12">
+        <f>IF(('Бие бялдар'!V31+'Бие бялдар'!X31+'Танин мэдэхүй'!AP31+'Танин мэдэхүй'!AR31+'Нийгэмшил'!V31+'Нийгэмшил'!X31)=0,"",ROUND(M28/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O28" s="15">
+        <f>IF(N28="","",IF(N28&gt;=80,"Хангалттай эзэмшиж байна",IF(N28&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2113,16 +2541,32 @@
         <f>IF(('Бие бялдар'!V32+'Бие бялдар'!X32+'Танин мэдэхүй'!AP32+'Танин мэдэхүй'!AR32+'Нийгэмшил'!V32+'Нийгэмшил'!X32)=0,"",ROUND((N('Нийгэмшил'!N32)+N('Нийгэмшил'!P32)+N('Нийгэмшил'!R32)+N('Нийгэмшил'!T32))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="12">
+        <f>IF(('Бие бялдар'!V32+'Бие бялдар'!X32+'Танин мэдэхүй'!AP32+'Танин мэдэхүй'!AR32+'Нийгэмшил'!V32+'Нийгэмшил'!X32)=0,"",ROUND((N('Бие бялдар'!D32)+N('Бие бялдар'!F32)+N('Бие бялдар'!R32)+N('Бие бялдар'!T32)+N('Нийгэмшил'!P32)+N('Нийгэмшил'!R32)+N('Нийгэмшил'!T32))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J29" s="12">
+        <f>IF(('Бие бялдар'!V32+'Бие бялдар'!X32+'Танин мэдэхүй'!AP32+'Танин мэдэхүй'!AR32+'Нийгэмшил'!V32+'Нийгэмшил'!X32)=0,"",ROUND((N('Бие бялдар'!H32)+N('Бие бялдар'!J32)+N('Бие бялдар'!L32)+N('Бие бялдар'!N32)+N('Бие бялдар'!P32)+N('Танин мэдэхүй'!AD32)+N('Танин мэдэхүй'!AF32)+N('Танин мэдэхүй'!AH32)+N('Танин мэдэхүй'!AJ32))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K29" s="12">
+        <f>IF(('Бие бялдар'!V32+'Бие бялдар'!X32+'Танин мэдэхүй'!AP32+'Танин мэдэхүй'!AR32+'Нийгэмшил'!V32+'Нийгэмшил'!X32)=0,"",ROUND((N('Танин мэдэхүй'!D32)+N('Нийгэмшил'!H32)+N('Танин мэдэхүй'!P32)+N('Танин мэдэхүй'!R32)+N('Танин мэдэхүй'!T32)+N('Танин мэдэхүй'!V32)+N('Нийгэмшил'!L32))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L29" s="12">
+        <f>IF(('Бие бялдар'!V32+'Бие бялдар'!X32+'Танин мэдэхүй'!AP32+'Танин мэдэхүй'!AR32+'Нийгэмшил'!V32+'Нийгэмшил'!X32)=0,"",ROUND((N('Танин мэдэхүй'!F32)+N('Танин мэдэхүй'!H32)+N('Танин мэдэхүй'!J32)+N('Нийгэмшил'!D32)+N('Танин мэдэхүй'!L32)+N('Танин мэдэхүй'!N32)+N('Нийгэмшил'!F32)+N('Танин мэдэхүй'!X32)+N('Танин мэдэхүй'!Z32)+N('Танин мэдэхүй'!AB32)+N('Нийгэмшил'!J32)+N('Танин мэдэхүй'!AL32)+N('Танин мэдэхүй'!AN32)+N('Нийгэмшил'!N32))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M29" s="14">
         <f>'Бие бялдар'!V32+'Танин мэдэхүй'!AP32+'Нийгэмшил'!V32</f>
         <v/>
       </c>
-      <c r="J29" s="12">
-        <f>IF(('Бие бялдар'!V32+'Бие бялдар'!X32+'Танин мэдэхүй'!AP32+'Танин мэдэхүй'!AR32+'Нийгэмшил'!V32+'Нийгэмшил'!X32)=0,"",ROUND(I29/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K29" s="15">
-        <f>IF(J29="","",IF(J29&gt;=80,"Хангалттай эзэмшиж байна",IF(J29&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N29" s="12">
+        <f>IF(('Бие бялдар'!V32+'Бие бялдар'!X32+'Танин мэдэхүй'!AP32+'Танин мэдэхүй'!AR32+'Нийгэмшил'!V32+'Нийгэмшил'!X32)=0,"",ROUND(M29/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O29" s="15">
+        <f>IF(N29="","",IF(N29&gt;=80,"Хангалттай эзэмшиж байна",IF(N29&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2155,16 +2599,32 @@
         <f>IF(('Бие бялдар'!V33+'Бие бялдар'!X33+'Танин мэдэхүй'!AP33+'Танин мэдэхүй'!AR33+'Нийгэмшил'!V33+'Нийгэмшил'!X33)=0,"",ROUND((N('Нийгэмшил'!N33)+N('Нийгэмшил'!P33)+N('Нийгэмшил'!R33)+N('Нийгэмшил'!T33))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="12">
+        <f>IF(('Бие бялдар'!V33+'Бие бялдар'!X33+'Танин мэдэхүй'!AP33+'Танин мэдэхүй'!AR33+'Нийгэмшил'!V33+'Нийгэмшил'!X33)=0,"",ROUND((N('Бие бялдар'!D33)+N('Бие бялдар'!F33)+N('Бие бялдар'!R33)+N('Бие бялдар'!T33)+N('Нийгэмшил'!P33)+N('Нийгэмшил'!R33)+N('Нийгэмшил'!T33))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J30" s="12">
+        <f>IF(('Бие бялдар'!V33+'Бие бялдар'!X33+'Танин мэдэхүй'!AP33+'Танин мэдэхүй'!AR33+'Нийгэмшил'!V33+'Нийгэмшил'!X33)=0,"",ROUND((N('Бие бялдар'!H33)+N('Бие бялдар'!J33)+N('Бие бялдар'!L33)+N('Бие бялдар'!N33)+N('Бие бялдар'!P33)+N('Танин мэдэхүй'!AD33)+N('Танин мэдэхүй'!AF33)+N('Танин мэдэхүй'!AH33)+N('Танин мэдэхүй'!AJ33))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K30" s="12">
+        <f>IF(('Бие бялдар'!V33+'Бие бялдар'!X33+'Танин мэдэхүй'!AP33+'Танин мэдэхүй'!AR33+'Нийгэмшил'!V33+'Нийгэмшил'!X33)=0,"",ROUND((N('Танин мэдэхүй'!D33)+N('Нийгэмшил'!H33)+N('Танин мэдэхүй'!P33)+N('Танин мэдэхүй'!R33)+N('Танин мэдэхүй'!T33)+N('Танин мэдэхүй'!V33)+N('Нийгэмшил'!L33))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L30" s="12">
+        <f>IF(('Бие бялдар'!V33+'Бие бялдар'!X33+'Танин мэдэхүй'!AP33+'Танин мэдэхүй'!AR33+'Нийгэмшил'!V33+'Нийгэмшил'!X33)=0,"",ROUND((N('Танин мэдэхүй'!F33)+N('Танин мэдэхүй'!H33)+N('Танин мэдэхүй'!J33)+N('Нийгэмшил'!D33)+N('Танин мэдэхүй'!L33)+N('Танин мэдэхүй'!N33)+N('Нийгэмшил'!F33)+N('Танин мэдэхүй'!X33)+N('Танин мэдэхүй'!Z33)+N('Танин мэдэхүй'!AB33)+N('Нийгэмшил'!J33)+N('Танин мэдэхүй'!AL33)+N('Танин мэдэхүй'!AN33)+N('Нийгэмшил'!N33))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M30" s="14">
         <f>'Бие бялдар'!V33+'Танин мэдэхүй'!AP33+'Нийгэмшил'!V33</f>
         <v/>
       </c>
-      <c r="J30" s="12">
-        <f>IF(('Бие бялдар'!V33+'Бие бялдар'!X33+'Танин мэдэхүй'!AP33+'Танин мэдэхүй'!AR33+'Нийгэмшил'!V33+'Нийгэмшил'!X33)=0,"",ROUND(I30/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K30" s="15">
-        <f>IF(J30="","",IF(J30&gt;=80,"Хангалттай эзэмшиж байна",IF(J30&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N30" s="12">
+        <f>IF(('Бие бялдар'!V33+'Бие бялдар'!X33+'Танин мэдэхүй'!AP33+'Танин мэдэхүй'!AR33+'Нийгэмшил'!V33+'Нийгэмшил'!X33)=0,"",ROUND(M30/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O30" s="15">
+        <f>IF(N30="","",IF(N30&gt;=80,"Хангалттай эзэмшиж байна",IF(N30&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2197,16 +2657,32 @@
         <f>IF(('Бие бялдар'!V34+'Бие бялдар'!X34+'Танин мэдэхүй'!AP34+'Танин мэдэхүй'!AR34+'Нийгэмшил'!V34+'Нийгэмшил'!X34)=0,"",ROUND((N('Нийгэмшил'!N34)+N('Нийгэмшил'!P34)+N('Нийгэмшил'!R34)+N('Нийгэмшил'!T34))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="12">
+        <f>IF(('Бие бялдар'!V34+'Бие бялдар'!X34+'Танин мэдэхүй'!AP34+'Танин мэдэхүй'!AR34+'Нийгэмшил'!V34+'Нийгэмшил'!X34)=0,"",ROUND((N('Бие бялдар'!D34)+N('Бие бялдар'!F34)+N('Бие бялдар'!R34)+N('Бие бялдар'!T34)+N('Нийгэмшил'!P34)+N('Нийгэмшил'!R34)+N('Нийгэмшил'!T34))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J31" s="12">
+        <f>IF(('Бие бялдар'!V34+'Бие бялдар'!X34+'Танин мэдэхүй'!AP34+'Танин мэдэхүй'!AR34+'Нийгэмшил'!V34+'Нийгэмшил'!X34)=0,"",ROUND((N('Бие бялдар'!H34)+N('Бие бялдар'!J34)+N('Бие бялдар'!L34)+N('Бие бялдар'!N34)+N('Бие бялдар'!P34)+N('Танин мэдэхүй'!AD34)+N('Танин мэдэхүй'!AF34)+N('Танин мэдэхүй'!AH34)+N('Танин мэдэхүй'!AJ34))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K31" s="12">
+        <f>IF(('Бие бялдар'!V34+'Бие бялдар'!X34+'Танин мэдэхүй'!AP34+'Танин мэдэхүй'!AR34+'Нийгэмшил'!V34+'Нийгэмшил'!X34)=0,"",ROUND((N('Танин мэдэхүй'!D34)+N('Нийгэмшил'!H34)+N('Танин мэдэхүй'!P34)+N('Танин мэдэхүй'!R34)+N('Танин мэдэхүй'!T34)+N('Танин мэдэхүй'!V34)+N('Нийгэмшил'!L34))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L31" s="12">
+        <f>IF(('Бие бялдар'!V34+'Бие бялдар'!X34+'Танин мэдэхүй'!AP34+'Танин мэдэхүй'!AR34+'Нийгэмшил'!V34+'Нийгэмшил'!X34)=0,"",ROUND((N('Танин мэдэхүй'!F34)+N('Танин мэдэхүй'!H34)+N('Танин мэдэхүй'!J34)+N('Нийгэмшил'!D34)+N('Танин мэдэхүй'!L34)+N('Танин мэдэхүй'!N34)+N('Нийгэмшил'!F34)+N('Танин мэдэхүй'!X34)+N('Танин мэдэхүй'!Z34)+N('Танин мэдэхүй'!AB34)+N('Нийгэмшил'!J34)+N('Танин мэдэхүй'!AL34)+N('Танин мэдэхүй'!AN34)+N('Нийгэмшил'!N34))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M31" s="14">
         <f>'Бие бялдар'!V34+'Танин мэдэхүй'!AP34+'Нийгэмшил'!V34</f>
         <v/>
       </c>
-      <c r="J31" s="12">
-        <f>IF(('Бие бялдар'!V34+'Бие бялдар'!X34+'Танин мэдэхүй'!AP34+'Танин мэдэхүй'!AR34+'Нийгэмшил'!V34+'Нийгэмшил'!X34)=0,"",ROUND(I31/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K31" s="15">
-        <f>IF(J31="","",IF(J31&gt;=80,"Хангалттай эзэмшиж байна",IF(J31&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N31" s="12">
+        <f>IF(('Бие бялдар'!V34+'Бие бялдар'!X34+'Танин мэдэхүй'!AP34+'Танин мэдэхүй'!AR34+'Нийгэмшил'!V34+'Нийгэмшил'!X34)=0,"",ROUND(M31/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O31" s="15">
+        <f>IF(N31="","",IF(N31&gt;=80,"Хангалттай эзэмшиж байна",IF(N31&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2239,16 +2715,32 @@
         <f>IF(('Бие бялдар'!V35+'Бие бялдар'!X35+'Танин мэдэхүй'!AP35+'Танин мэдэхүй'!AR35+'Нийгэмшил'!V35+'Нийгэмшил'!X35)=0,"",ROUND((N('Нийгэмшил'!N35)+N('Нийгэмшил'!P35)+N('Нийгэмшил'!R35)+N('Нийгэмшил'!T35))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="12">
+        <f>IF(('Бие бялдар'!V35+'Бие бялдар'!X35+'Танин мэдэхүй'!AP35+'Танин мэдэхүй'!AR35+'Нийгэмшил'!V35+'Нийгэмшил'!X35)=0,"",ROUND((N('Бие бялдар'!D35)+N('Бие бялдар'!F35)+N('Бие бялдар'!R35)+N('Бие бялдар'!T35)+N('Нийгэмшил'!P35)+N('Нийгэмшил'!R35)+N('Нийгэмшил'!T35))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J32" s="12">
+        <f>IF(('Бие бялдар'!V35+'Бие бялдар'!X35+'Танин мэдэхүй'!AP35+'Танин мэдэхүй'!AR35+'Нийгэмшил'!V35+'Нийгэмшил'!X35)=0,"",ROUND((N('Бие бялдар'!H35)+N('Бие бялдар'!J35)+N('Бие бялдар'!L35)+N('Бие бялдар'!N35)+N('Бие бялдар'!P35)+N('Танин мэдэхүй'!AD35)+N('Танин мэдэхүй'!AF35)+N('Танин мэдэхүй'!AH35)+N('Танин мэдэхүй'!AJ35))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K32" s="12">
+        <f>IF(('Бие бялдар'!V35+'Бие бялдар'!X35+'Танин мэдэхүй'!AP35+'Танин мэдэхүй'!AR35+'Нийгэмшил'!V35+'Нийгэмшил'!X35)=0,"",ROUND((N('Танин мэдэхүй'!D35)+N('Нийгэмшил'!H35)+N('Танин мэдэхүй'!P35)+N('Танин мэдэхүй'!R35)+N('Танин мэдэхүй'!T35)+N('Танин мэдэхүй'!V35)+N('Нийгэмшил'!L35))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L32" s="12">
+        <f>IF(('Бие бялдар'!V35+'Бие бялдар'!X35+'Танин мэдэхүй'!AP35+'Танин мэдэхүй'!AR35+'Нийгэмшил'!V35+'Нийгэмшил'!X35)=0,"",ROUND((N('Танин мэдэхүй'!F35)+N('Танин мэдэхүй'!H35)+N('Танин мэдэхүй'!J35)+N('Нийгэмшил'!D35)+N('Танин мэдэхүй'!L35)+N('Танин мэдэхүй'!N35)+N('Нийгэмшил'!F35)+N('Танин мэдэхүй'!X35)+N('Танин мэдэхүй'!Z35)+N('Танин мэдэхүй'!AB35)+N('Нийгэмшил'!J35)+N('Танин мэдэхүй'!AL35)+N('Танин мэдэхүй'!AN35)+N('Нийгэмшил'!N35))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M32" s="14">
         <f>'Бие бялдар'!V35+'Танин мэдэхүй'!AP35+'Нийгэмшил'!V35</f>
         <v/>
       </c>
-      <c r="J32" s="12">
-        <f>IF(('Бие бялдар'!V35+'Бие бялдар'!X35+'Танин мэдэхүй'!AP35+'Танин мэдэхүй'!AR35+'Нийгэмшил'!V35+'Нийгэмшил'!X35)=0,"",ROUND(I32/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K32" s="15">
-        <f>IF(J32="","",IF(J32&gt;=80,"Хангалттай эзэмшиж байна",IF(J32&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N32" s="12">
+        <f>IF(('Бие бялдар'!V35+'Бие бялдар'!X35+'Танин мэдэхүй'!AP35+'Танин мэдэхүй'!AR35+'Нийгэмшил'!V35+'Нийгэмшил'!X35)=0,"",ROUND(M32/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O32" s="15">
+        <f>IF(N32="","",IF(N32&gt;=80,"Хангалттай эзэмшиж байна",IF(N32&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2281,16 +2773,32 @@
         <f>IF(('Бие бялдар'!V36+'Бие бялдар'!X36+'Танин мэдэхүй'!AP36+'Танин мэдэхүй'!AR36+'Нийгэмшил'!V36+'Нийгэмшил'!X36)=0,"",ROUND((N('Нийгэмшил'!N36)+N('Нийгэмшил'!P36)+N('Нийгэмшил'!R36)+N('Нийгэмшил'!T36))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="12">
+        <f>IF(('Бие бялдар'!V36+'Бие бялдар'!X36+'Танин мэдэхүй'!AP36+'Танин мэдэхүй'!AR36+'Нийгэмшил'!V36+'Нийгэмшил'!X36)=0,"",ROUND((N('Бие бялдар'!D36)+N('Бие бялдар'!F36)+N('Бие бялдар'!R36)+N('Бие бялдар'!T36)+N('Нийгэмшил'!P36)+N('Нийгэмшил'!R36)+N('Нийгэмшил'!T36))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J33" s="12">
+        <f>IF(('Бие бялдар'!V36+'Бие бялдар'!X36+'Танин мэдэхүй'!AP36+'Танин мэдэхүй'!AR36+'Нийгэмшил'!V36+'Нийгэмшил'!X36)=0,"",ROUND((N('Бие бялдар'!H36)+N('Бие бялдар'!J36)+N('Бие бялдар'!L36)+N('Бие бялдар'!N36)+N('Бие бялдар'!P36)+N('Танин мэдэхүй'!AD36)+N('Танин мэдэхүй'!AF36)+N('Танин мэдэхүй'!AH36)+N('Танин мэдэхүй'!AJ36))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K33" s="12">
+        <f>IF(('Бие бялдар'!V36+'Бие бялдар'!X36+'Танин мэдэхүй'!AP36+'Танин мэдэхүй'!AR36+'Нийгэмшил'!V36+'Нийгэмшил'!X36)=0,"",ROUND((N('Танин мэдэхүй'!D36)+N('Нийгэмшил'!H36)+N('Танин мэдэхүй'!P36)+N('Танин мэдэхүй'!R36)+N('Танин мэдэхүй'!T36)+N('Танин мэдэхүй'!V36)+N('Нийгэмшил'!L36))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L33" s="12">
+        <f>IF(('Бие бялдар'!V36+'Бие бялдар'!X36+'Танин мэдэхүй'!AP36+'Танин мэдэхүй'!AR36+'Нийгэмшил'!V36+'Нийгэмшил'!X36)=0,"",ROUND((N('Танин мэдэхүй'!F36)+N('Танин мэдэхүй'!H36)+N('Танин мэдэхүй'!J36)+N('Нийгэмшил'!D36)+N('Танин мэдэхүй'!L36)+N('Танин мэдэхүй'!N36)+N('Нийгэмшил'!F36)+N('Танин мэдэхүй'!X36)+N('Танин мэдэхүй'!Z36)+N('Танин мэдэхүй'!AB36)+N('Нийгэмшил'!J36)+N('Танин мэдэхүй'!AL36)+N('Танин мэдэхүй'!AN36)+N('Нийгэмшил'!N36))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M33" s="14">
         <f>'Бие бялдар'!V36+'Танин мэдэхүй'!AP36+'Нийгэмшил'!V36</f>
         <v/>
       </c>
-      <c r="J33" s="12">
-        <f>IF(('Бие бялдар'!V36+'Бие бялдар'!X36+'Танин мэдэхүй'!AP36+'Танин мэдэхүй'!AR36+'Нийгэмшил'!V36+'Нийгэмшил'!X36)=0,"",ROUND(I33/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K33" s="15">
-        <f>IF(J33="","",IF(J33&gt;=80,"Хангалттай эзэмшиж байна",IF(J33&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N33" s="12">
+        <f>IF(('Бие бялдар'!V36+'Бие бялдар'!X36+'Танин мэдэхүй'!AP36+'Танин мэдэхүй'!AR36+'Нийгэмшил'!V36+'Нийгэмшил'!X36)=0,"",ROUND(M33/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O33" s="15">
+        <f>IF(N33="","",IF(N33&gt;=80,"Хангалттай эзэмшиж байна",IF(N33&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2323,16 +2831,32 @@
         <f>IF(('Бие бялдар'!V37+'Бие бялдар'!X37+'Танин мэдэхүй'!AP37+'Танин мэдэхүй'!AR37+'Нийгэмшил'!V37+'Нийгэмшил'!X37)=0,"",ROUND((N('Нийгэмшил'!N37)+N('Нийгэмшил'!P37)+N('Нийгэмшил'!R37)+N('Нийгэмшил'!T37))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="12">
+        <f>IF(('Бие бялдар'!V37+'Бие бялдар'!X37+'Танин мэдэхүй'!AP37+'Танин мэдэхүй'!AR37+'Нийгэмшил'!V37+'Нийгэмшил'!X37)=0,"",ROUND((N('Бие бялдар'!D37)+N('Бие бялдар'!F37)+N('Бие бялдар'!R37)+N('Бие бялдар'!T37)+N('Нийгэмшил'!P37)+N('Нийгэмшил'!R37)+N('Нийгэмшил'!T37))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J34" s="12">
+        <f>IF(('Бие бялдар'!V37+'Бие бялдар'!X37+'Танин мэдэхүй'!AP37+'Танин мэдэхүй'!AR37+'Нийгэмшил'!V37+'Нийгэмшил'!X37)=0,"",ROUND((N('Бие бялдар'!H37)+N('Бие бялдар'!J37)+N('Бие бялдар'!L37)+N('Бие бялдар'!N37)+N('Бие бялдар'!P37)+N('Танин мэдэхүй'!AD37)+N('Танин мэдэхүй'!AF37)+N('Танин мэдэхүй'!AH37)+N('Танин мэдэхүй'!AJ37))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K34" s="12">
+        <f>IF(('Бие бялдар'!V37+'Бие бялдар'!X37+'Танин мэдэхүй'!AP37+'Танин мэдэхүй'!AR37+'Нийгэмшил'!V37+'Нийгэмшил'!X37)=0,"",ROUND((N('Танин мэдэхүй'!D37)+N('Нийгэмшил'!H37)+N('Танин мэдэхүй'!P37)+N('Танин мэдэхүй'!R37)+N('Танин мэдэхүй'!T37)+N('Танин мэдэхүй'!V37)+N('Нийгэмшил'!L37))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L34" s="12">
+        <f>IF(('Бие бялдар'!V37+'Бие бялдар'!X37+'Танин мэдэхүй'!AP37+'Танин мэдэхүй'!AR37+'Нийгэмшил'!V37+'Нийгэмшил'!X37)=0,"",ROUND((N('Танин мэдэхүй'!F37)+N('Танин мэдэхүй'!H37)+N('Танин мэдэхүй'!J37)+N('Нийгэмшил'!D37)+N('Танин мэдэхүй'!L37)+N('Танин мэдэхүй'!N37)+N('Нийгэмшил'!F37)+N('Танин мэдэхүй'!X37)+N('Танин мэдэхүй'!Z37)+N('Танин мэдэхүй'!AB37)+N('Нийгэмшил'!J37)+N('Танин мэдэхүй'!AL37)+N('Танин мэдэхүй'!AN37)+N('Нийгэмшил'!N37))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M34" s="14">
         <f>'Бие бялдар'!V37+'Танин мэдэхүй'!AP37+'Нийгэмшил'!V37</f>
         <v/>
       </c>
-      <c r="J34" s="12">
-        <f>IF(('Бие бялдар'!V37+'Бие бялдар'!X37+'Танин мэдэхүй'!AP37+'Танин мэдэхүй'!AR37+'Нийгэмшил'!V37+'Нийгэмшил'!X37)=0,"",ROUND(I34/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K34" s="15">
-        <f>IF(J34="","",IF(J34&gt;=80,"Хангалттай эзэмшиж байна",IF(J34&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N34" s="12">
+        <f>IF(('Бие бялдар'!V37+'Бие бялдар'!X37+'Танин мэдэхүй'!AP37+'Танин мэдэхүй'!AR37+'Нийгэмшил'!V37+'Нийгэмшил'!X37)=0,"",ROUND(M34/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O34" s="15">
+        <f>IF(N34="","",IF(N34&gt;=80,"Хангалттай эзэмшиж байна",IF(N34&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2365,16 +2889,32 @@
         <f>IF(('Бие бялдар'!V38+'Бие бялдар'!X38+'Танин мэдэхүй'!AP38+'Танин мэдэхүй'!AR38+'Нийгэмшил'!V38+'Нийгэмшил'!X38)=0,"",ROUND((N('Нийгэмшил'!N38)+N('Нийгэмшил'!P38)+N('Нийгэмшил'!R38)+N('Нийгэмшил'!T38))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="12">
+        <f>IF(('Бие бялдар'!V38+'Бие бялдар'!X38+'Танин мэдэхүй'!AP38+'Танин мэдэхүй'!AR38+'Нийгэмшил'!V38+'Нийгэмшил'!X38)=0,"",ROUND((N('Бие бялдар'!D38)+N('Бие бялдар'!F38)+N('Бие бялдар'!R38)+N('Бие бялдар'!T38)+N('Нийгэмшил'!P38)+N('Нийгэмшил'!R38)+N('Нийгэмшил'!T38))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J35" s="12">
+        <f>IF(('Бие бялдар'!V38+'Бие бялдар'!X38+'Танин мэдэхүй'!AP38+'Танин мэдэхүй'!AR38+'Нийгэмшил'!V38+'Нийгэмшил'!X38)=0,"",ROUND((N('Бие бялдар'!H38)+N('Бие бялдар'!J38)+N('Бие бялдар'!L38)+N('Бие бялдар'!N38)+N('Бие бялдар'!P38)+N('Танин мэдэхүй'!AD38)+N('Танин мэдэхүй'!AF38)+N('Танин мэдэхүй'!AH38)+N('Танин мэдэхүй'!AJ38))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K35" s="12">
+        <f>IF(('Бие бялдар'!V38+'Бие бялдар'!X38+'Танин мэдэхүй'!AP38+'Танин мэдэхүй'!AR38+'Нийгэмшил'!V38+'Нийгэмшил'!X38)=0,"",ROUND((N('Танин мэдэхүй'!D38)+N('Нийгэмшил'!H38)+N('Танин мэдэхүй'!P38)+N('Танин мэдэхүй'!R38)+N('Танин мэдэхүй'!T38)+N('Танин мэдэхүй'!V38)+N('Нийгэмшил'!L38))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L35" s="12">
+        <f>IF(('Бие бялдар'!V38+'Бие бялдар'!X38+'Танин мэдэхүй'!AP38+'Танин мэдэхүй'!AR38+'Нийгэмшил'!V38+'Нийгэмшил'!X38)=0,"",ROUND((N('Танин мэдэхүй'!F38)+N('Танин мэдэхүй'!H38)+N('Танин мэдэхүй'!J38)+N('Нийгэмшил'!D38)+N('Танин мэдэхүй'!L38)+N('Танин мэдэхүй'!N38)+N('Нийгэмшил'!F38)+N('Танин мэдэхүй'!X38)+N('Танин мэдэхүй'!Z38)+N('Танин мэдэхүй'!AB38)+N('Нийгэмшил'!J38)+N('Танин мэдэхүй'!AL38)+N('Танин мэдэхүй'!AN38)+N('Нийгэмшил'!N38))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M35" s="14">
         <f>'Бие бялдар'!V38+'Танин мэдэхүй'!AP38+'Нийгэмшил'!V38</f>
         <v/>
       </c>
-      <c r="J35" s="12">
-        <f>IF(('Бие бялдар'!V38+'Бие бялдар'!X38+'Танин мэдэхүй'!AP38+'Танин мэдэхүй'!AR38+'Нийгэмшил'!V38+'Нийгэмшил'!X38)=0,"",ROUND(I35/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K35" s="15">
-        <f>IF(J35="","",IF(J35&gt;=80,"Хангалттай эзэмшиж байна",IF(J35&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N35" s="12">
+        <f>IF(('Бие бялдар'!V38+'Бие бялдар'!X38+'Танин мэдэхүй'!AP38+'Танин мэдэхүй'!AR38+'Нийгэмшил'!V38+'Нийгэмшил'!X38)=0,"",ROUND(M35/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O35" s="15">
+        <f>IF(N35="","",IF(N35&gt;=80,"Хангалттай эзэмшиж байна",IF(N35&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2407,16 +2947,32 @@
         <f>IF(('Бие бялдар'!V39+'Бие бялдар'!X39+'Танин мэдэхүй'!AP39+'Танин мэдэхүй'!AR39+'Нийгэмшил'!V39+'Нийгэмшил'!X39)=0,"",ROUND((N('Нийгэмшил'!N39)+N('Нийгэмшил'!P39)+N('Нийгэмшил'!R39)+N('Нийгэмшил'!T39))/4*100,1))</f>
         <v/>
       </c>
-      <c r="I36" s="14">
+      <c r="I36" s="12">
+        <f>IF(('Бие бялдар'!V39+'Бие бялдар'!X39+'Танин мэдэхүй'!AP39+'Танин мэдэхүй'!AR39+'Нийгэмшил'!V39+'Нийгэмшил'!X39)=0,"",ROUND((N('Бие бялдар'!D39)+N('Бие бялдар'!F39)+N('Бие бялдар'!R39)+N('Бие бялдар'!T39)+N('Нийгэмшил'!P39)+N('Нийгэмшил'!R39)+N('Нийгэмшил'!T39))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="J36" s="12">
+        <f>IF(('Бие бялдар'!V39+'Бие бялдар'!X39+'Танин мэдэхүй'!AP39+'Танин мэдэхүй'!AR39+'Нийгэмшил'!V39+'Нийгэмшил'!X39)=0,"",ROUND((N('Бие бялдар'!H39)+N('Бие бялдар'!J39)+N('Бие бялдар'!L39)+N('Бие бялдар'!N39)+N('Бие бялдар'!P39)+N('Танин мэдэхүй'!AD39)+N('Танин мэдэхүй'!AF39)+N('Танин мэдэхүй'!AH39)+N('Танин мэдэхүй'!AJ39))/9*100,1))</f>
+        <v/>
+      </c>
+      <c r="K36" s="12">
+        <f>IF(('Бие бялдар'!V39+'Бие бялдар'!X39+'Танин мэдэхүй'!AP39+'Танин мэдэхүй'!AR39+'Нийгэмшил'!V39+'Нийгэмшил'!X39)=0,"",ROUND((N('Танин мэдэхүй'!D39)+N('Нийгэмшил'!H39)+N('Танин мэдэхүй'!P39)+N('Танин мэдэхүй'!R39)+N('Танин мэдэхүй'!T39)+N('Танин мэдэхүй'!V39)+N('Нийгэмшил'!L39))/7*100,1))</f>
+        <v/>
+      </c>
+      <c r="L36" s="12">
+        <f>IF(('Бие бялдар'!V39+'Бие бялдар'!X39+'Танин мэдэхүй'!AP39+'Танин мэдэхүй'!AR39+'Нийгэмшил'!V39+'Нийгэмшил'!X39)=0,"",ROUND((N('Танин мэдэхүй'!F39)+N('Танин мэдэхүй'!H39)+N('Танин мэдэхүй'!J39)+N('Нийгэмшил'!D39)+N('Танин мэдэхүй'!L39)+N('Танин мэдэхүй'!N39)+N('Нийгэмшил'!F39)+N('Танин мэдэхүй'!X39)+N('Танин мэдэхүй'!Z39)+N('Танин мэдэхүй'!AB39)+N('Нийгэмшил'!J39)+N('Танин мэдэхүй'!AL39)+N('Танин мэдэхүй'!AN39)+N('Нийгэмшил'!N39))/14*100,1))</f>
+        <v/>
+      </c>
+      <c r="M36" s="14">
         <f>'Бие бялдар'!V39+'Танин мэдэхүй'!AP39+'Нийгэмшил'!V39</f>
         <v/>
       </c>
-      <c r="J36" s="12">
-        <f>IF(('Бие бялдар'!V39+'Бие бялдар'!X39+'Танин мэдэхүй'!AP39+'Танин мэдэхүй'!AR39+'Нийгэмшил'!V39+'Нийгэмшил'!X39)=0,"",ROUND(I36/37*100,1))</f>
-        <v/>
-      </c>
-      <c r="K36" s="15">
-        <f>IF(J36="","",IF(J36&gt;=80,"Хангалттай эзэмшиж байна",IF(J36&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
+      <c r="N36" s="12">
+        <f>IF(('Бие бялдар'!V39+'Бие бялдар'!X39+'Танин мэдэхүй'!AP39+'Танин мэдэхүй'!AR39+'Нийгэмшил'!V39+'Нийгэмшил'!X39)=0,"",ROUND(M36/37*100,1))</f>
+        <v/>
+      </c>
+      <c r="O36" s="15">
+        <f>IF(N36="","",IF(N36&gt;=80,"Хангалттай эзэмшиж байна",IF(N36&gt;=50,"Ахиж байна","Хөгжиж байна")))</f>
         <v/>
       </c>
     </row>
@@ -2451,12 +3007,28 @@
         <f>IFERROR(ROUND(AVERAGE(H7:H36),1),"")</f>
         <v/>
       </c>
-      <c r="I37" s="17" t="inlineStr"/>
+      <c r="I37" s="9">
+        <f>IFERROR(ROUND(AVERAGE(I7:I36),1),"")</f>
+        <v/>
+      </c>
       <c r="J37" s="9">
         <f>IFERROR(ROUND(AVERAGE(J7:J36),1),"")</f>
         <v/>
       </c>
-      <c r="K37" s="17" t="inlineStr"/>
+      <c r="K37" s="9">
+        <f>IFERROR(ROUND(AVERAGE(K7:K36),1),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="9">
+        <f>IFERROR(ROUND(AVERAGE(L7:L36),1),"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="17" t="inlineStr"/>
+      <c r="N37" s="9">
+        <f>IFERROR(ROUND(AVERAGE(N7:N36),1),"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="17" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
@@ -2489,13 +3061,29 @@
         <f>COUNTIFS(H7:H36,"&gt;=80",H7:H36,"&lt;=1000")</f>
         <v/>
       </c>
-      <c r="I38" s="17" t="inlineStr"/>
+      <c r="I38" s="9">
+        <f>COUNTIFS(I7:I36,"&gt;=80",I7:I36,"&lt;=1000")</f>
+        <v/>
+      </c>
       <c r="J38" s="9">
         <f>COUNTIFS(J7:J36,"&gt;=80",J7:J36,"&lt;=1000")</f>
         <v/>
       </c>
       <c r="K38" s="9">
-        <f>COUNTIF(K7:K36,"Хангалттай эзэмшиж байна")</f>
+        <f>COUNTIFS(K7:K36,"&gt;=80",K7:K36,"&lt;=1000")</f>
+        <v/>
+      </c>
+      <c r="L38" s="9">
+        <f>COUNTIFS(L7:L36,"&gt;=80",L7:L36,"&lt;=1000")</f>
+        <v/>
+      </c>
+      <c r="M38" s="17" t="inlineStr"/>
+      <c r="N38" s="9">
+        <f>COUNTIFS(N7:N36,"&gt;=80",N7:N36,"&lt;=1000")</f>
+        <v/>
+      </c>
+      <c r="O38" s="9">
+        <f>COUNTIF(O7:O36,"Хангалттай эзэмшиж байна")</f>
         <v/>
       </c>
     </row>
@@ -2530,13 +3118,29 @@
         <f>COUNTIFS(H7:H36,"&gt;=50",H7:H36,"&lt;=79.99")</f>
         <v/>
       </c>
-      <c r="I39" s="17" t="inlineStr"/>
+      <c r="I39" s="9">
+        <f>COUNTIFS(I7:I36,"&gt;=50",I7:I36,"&lt;=79.99")</f>
+        <v/>
+      </c>
       <c r="J39" s="9">
         <f>COUNTIFS(J7:J36,"&gt;=50",J7:J36,"&lt;=79.99")</f>
         <v/>
       </c>
       <c r="K39" s="9">
-        <f>COUNTIF(K7:K36,"Ахиж байна")</f>
+        <f>COUNTIFS(K7:K36,"&gt;=50",K7:K36,"&lt;=79.99")</f>
+        <v/>
+      </c>
+      <c r="L39" s="9">
+        <f>COUNTIFS(L7:L36,"&gt;=50",L7:L36,"&lt;=79.99")</f>
+        <v/>
+      </c>
+      <c r="M39" s="17" t="inlineStr"/>
+      <c r="N39" s="9">
+        <f>COUNTIFS(N7:N36,"&gt;=50",N7:N36,"&lt;=79.99")</f>
+        <v/>
+      </c>
+      <c r="O39" s="9">
+        <f>COUNTIF(O7:O36,"Ахиж байна")</f>
         <v/>
       </c>
     </row>
@@ -2571,32 +3175,49 @@
         <f>COUNTIFS(H7:H36,"&gt;=0",H7:H36,"&lt;=49.99")</f>
         <v/>
       </c>
-      <c r="I40" s="17" t="inlineStr"/>
+      <c r="I40" s="9">
+        <f>COUNTIFS(I7:I36,"&gt;=0",I7:I36,"&lt;=49.99")</f>
+        <v/>
+      </c>
       <c r="J40" s="9">
         <f>COUNTIFS(J7:J36,"&gt;=0",J7:J36,"&lt;=49.99")</f>
         <v/>
       </c>
       <c r="K40" s="9">
-        <f>COUNTIF(K7:K36,"Хөгжиж байна")</f>
+        <f>COUNTIFS(K7:K36,"&gt;=0",K7:K36,"&lt;=49.99")</f>
+        <v/>
+      </c>
+      <c r="L40" s="9">
+        <f>COUNTIFS(L7:L36,"&gt;=0",L7:L36,"&lt;=49.99")</f>
+        <v/>
+      </c>
+      <c r="M40" s="17" t="inlineStr"/>
+      <c r="N40" s="9">
+        <f>COUNTIFS(N7:N36,"&gt;=0",N7:N36,"&lt;=49.99")</f>
+        <v/>
+      </c>
+      <c r="O40" s="9">
+        <f>COUNTIF(O7:O36,"Хөгжиж байна")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="K3:K6"/>
-    <mergeCell ref="I3:I6"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="O3:O6"/>
+    <mergeCell ref="M3:M6"/>
+    <mergeCell ref="C3:L3"/>
+    <mergeCell ref="N3:N6"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B3:B6"/>
     <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5905511811023622" right="0.1968503937007874" top="0.5905511811023622" bottom="0.5905511811023622" header="0.3149606299212598" footer="0.3149606299212598"/>
@@ -2715,61 +3336,61 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="104" customHeight="1">
+    <row r="4" ht="116" customHeight="1">
       <c r="A4" s="8" t="n"/>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 1. Чанаж болгоогүй хүнсийг идэж болохгүйг мэддэг.</t>
+          <t>[Мэдлэг · 10.5: Эрүүл мэнд] 1. Чанаж болгоогүй хүнсийг идэж болохгүйг мэддэг.</t>
         </is>
       </c>
       <c r="E4" s="19" t="n"/>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 2. Хүрээлэн байгаа орчноос болгоомжлох зүйлсийг таньдаг.</t>
+          <t>[Мэдлэг · 10.5: Эрүүл мэнд] 2. Хүрээлэн байгаа орчноос болгоомжлох зүйлсийг таньдаг.</t>
         </is>
       </c>
       <c r="G4" s="19" t="n"/>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 12. 1-2 саадыг сүлжиж алхдаг (10 метр зайд).</t>
+          <t>[Чадвар · 10.5: Өсөлт] 12. 1-2 саадыг сүлжиж алхдаг (10 метр зайд).</t>
         </is>
       </c>
       <c r="I4" s="19" t="n"/>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 13. Хоорондоо 20 см зайтай байрлуулсан зураасны дундуур шулуун чиглэлээр гүйдэг.</t>
+          <t>[Чадвар · 10.5: Өсөлт] 13. Хоорондоо 20 см зайтай байрлуулсан зураасны дундуур шулуун чиглэлээр гүйдэг.</t>
         </is>
       </c>
       <c r="K4" s="19" t="n"/>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 14. 20 см зайтай зураасны хооронд дөрвөн хөллөж мөлхдөг.</t>
+          <t>[Чадвар · 10.5: Өсөлт] 14. 20 см зайтай зураасны хооронд дөрвөн хөллөж мөлхдөг.</t>
         </is>
       </c>
       <c r="M4" s="19" t="n"/>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 15. Хоёр хөл дээрээ үсэрч буудаг.</t>
+          <t>[Чадвар · 10.5: Өсөлт] 15. Хоёр хөл дээрээ үсэрч буудаг.</t>
         </is>
       </c>
       <c r="O4" s="19" t="n"/>
       <c r="P4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 16. Тоглоом, юмс (бөмбөг, базсан цаас гэх мэт)-ыг тодорхой чиглэлд (урагш, дээш гэх мэт) шидэж дамжуулдаг.</t>
+          <t>[Чадвар · 10.5: Өсөлт] 16. Тоглоом, юмс (бөмбөг, базсан цаас гэх мэт)-ыг тодорхой чиглэлд (урагш, дээш гэх мэт) шидэж дамжуулдаг.</t>
         </is>
       </c>
       <c r="Q4" s="19" t="n"/>
       <c r="R4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 17. Гар, нүүр, шүдээ угаах, хоолой амаа зайлах үйлийг бусдын дэмжлэгтэйгээр хийж чаддаг.</t>
+          <t>[Чадвар · 10.5: Эрүүл мэнд] 17. Гар, нүүр, шүдээ угаах, хоолой амаа зайлах үйлийг бусдын дэмжлэгтэйгээр хийж чаддаг.</t>
         </is>
       </c>
       <c r="S4" s="19" t="n"/>
       <c r="T4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 18. Хоолны хэрэгслийг зориулалтын дагуу хэрэглэдэг.</t>
+          <t>[Чадвар · 10.5: Эрүүл мэнд] 18. Хоолны хэрэгслийг зориулалтын дагуу хэрэглэдэг.</t>
         </is>
       </c>
       <c r="U4" s="19" t="n"/>
@@ -5125,121 +5746,121 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="92" customHeight="1">
+    <row r="4" ht="104" customHeight="1">
       <c r="A4" s="8" t="n"/>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 3. Зурагт номоос танил эд юмсыг нэрлэдэг.</t>
+          <t>[Мэдлэг · 10.5: Хэл яриа] 3. Зурагт номоос танил эд юмсыг нэрлэдэг.</t>
         </is>
       </c>
       <c r="E4" s="19" t="n"/>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 4. Орчныхоо ургамал, амьтнаас заримыг нь нэрлэдэг.</t>
+          <t>[Мэдлэг · 10.5: Танин мэдэхүй] 4. Орчныхоо ургамал, амьтнаас заримыг нь нэрлэдэг.</t>
         </is>
       </c>
       <c r="G4" s="19" t="n"/>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 5. Цаг агаарын үзэгдлийг таньж нэрлэдэг.</t>
+          <t>[Мэдлэг · 10.5: Танин мэдэхүй] 5. Цаг агаарын үзэгдлийг таньж нэрлэдэг.</t>
         </is>
       </c>
       <c r="I4" s="19" t="n"/>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 6. Өөрийн нэр, нас, биеийн эрхтнээ нэрлэдэг.</t>
+          <t>[Мэдлэг · 10.5: Танин мэдэхүй] 6. Өөрийн нэр, нас, биеийн эрхтнээ нэрлэдэг.</t>
         </is>
       </c>
       <c r="K4" s="19" t="n"/>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 8. Үндсэн гурван өнгийг нэрлэдэг.</t>
+          <t>[Мэдлэг · 10.5: Танин мэдэхүй] 8. Үндсэн гурван өнгийг нэрлэдэг.</t>
         </is>
       </c>
       <c r="M4" s="19" t="n"/>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 9. Тоглоом, юмсын заасан байршил (дээр, доор)-ыг нэрлэдэг.</t>
+          <t>[Мэдлэг · 10.5: Танин мэдэхүй] 9. Тоглоом, юмсын заасан байршил (дээр, доор)-ыг нэрлэдэг.</t>
         </is>
       </c>
       <c r="O4" s="19" t="n"/>
       <c r="P4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 19. Бусдын яриаг сонсож ойлгоод, үг, үйлдэл, дохио зангаагаар харилцдаг.</t>
+          <t>[Чадвар · 10.5: Хэл яриа] 19. Бусдын яриаг сонсож ойлгоод, үг, үйлдэл, дохио зангаагаар харилцдаг.</t>
         </is>
       </c>
       <c r="Q4" s="19" t="n"/>
       <c r="R4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 20. Энгийн өгүүлбэрийг дуурайн хэлдэг.</t>
+          <t>[Чадвар · 10.5: Хэл яриа] 20. Энгийн өгүүлбэрийг дуурайн хэлдэг.</t>
         </is>
       </c>
       <c r="S4" s="19" t="n"/>
       <c r="T4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 21. Авиа, үгийг сонсоод давтан хэлдэг.</t>
+          <t>[Чадвар · 10.5: Хэл яриа] 21. Авиа, үгийг сонсоод давтан хэлдэг.</t>
         </is>
       </c>
       <c r="U4" s="19" t="n"/>
       <c r="V4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 22. Ярилцах болон тоглох явцад асуулт асуухыг оролддог.</t>
+          <t>[Чадвар · 10.5: Хэл яриа] 22. Ярилцах болон тоглох явцад асуулт асуухыг оролддог.</t>
         </is>
       </c>
       <c r="W4" s="19" t="n"/>
       <c r="X4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 23. 3 хүртэлх тоглоом, юмсыг тоолдог.</t>
+          <t>[Чадвар · 10.5: Танин мэдэхүй] 23. 3 хүртэлх тоглоом, юмсыг тоолдог.</t>
         </is>
       </c>
       <c r="Y4" s="19" t="n"/>
       <c r="Z4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 24. Том, жижгийг ялгадаг.</t>
+          <t>[Чадвар · 10.5: Танин мэдэхүй] 24. Том, жижгийг ялгадаг.</t>
         </is>
       </c>
       <c r="AA4" s="19" t="n"/>
       <c r="AB4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 25. Юмсыг нэг ижил шинжээр нь ангилдаг.</t>
+          <t>[Чадвар · 10.5: Танин мэдэхүй] 25. Юмсыг нэг ижил шинжээр нь ангилдаг.</t>
         </is>
       </c>
       <c r="AC4" s="19" t="n"/>
       <c r="AD4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 26. Харандаагаар мөр, зураас гаргадаг.</t>
+          <t>[Чадвар · 10.5: Өсөлт] 26. Харандаагаар мөр, зураас гаргадаг.</t>
         </is>
       </c>
       <c r="AE4" s="19" t="n"/>
       <c r="AF4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 28. Бэлдэц дүрс ашиглан бусдын дэмжлэгтэй наамал хийдэг.</t>
+          <t>[Чадвар · 10.5: Өсөлт] 28. Бэлдэц дүрс ашиглан бусдын дэмжлэгтэй наамал хийдэг.</t>
         </is>
       </c>
       <c r="AG4" s="19" t="n"/>
       <c r="AH4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 29. Хэв ашиглан хэлбэр гаргадаг.</t>
+          <t>[Чадвар · 10.5: Өсөлт] 29. Хэв ашиглан хэлбэр гаргадаг.</t>
         </is>
       </c>
       <c r="AI4" s="19" t="n"/>
       <c r="AJ4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 30. Тоглоом, эд юмсыг бусдын дэмжлэгтэй өрдөг.</t>
+          <t>[Чадвар · 10.5: Өсөлт] 30. Тоглоом, эд юмсыг бусдын дэмжлэгтэй өрдөг.</t>
         </is>
       </c>
       <c r="AK4" s="19" t="n"/>
       <c r="AL4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 32. Хүн, амьтны дуу авиаг сонсоод ялгадаг.</t>
+          <t>[Чадвар · 10.5: Танин мэдэхүй] 32. Хүн, амьтны дуу авиаг сонсоод ялгадаг.</t>
         </is>
       </c>
       <c r="AM4" s="19" t="n"/>
       <c r="AN4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 33. Дуу, хөгжмийн хэмнэлийг хөдөлгөөн (алга таших, өвдөг цохих гэх мэт)-өөр илэрхийлдэг.</t>
+          <t>[Чадвар · 10.5: Танин мэдэхүй] 33. Дуу, хөгжмийн хэмнэлийг хөдөлгөөн (алга таших, өвдөг цохих гэх мэт)-өөр илэрхийлдэг.</t>
         </is>
       </c>
       <c r="AO4" s="19" t="n"/>
@@ -8793,55 +9414,55 @@
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 7. Үндэсний хувцас (дээл, гутал, малгай)-ыг нэрлэдэг.</t>
+          <t>[Мэдлэг · 10.5: Танин мэдэхүй] 7. Үндэсний хувцас (дээл, гутал, малгай)-ыг нэрлэдэг.</t>
         </is>
       </c>
       <c r="E4" s="19" t="n"/>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 10. Болно, болохгүйг ойлгодог.</t>
+          <t>[Мэдлэг · 10.5: Танин мэдэхүй] 10. Болно, болохгүйг ойлгодог.</t>
         </is>
       </c>
       <c r="G4" s="19" t="n"/>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>[Мэдлэг] 11. Бусдын нүүрний хувирал, гарын дохио, дуу авиа, үгээр илэрхийлсэн харилцааг ойлгодог.</t>
+          <t>[Мэдлэг · 10.5: Хэл яриа] 11. Бусдын нүүрний хувирал, гарын дохио, дуу авиа, үгээр илэрхийлсэн харилцааг ойлгодог.</t>
         </is>
       </c>
       <c r="I4" s="19" t="n"/>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 27. Бусдын үйлийг ажиглаж дуурайдаг.</t>
+          <t>[Чадвар · 10.5: Танин мэдэхүй] 27. Бусдын үйлийг ажиглаж дуурайдаг.</t>
         </is>
       </c>
       <c r="K4" s="19" t="n"/>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>[Чадвар] 31. Өөрийн хэрэгцээ, биеийн зарим мэдрэмжээ нүүрний хувирал, биеийн хөдөлгөөн, үгээр илэрхийлдэг.</t>
+          <t>[Чадвар · 10.5: Хэл яриа] 31. Өөрийн хэрэгцээ, биеийн зарим мэдрэмжээ нүүрний хувирал, биеийн хөдөлгөөн, үгээр илэрхийлдэг.</t>
         </is>
       </c>
       <c r="M4" s="19" t="n"/>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>[Төлөвшил] 34. Бусдын бүтээлийг ажиглаж сонирхдог.</t>
+          <t>[Төлөвшил · 10.5: Танин мэдэхүй] 34. Бусдын бүтээлийг ажиглаж сонирхдог.</t>
         </is>
       </c>
       <c r="O4" s="19" t="n"/>
       <c r="P4" s="10" t="inlineStr">
         <is>
-          <t>[Төлөвшил] 35. Хогийг хогийн саванд хийдэг.</t>
+          <t>[Төлөвшил · 10.5: Эрүүл мэнд] 35. Хогийг хогийн саванд хийдэг.</t>
         </is>
       </c>
       <c r="Q4" s="19" t="n"/>
       <c r="R4" s="10" t="inlineStr">
         <is>
-          <t>[Төлөвшил] 36. Өөр хэн нэгэн аргадах (уурлаж тавгүйтсэн, уйлсан үед)-д тайвширдаг.</t>
+          <t>[Төлөвшил · 10.5: Эрүүл мэнд] 36. Өөр хэн нэгэн аргадах (уурлаж тавгүйтсэн, уйлсан үед)-д тайвширдаг.</t>
         </is>
       </c>
       <c r="S4" s="19" t="n"/>
       <c r="T4" s="10" t="inlineStr">
         <is>
-          <t>[Төлөвшил] 37. Хэрэглэсэн эд зүйл, тоглоомоо хураадаг.</t>
+          <t>[Төлөвшил · 10.5: Эрүүл мэнд] 37. Хэрэглэсэн эд зүйл, тоглоомоо хураадаг.</t>
         </is>
       </c>
       <c r="U4" s="19" t="n"/>

--- a/Гарааны_үнэлгээ/2_нас_гарааны_үнэлгээ_А79.xlsx
+++ b/Гарааны_үнэлгээ/2_нас_гарааны_үнэлгээ_А79.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Хуулийн тайлбараар гурав хүртэлх насны хүүхдийн цогц хөгжлийг дэмжих хөтөлбөр нь эрүүл мэнд, өсөлт, хэл яриа, танин мэдэхүйн хөгжлийг дэмжинэ. Хөтөлбөрийн бичвэр нийтэд олдоогүй тул А/79-ийн 37 шалгуурыг эдгээр 4 чиглэлд багш хуваарилсан (шалгуурын толгойд «10.5: ...» гэж заасан): Эрүүл мэнд — 1, 2, 17, 18, 35, 36, 37; Өсөлт (бие бялдар, их ба нарийн хөдөлгөөн) — 12–16, 26, 28–30; Хэл яриа — 3, 11, 19–22, 31; Танин мэдэхүй — үлдсэн 14 шалгуур. Нэгтгэл шийтэд 4 чиглэл тус бүрийн хувь бодогдоно. Хөтөлбөр батлагдаж нийтлэгдвэл хуваарилалтыг тулгаж засна.</t>
+          <t>Хуулийн тайлбараар гурав хүртэлх насны хүүхдийн цогц хөгжлийг дэмжих хөтөлбөр нь эрүүл мэнд, өсөлт, хэл яриа, танин мэдэхүйн хөгжлийг дэмжинэ. Хөтөлбөрийн бичвэр нийтэд олдоогүй тул А/79-ийн 37 шалгуурыг энэ файлд эдгээр 4 чиглэлд урьдчилан хуваарилсан, багш шалгаж засаж болно (шалгуурын толгойд «10.5: ...» гэж заасан): Эрүүл мэнд — 1, 2, 17, 18, 35, 36, 37; Өсөлт (бие бялдар, их ба нарийн хөдөлгөөн) — 12–16, 26, 28–30; Хэл яриа — 3, 11, 19–22, 31; Танин мэдэхүй — үлдсэн 14 шалгуур. Нэгтгэл шийтэд 4 чиглэл тус бүрийн хувь бодогдоно. Хөтөлбөр батлагдаж нийтлэгдвэл хуваарилалтыг тулгаж засна.</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">

--- a/Гарааны_үнэлгээ/2_нас_гарааны_үнэлгээ_А79.xlsx
+++ b/Гарааны_үнэлгээ/2_нас_гарааны_үнэлгээ_А79.xlsx
@@ -15,12 +15,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Нэгтгэл'!$3:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Нэгтгэл'!$A$1:$H$41</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Мэдлэг'!$3:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Мэдлэг'!$A$1:$S$42</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Чадвар'!$3:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Чадвар'!$A$1:$AD$42</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Төлөвшил'!$3:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Төлөвшил'!$A$1:$L$42</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Мэдлэг'!$3:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Мэдлэг'!$A$1:$S$41</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Чадвар'!$3:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Чадвар'!$A$1:$AD$41</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Төлөвшил'!$3:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Төлөвшил'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -765,23 +765,23 @@
         </is>
       </c>
       <c r="C7" s="12">
-        <f>IF(COUNT('Мэдлэг'!D8:N8)=0,"",ROUND(COUNTIF('Мэдлэг'!D8:N8,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D7:N7)=0,"",ROUND(COUNTIF('Мэдлэг'!D7:N7,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D7" s="12">
-        <f>IF(COUNT('Чадвар'!D8:Y8)=0,"",ROUND(COUNTIF('Чадвар'!D8:Y8,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D7:Y7)=0,"",ROUND(COUNTIF('Чадвар'!D7:Y7,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>IF(COUNT('Төлөвшил'!D8:G8)=0,"",ROUND(COUNTIF('Төлөвшил'!D8:G8,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D7:G7)=0,"",ROUND(COUNTIF('Төлөвшил'!D7:G7,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>COUNTIF('Мэдлэг'!D8:N8,1)+COUNTIF('Чадвар'!D8:Y8,1)+COUNTIF('Төлөвшил'!D8:G8,1)</f>
+        <f>COUNTIF('Мэдлэг'!D7:N7,1)+COUNTIF('Чадвар'!D7:Y7,1)+COUNTIF('Төлөвшил'!D7:G7,1)</f>
         <v/>
       </c>
       <c r="G7" s="12">
-        <f>IF((COUNT('Мэдлэг'!D8:N8)+COUNT('Чадвар'!D8:Y8)+COUNT('Төлөвшил'!D8:G8))=0,"",ROUND(F7/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D7:N7)+COUNT('Чадвар'!D7:Y7)+COUNT('Төлөвшил'!D7:G7))=0,"",ROUND(F7/37*100,1))</f>
         <v/>
       </c>
       <c r="H7" s="14">
@@ -799,23 +799,23 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>IF(COUNT('Мэдлэг'!D9:N9)=0,"",ROUND(COUNTIF('Мэдлэг'!D9:N9,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D8:N8)=0,"",ROUND(COUNTIF('Мэдлэг'!D8:N8,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>IF(COUNT('Чадвар'!D9:Y9)=0,"",ROUND(COUNTIF('Чадвар'!D9:Y9,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D8:Y8)=0,"",ROUND(COUNTIF('Чадвар'!D8:Y8,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>IF(COUNT('Төлөвшил'!D9:G9)=0,"",ROUND(COUNTIF('Төлөвшил'!D9:G9,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D8:G8)=0,"",ROUND(COUNTIF('Төлөвшил'!D8:G8,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>COUNTIF('Мэдлэг'!D9:N9,1)+COUNTIF('Чадвар'!D9:Y9,1)+COUNTIF('Төлөвшил'!D9:G9,1)</f>
+        <f>COUNTIF('Мэдлэг'!D8:N8,1)+COUNTIF('Чадвар'!D8:Y8,1)+COUNTIF('Төлөвшил'!D8:G8,1)</f>
         <v/>
       </c>
       <c r="G8" s="12">
-        <f>IF((COUNT('Мэдлэг'!D9:N9)+COUNT('Чадвар'!D9:Y9)+COUNT('Төлөвшил'!D9:G9))=0,"",ROUND(F8/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D8:N8)+COUNT('Чадвар'!D8:Y8)+COUNT('Төлөвшил'!D8:G8))=0,"",ROUND(F8/37*100,1))</f>
         <v/>
       </c>
       <c r="H8" s="14">
@@ -833,23 +833,23 @@
         </is>
       </c>
       <c r="C9" s="12">
-        <f>IF(COUNT('Мэдлэг'!D10:N10)=0,"",ROUND(COUNTIF('Мэдлэг'!D10:N10,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D9:N9)=0,"",ROUND(COUNTIF('Мэдлэг'!D9:N9,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>IF(COUNT('Чадвар'!D10:Y10)=0,"",ROUND(COUNTIF('Чадвар'!D10:Y10,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D9:Y9)=0,"",ROUND(COUNTIF('Чадвар'!D9:Y9,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>IF(COUNT('Төлөвшил'!D10:G10)=0,"",ROUND(COUNTIF('Төлөвшил'!D10:G10,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D9:G9)=0,"",ROUND(COUNTIF('Төлөвшил'!D9:G9,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>COUNTIF('Мэдлэг'!D10:N10,1)+COUNTIF('Чадвар'!D10:Y10,1)+COUNTIF('Төлөвшил'!D10:G10,1)</f>
+        <f>COUNTIF('Мэдлэг'!D9:N9,1)+COUNTIF('Чадвар'!D9:Y9,1)+COUNTIF('Төлөвшил'!D9:G9,1)</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>IF((COUNT('Мэдлэг'!D10:N10)+COUNT('Чадвар'!D10:Y10)+COUNT('Төлөвшил'!D10:G10))=0,"",ROUND(F9/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D9:N9)+COUNT('Чадвар'!D9:Y9)+COUNT('Төлөвшил'!D9:G9))=0,"",ROUND(F9/37*100,1))</f>
         <v/>
       </c>
       <c r="H9" s="14">
@@ -867,23 +867,23 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>IF(COUNT('Мэдлэг'!D11:N11)=0,"",ROUND(COUNTIF('Мэдлэг'!D11:N11,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D10:N10)=0,"",ROUND(COUNTIF('Мэдлэг'!D10:N10,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D10" s="12">
-        <f>IF(COUNT('Чадвар'!D11:Y11)=0,"",ROUND(COUNTIF('Чадвар'!D11:Y11,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D10:Y10)=0,"",ROUND(COUNTIF('Чадвар'!D10:Y10,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>IF(COUNT('Төлөвшил'!D11:G11)=0,"",ROUND(COUNTIF('Төлөвшил'!D11:G11,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D10:G10)=0,"",ROUND(COUNTIF('Төлөвшил'!D10:G10,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>COUNTIF('Мэдлэг'!D11:N11,1)+COUNTIF('Чадвар'!D11:Y11,1)+COUNTIF('Төлөвшил'!D11:G11,1)</f>
+        <f>COUNTIF('Мэдлэг'!D10:N10,1)+COUNTIF('Чадвар'!D10:Y10,1)+COUNTIF('Төлөвшил'!D10:G10,1)</f>
         <v/>
       </c>
       <c r="G10" s="12">
-        <f>IF((COUNT('Мэдлэг'!D11:N11)+COUNT('Чадвар'!D11:Y11)+COUNT('Төлөвшил'!D11:G11))=0,"",ROUND(F10/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D10:N10)+COUNT('Чадвар'!D10:Y10)+COUNT('Төлөвшил'!D10:G10))=0,"",ROUND(F10/37*100,1))</f>
         <v/>
       </c>
       <c r="H10" s="14">
@@ -901,23 +901,23 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>IF(COUNT('Мэдлэг'!D12:N12)=0,"",ROUND(COUNTIF('Мэдлэг'!D12:N12,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D11:N11)=0,"",ROUND(COUNTIF('Мэдлэг'!D11:N11,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>IF(COUNT('Чадвар'!D12:Y12)=0,"",ROUND(COUNTIF('Чадвар'!D12:Y12,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D11:Y11)=0,"",ROUND(COUNTIF('Чадвар'!D11:Y11,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>IF(COUNT('Төлөвшил'!D12:G12)=0,"",ROUND(COUNTIF('Төлөвшил'!D12:G12,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D11:G11)=0,"",ROUND(COUNTIF('Төлөвшил'!D11:G11,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>COUNTIF('Мэдлэг'!D12:N12,1)+COUNTIF('Чадвар'!D12:Y12,1)+COUNTIF('Төлөвшил'!D12:G12,1)</f>
+        <f>COUNTIF('Мэдлэг'!D11:N11,1)+COUNTIF('Чадвар'!D11:Y11,1)+COUNTIF('Төлөвшил'!D11:G11,1)</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>IF((COUNT('Мэдлэг'!D12:N12)+COUNT('Чадвар'!D12:Y12)+COUNT('Төлөвшил'!D12:G12))=0,"",ROUND(F11/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D11:N11)+COUNT('Чадвар'!D11:Y11)+COUNT('Төлөвшил'!D11:G11))=0,"",ROUND(F11/37*100,1))</f>
         <v/>
       </c>
       <c r="H11" s="14">
@@ -935,23 +935,23 @@
         </is>
       </c>
       <c r="C12" s="12">
-        <f>IF(COUNT('Мэдлэг'!D13:N13)=0,"",ROUND(COUNTIF('Мэдлэг'!D13:N13,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D12:N12)=0,"",ROUND(COUNTIF('Мэдлэг'!D12:N12,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D12" s="12">
-        <f>IF(COUNT('Чадвар'!D13:Y13)=0,"",ROUND(COUNTIF('Чадвар'!D13:Y13,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D12:Y12)=0,"",ROUND(COUNTIF('Чадвар'!D12:Y12,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>IF(COUNT('Төлөвшил'!D13:G13)=0,"",ROUND(COUNTIF('Төлөвшил'!D13:G13,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D12:G12)=0,"",ROUND(COUNTIF('Төлөвшил'!D12:G12,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F12" s="12">
-        <f>COUNTIF('Мэдлэг'!D13:N13,1)+COUNTIF('Чадвар'!D13:Y13,1)+COUNTIF('Төлөвшил'!D13:G13,1)</f>
+        <f>COUNTIF('Мэдлэг'!D12:N12,1)+COUNTIF('Чадвар'!D12:Y12,1)+COUNTIF('Төлөвшил'!D12:G12,1)</f>
         <v/>
       </c>
       <c r="G12" s="12">
-        <f>IF((COUNT('Мэдлэг'!D13:N13)+COUNT('Чадвар'!D13:Y13)+COUNT('Төлөвшил'!D13:G13))=0,"",ROUND(F12/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D12:N12)+COUNT('Чадвар'!D12:Y12)+COUNT('Төлөвшил'!D12:G12))=0,"",ROUND(F12/37*100,1))</f>
         <v/>
       </c>
       <c r="H12" s="14">
@@ -969,23 +969,23 @@
         </is>
       </c>
       <c r="C13" s="12">
-        <f>IF(COUNT('Мэдлэг'!D14:N14)=0,"",ROUND(COUNTIF('Мэдлэг'!D14:N14,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D13:N13)=0,"",ROUND(COUNTIF('Мэдлэг'!D13:N13,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D13" s="12">
-        <f>IF(COUNT('Чадвар'!D14:Y14)=0,"",ROUND(COUNTIF('Чадвар'!D14:Y14,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D13:Y13)=0,"",ROUND(COUNTIF('Чадвар'!D13:Y13,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>IF(COUNT('Төлөвшил'!D14:G14)=0,"",ROUND(COUNTIF('Төлөвшил'!D14:G14,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D13:G13)=0,"",ROUND(COUNTIF('Төлөвшил'!D13:G13,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F13" s="12">
-        <f>COUNTIF('Мэдлэг'!D14:N14,1)+COUNTIF('Чадвар'!D14:Y14,1)+COUNTIF('Төлөвшил'!D14:G14,1)</f>
+        <f>COUNTIF('Мэдлэг'!D13:N13,1)+COUNTIF('Чадвар'!D13:Y13,1)+COUNTIF('Төлөвшил'!D13:G13,1)</f>
         <v/>
       </c>
       <c r="G13" s="12">
-        <f>IF((COUNT('Мэдлэг'!D14:N14)+COUNT('Чадвар'!D14:Y14)+COUNT('Төлөвшил'!D14:G14))=0,"",ROUND(F13/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D13:N13)+COUNT('Чадвар'!D13:Y13)+COUNT('Төлөвшил'!D13:G13))=0,"",ROUND(F13/37*100,1))</f>
         <v/>
       </c>
       <c r="H13" s="14">
@@ -1003,23 +1003,23 @@
         </is>
       </c>
       <c r="C14" s="12">
-        <f>IF(COUNT('Мэдлэг'!D15:N15)=0,"",ROUND(COUNTIF('Мэдлэг'!D15:N15,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D14:N14)=0,"",ROUND(COUNTIF('Мэдлэг'!D14:N14,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D14" s="12">
-        <f>IF(COUNT('Чадвар'!D15:Y15)=0,"",ROUND(COUNTIF('Чадвар'!D15:Y15,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D14:Y14)=0,"",ROUND(COUNTIF('Чадвар'!D14:Y14,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E14" s="12">
-        <f>IF(COUNT('Төлөвшил'!D15:G15)=0,"",ROUND(COUNTIF('Төлөвшил'!D15:G15,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D14:G14)=0,"",ROUND(COUNTIF('Төлөвшил'!D14:G14,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F14" s="12">
-        <f>COUNTIF('Мэдлэг'!D15:N15,1)+COUNTIF('Чадвар'!D15:Y15,1)+COUNTIF('Төлөвшил'!D15:G15,1)</f>
+        <f>COUNTIF('Мэдлэг'!D14:N14,1)+COUNTIF('Чадвар'!D14:Y14,1)+COUNTIF('Төлөвшил'!D14:G14,1)</f>
         <v/>
       </c>
       <c r="G14" s="12">
-        <f>IF((COUNT('Мэдлэг'!D15:N15)+COUNT('Чадвар'!D15:Y15)+COUNT('Төлөвшил'!D15:G15))=0,"",ROUND(F14/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D14:N14)+COUNT('Чадвар'!D14:Y14)+COUNT('Төлөвшил'!D14:G14))=0,"",ROUND(F14/37*100,1))</f>
         <v/>
       </c>
       <c r="H14" s="14">
@@ -1037,23 +1037,23 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>IF(COUNT('Мэдлэг'!D16:N16)=0,"",ROUND(COUNTIF('Мэдлэг'!D16:N16,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D15:N15)=0,"",ROUND(COUNTIF('Мэдлэг'!D15:N15,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D15" s="12">
-        <f>IF(COUNT('Чадвар'!D16:Y16)=0,"",ROUND(COUNTIF('Чадвар'!D16:Y16,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D15:Y15)=0,"",ROUND(COUNTIF('Чадвар'!D15:Y15,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>IF(COUNT('Төлөвшил'!D16:G16)=0,"",ROUND(COUNTIF('Төлөвшил'!D16:G16,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D15:G15)=0,"",ROUND(COUNTIF('Төлөвшил'!D15:G15,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>COUNTIF('Мэдлэг'!D16:N16,1)+COUNTIF('Чадвар'!D16:Y16,1)+COUNTIF('Төлөвшил'!D16:G16,1)</f>
+        <f>COUNTIF('Мэдлэг'!D15:N15,1)+COUNTIF('Чадвар'!D15:Y15,1)+COUNTIF('Төлөвшил'!D15:G15,1)</f>
         <v/>
       </c>
       <c r="G15" s="12">
-        <f>IF((COUNT('Мэдлэг'!D16:N16)+COUNT('Чадвар'!D16:Y16)+COUNT('Төлөвшил'!D16:G16))=0,"",ROUND(F15/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D15:N15)+COUNT('Чадвар'!D15:Y15)+COUNT('Төлөвшил'!D15:G15))=0,"",ROUND(F15/37*100,1))</f>
         <v/>
       </c>
       <c r="H15" s="14">
@@ -1071,23 +1071,23 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>IF(COUNT('Мэдлэг'!D17:N17)=0,"",ROUND(COUNTIF('Мэдлэг'!D17:N17,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D16:N16)=0,"",ROUND(COUNTIF('Мэдлэг'!D16:N16,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>IF(COUNT('Чадвар'!D17:Y17)=0,"",ROUND(COUNTIF('Чадвар'!D17:Y17,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D16:Y16)=0,"",ROUND(COUNTIF('Чадвар'!D16:Y16,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>IF(COUNT('Төлөвшил'!D17:G17)=0,"",ROUND(COUNTIF('Төлөвшил'!D17:G17,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D16:G16)=0,"",ROUND(COUNTIF('Төлөвшил'!D16:G16,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>COUNTIF('Мэдлэг'!D17:N17,1)+COUNTIF('Чадвар'!D17:Y17,1)+COUNTIF('Төлөвшил'!D17:G17,1)</f>
+        <f>COUNTIF('Мэдлэг'!D16:N16,1)+COUNTIF('Чадвар'!D16:Y16,1)+COUNTIF('Төлөвшил'!D16:G16,1)</f>
         <v/>
       </c>
       <c r="G16" s="12">
-        <f>IF((COUNT('Мэдлэг'!D17:N17)+COUNT('Чадвар'!D17:Y17)+COUNT('Төлөвшил'!D17:G17))=0,"",ROUND(F16/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D16:N16)+COUNT('Чадвар'!D16:Y16)+COUNT('Төлөвшил'!D16:G16))=0,"",ROUND(F16/37*100,1))</f>
         <v/>
       </c>
       <c r="H16" s="14">
@@ -1105,23 +1105,23 @@
         </is>
       </c>
       <c r="C17" s="12">
-        <f>IF(COUNT('Мэдлэг'!D18:N18)=0,"",ROUND(COUNTIF('Мэдлэг'!D18:N18,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D17:N17)=0,"",ROUND(COUNTIF('Мэдлэг'!D17:N17,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>IF(COUNT('Чадвар'!D18:Y18)=0,"",ROUND(COUNTIF('Чадвар'!D18:Y18,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D17:Y17)=0,"",ROUND(COUNTIF('Чадвар'!D17:Y17,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>IF(COUNT('Төлөвшил'!D18:G18)=0,"",ROUND(COUNTIF('Төлөвшил'!D18:G18,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D17:G17)=0,"",ROUND(COUNTIF('Төлөвшил'!D17:G17,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>COUNTIF('Мэдлэг'!D18:N18,1)+COUNTIF('Чадвар'!D18:Y18,1)+COUNTIF('Төлөвшил'!D18:G18,1)</f>
+        <f>COUNTIF('Мэдлэг'!D17:N17,1)+COUNTIF('Чадвар'!D17:Y17,1)+COUNTIF('Төлөвшил'!D17:G17,1)</f>
         <v/>
       </c>
       <c r="G17" s="12">
-        <f>IF((COUNT('Мэдлэг'!D18:N18)+COUNT('Чадвар'!D18:Y18)+COUNT('Төлөвшил'!D18:G18))=0,"",ROUND(F17/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D17:N17)+COUNT('Чадвар'!D17:Y17)+COUNT('Төлөвшил'!D17:G17))=0,"",ROUND(F17/37*100,1))</f>
         <v/>
       </c>
       <c r="H17" s="14">
@@ -1139,23 +1139,23 @@
         </is>
       </c>
       <c r="C18" s="12">
-        <f>IF(COUNT('Мэдлэг'!D19:N19)=0,"",ROUND(COUNTIF('Мэдлэг'!D19:N19,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D18:N18)=0,"",ROUND(COUNTIF('Мэдлэг'!D18:N18,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>IF(COUNT('Чадвар'!D19:Y19)=0,"",ROUND(COUNTIF('Чадвар'!D19:Y19,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D18:Y18)=0,"",ROUND(COUNTIF('Чадвар'!D18:Y18,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>IF(COUNT('Төлөвшил'!D19:G19)=0,"",ROUND(COUNTIF('Төлөвшил'!D19:G19,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D18:G18)=0,"",ROUND(COUNTIF('Төлөвшил'!D18:G18,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>COUNTIF('Мэдлэг'!D19:N19,1)+COUNTIF('Чадвар'!D19:Y19,1)+COUNTIF('Төлөвшил'!D19:G19,1)</f>
+        <f>COUNTIF('Мэдлэг'!D18:N18,1)+COUNTIF('Чадвар'!D18:Y18,1)+COUNTIF('Төлөвшил'!D18:G18,1)</f>
         <v/>
       </c>
       <c r="G18" s="12">
-        <f>IF((COUNT('Мэдлэг'!D19:N19)+COUNT('Чадвар'!D19:Y19)+COUNT('Төлөвшил'!D19:G19))=0,"",ROUND(F18/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D18:N18)+COUNT('Чадвар'!D18:Y18)+COUNT('Төлөвшил'!D18:G18))=0,"",ROUND(F18/37*100,1))</f>
         <v/>
       </c>
       <c r="H18" s="14">
@@ -1173,23 +1173,23 @@
         </is>
       </c>
       <c r="C19" s="12">
-        <f>IF(COUNT('Мэдлэг'!D20:N20)=0,"",ROUND(COUNTIF('Мэдлэг'!D20:N20,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D19:N19)=0,"",ROUND(COUNTIF('Мэдлэг'!D19:N19,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D19" s="12">
-        <f>IF(COUNT('Чадвар'!D20:Y20)=0,"",ROUND(COUNTIF('Чадвар'!D20:Y20,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D19:Y19)=0,"",ROUND(COUNTIF('Чадвар'!D19:Y19,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>IF(COUNT('Төлөвшил'!D20:G20)=0,"",ROUND(COUNTIF('Төлөвшил'!D20:G20,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D19:G19)=0,"",ROUND(COUNTIF('Төлөвшил'!D19:G19,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F19" s="12">
-        <f>COUNTIF('Мэдлэг'!D20:N20,1)+COUNTIF('Чадвар'!D20:Y20,1)+COUNTIF('Төлөвшил'!D20:G20,1)</f>
+        <f>COUNTIF('Мэдлэг'!D19:N19,1)+COUNTIF('Чадвар'!D19:Y19,1)+COUNTIF('Төлөвшил'!D19:G19,1)</f>
         <v/>
       </c>
       <c r="G19" s="12">
-        <f>IF((COUNT('Мэдлэг'!D20:N20)+COUNT('Чадвар'!D20:Y20)+COUNT('Төлөвшил'!D20:G20))=0,"",ROUND(F19/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D19:N19)+COUNT('Чадвар'!D19:Y19)+COUNT('Төлөвшил'!D19:G19))=0,"",ROUND(F19/37*100,1))</f>
         <v/>
       </c>
       <c r="H19" s="14">
@@ -1207,23 +1207,23 @@
         </is>
       </c>
       <c r="C20" s="12">
-        <f>IF(COUNT('Мэдлэг'!D21:N21)=0,"",ROUND(COUNTIF('Мэдлэг'!D21:N21,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D20:N20)=0,"",ROUND(COUNTIF('Мэдлэг'!D20:N20,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D20" s="12">
-        <f>IF(COUNT('Чадвар'!D21:Y21)=0,"",ROUND(COUNTIF('Чадвар'!D21:Y21,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D20:Y20)=0,"",ROUND(COUNTIF('Чадвар'!D20:Y20,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>IF(COUNT('Төлөвшил'!D21:G21)=0,"",ROUND(COUNTIF('Төлөвшил'!D21:G21,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D20:G20)=0,"",ROUND(COUNTIF('Төлөвшил'!D20:G20,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F20" s="12">
-        <f>COUNTIF('Мэдлэг'!D21:N21,1)+COUNTIF('Чадвар'!D21:Y21,1)+COUNTIF('Төлөвшил'!D21:G21,1)</f>
+        <f>COUNTIF('Мэдлэг'!D20:N20,1)+COUNTIF('Чадвар'!D20:Y20,1)+COUNTIF('Төлөвшил'!D20:G20,1)</f>
         <v/>
       </c>
       <c r="G20" s="12">
-        <f>IF((COUNT('Мэдлэг'!D21:N21)+COUNT('Чадвар'!D21:Y21)+COUNT('Төлөвшил'!D21:G21))=0,"",ROUND(F20/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D20:N20)+COUNT('Чадвар'!D20:Y20)+COUNT('Төлөвшил'!D20:G20))=0,"",ROUND(F20/37*100,1))</f>
         <v/>
       </c>
       <c r="H20" s="14">
@@ -1241,23 +1241,23 @@
         </is>
       </c>
       <c r="C21" s="12">
-        <f>IF(COUNT('Мэдлэг'!D22:N22)=0,"",ROUND(COUNTIF('Мэдлэг'!D22:N22,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D21:N21)=0,"",ROUND(COUNTIF('Мэдлэг'!D21:N21,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D21" s="12">
-        <f>IF(COUNT('Чадвар'!D22:Y22)=0,"",ROUND(COUNTIF('Чадвар'!D22:Y22,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D21:Y21)=0,"",ROUND(COUNTIF('Чадвар'!D21:Y21,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>IF(COUNT('Төлөвшил'!D22:G22)=0,"",ROUND(COUNTIF('Төлөвшил'!D22:G22,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D21:G21)=0,"",ROUND(COUNTIF('Төлөвшил'!D21:G21,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F21" s="12">
-        <f>COUNTIF('Мэдлэг'!D22:N22,1)+COUNTIF('Чадвар'!D22:Y22,1)+COUNTIF('Төлөвшил'!D22:G22,1)</f>
+        <f>COUNTIF('Мэдлэг'!D21:N21,1)+COUNTIF('Чадвар'!D21:Y21,1)+COUNTIF('Төлөвшил'!D21:G21,1)</f>
         <v/>
       </c>
       <c r="G21" s="12">
-        <f>IF((COUNT('Мэдлэг'!D22:N22)+COUNT('Чадвар'!D22:Y22)+COUNT('Төлөвшил'!D22:G22))=0,"",ROUND(F21/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D21:N21)+COUNT('Чадвар'!D21:Y21)+COUNT('Төлөвшил'!D21:G21))=0,"",ROUND(F21/37*100,1))</f>
         <v/>
       </c>
       <c r="H21" s="14">
@@ -1275,23 +1275,23 @@
         </is>
       </c>
       <c r="C22" s="12">
-        <f>IF(COUNT('Мэдлэг'!D23:N23)=0,"",ROUND(COUNTIF('Мэдлэг'!D23:N23,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D22:N22)=0,"",ROUND(COUNTIF('Мэдлэг'!D22:N22,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D22" s="12">
-        <f>IF(COUNT('Чадвар'!D23:Y23)=0,"",ROUND(COUNTIF('Чадвар'!D23:Y23,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D22:Y22)=0,"",ROUND(COUNTIF('Чадвар'!D22:Y22,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>IF(COUNT('Төлөвшил'!D23:G23)=0,"",ROUND(COUNTIF('Төлөвшил'!D23:G23,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D22:G22)=0,"",ROUND(COUNTIF('Төлөвшил'!D22:G22,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F22" s="12">
-        <f>COUNTIF('Мэдлэг'!D23:N23,1)+COUNTIF('Чадвар'!D23:Y23,1)+COUNTIF('Төлөвшил'!D23:G23,1)</f>
+        <f>COUNTIF('Мэдлэг'!D22:N22,1)+COUNTIF('Чадвар'!D22:Y22,1)+COUNTIF('Төлөвшил'!D22:G22,1)</f>
         <v/>
       </c>
       <c r="G22" s="12">
-        <f>IF((COUNT('Мэдлэг'!D23:N23)+COUNT('Чадвар'!D23:Y23)+COUNT('Төлөвшил'!D23:G23))=0,"",ROUND(F22/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D22:N22)+COUNT('Чадвар'!D22:Y22)+COUNT('Төлөвшил'!D22:G22))=0,"",ROUND(F22/37*100,1))</f>
         <v/>
       </c>
       <c r="H22" s="14">
@@ -1309,23 +1309,23 @@
         </is>
       </c>
       <c r="C23" s="12">
-        <f>IF(COUNT('Мэдлэг'!D24:N24)=0,"",ROUND(COUNTIF('Мэдлэг'!D24:N24,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D23:N23)=0,"",ROUND(COUNTIF('Мэдлэг'!D23:N23,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D23" s="12">
-        <f>IF(COUNT('Чадвар'!D24:Y24)=0,"",ROUND(COUNTIF('Чадвар'!D24:Y24,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D23:Y23)=0,"",ROUND(COUNTIF('Чадвар'!D23:Y23,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>IF(COUNT('Төлөвшил'!D24:G24)=0,"",ROUND(COUNTIF('Төлөвшил'!D24:G24,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D23:G23)=0,"",ROUND(COUNTIF('Төлөвшил'!D23:G23,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F23" s="12">
-        <f>COUNTIF('Мэдлэг'!D24:N24,1)+COUNTIF('Чадвар'!D24:Y24,1)+COUNTIF('Төлөвшил'!D24:G24,1)</f>
+        <f>COUNTIF('Мэдлэг'!D23:N23,1)+COUNTIF('Чадвар'!D23:Y23,1)+COUNTIF('Төлөвшил'!D23:G23,1)</f>
         <v/>
       </c>
       <c r="G23" s="12">
-        <f>IF((COUNT('Мэдлэг'!D24:N24)+COUNT('Чадвар'!D24:Y24)+COUNT('Төлөвшил'!D24:G24))=0,"",ROUND(F23/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D23:N23)+COUNT('Чадвар'!D23:Y23)+COUNT('Төлөвшил'!D23:G23))=0,"",ROUND(F23/37*100,1))</f>
         <v/>
       </c>
       <c r="H23" s="14">
@@ -1343,23 +1343,23 @@
         </is>
       </c>
       <c r="C24" s="12">
-        <f>IF(COUNT('Мэдлэг'!D25:N25)=0,"",ROUND(COUNTIF('Мэдлэг'!D25:N25,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D24:N24)=0,"",ROUND(COUNTIF('Мэдлэг'!D24:N24,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D24" s="12">
-        <f>IF(COUNT('Чадвар'!D25:Y25)=0,"",ROUND(COUNTIF('Чадвар'!D25:Y25,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D24:Y24)=0,"",ROUND(COUNTIF('Чадвар'!D24:Y24,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>IF(COUNT('Төлөвшил'!D25:G25)=0,"",ROUND(COUNTIF('Төлөвшил'!D25:G25,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D24:G24)=0,"",ROUND(COUNTIF('Төлөвшил'!D24:G24,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F24" s="12">
-        <f>COUNTIF('Мэдлэг'!D25:N25,1)+COUNTIF('Чадвар'!D25:Y25,1)+COUNTIF('Төлөвшил'!D25:G25,1)</f>
+        <f>COUNTIF('Мэдлэг'!D24:N24,1)+COUNTIF('Чадвар'!D24:Y24,1)+COUNTIF('Төлөвшил'!D24:G24,1)</f>
         <v/>
       </c>
       <c r="G24" s="12">
-        <f>IF((COUNT('Мэдлэг'!D25:N25)+COUNT('Чадвар'!D25:Y25)+COUNT('Төлөвшил'!D25:G25))=0,"",ROUND(F24/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D24:N24)+COUNT('Чадвар'!D24:Y24)+COUNT('Төлөвшил'!D24:G24))=0,"",ROUND(F24/37*100,1))</f>
         <v/>
       </c>
       <c r="H24" s="14">
@@ -1377,23 +1377,23 @@
         </is>
       </c>
       <c r="C25" s="12">
-        <f>IF(COUNT('Мэдлэг'!D26:N26)=0,"",ROUND(COUNTIF('Мэдлэг'!D26:N26,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D25:N25)=0,"",ROUND(COUNTIF('Мэдлэг'!D25:N25,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D25" s="12">
-        <f>IF(COUNT('Чадвар'!D26:Y26)=0,"",ROUND(COUNTIF('Чадвар'!D26:Y26,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D25:Y25)=0,"",ROUND(COUNTIF('Чадвар'!D25:Y25,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>IF(COUNT('Төлөвшил'!D26:G26)=0,"",ROUND(COUNTIF('Төлөвшил'!D26:G26,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D25:G25)=0,"",ROUND(COUNTIF('Төлөвшил'!D25:G25,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F25" s="12">
-        <f>COUNTIF('Мэдлэг'!D26:N26,1)+COUNTIF('Чадвар'!D26:Y26,1)+COUNTIF('Төлөвшил'!D26:G26,1)</f>
+        <f>COUNTIF('Мэдлэг'!D25:N25,1)+COUNTIF('Чадвар'!D25:Y25,1)+COUNTIF('Төлөвшил'!D25:G25,1)</f>
         <v/>
       </c>
       <c r="G25" s="12">
-        <f>IF((COUNT('Мэдлэг'!D26:N26)+COUNT('Чадвар'!D26:Y26)+COUNT('Төлөвшил'!D26:G26))=0,"",ROUND(F25/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D25:N25)+COUNT('Чадвар'!D25:Y25)+COUNT('Төлөвшил'!D25:G25))=0,"",ROUND(F25/37*100,1))</f>
         <v/>
       </c>
       <c r="H25" s="14">
@@ -1411,23 +1411,23 @@
         </is>
       </c>
       <c r="C26" s="12">
-        <f>IF(COUNT('Мэдлэг'!D27:N27)=0,"",ROUND(COUNTIF('Мэдлэг'!D27:N27,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D26:N26)=0,"",ROUND(COUNTIF('Мэдлэг'!D26:N26,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D26" s="12">
-        <f>IF(COUNT('Чадвар'!D27:Y27)=0,"",ROUND(COUNTIF('Чадвар'!D27:Y27,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D26:Y26)=0,"",ROUND(COUNTIF('Чадвар'!D26:Y26,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>IF(COUNT('Төлөвшил'!D27:G27)=0,"",ROUND(COUNTIF('Төлөвшил'!D27:G27,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D26:G26)=0,"",ROUND(COUNTIF('Төлөвшил'!D26:G26,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F26" s="12">
-        <f>COUNTIF('Мэдлэг'!D27:N27,1)+COUNTIF('Чадвар'!D27:Y27,1)+COUNTIF('Төлөвшил'!D27:G27,1)</f>
+        <f>COUNTIF('Мэдлэг'!D26:N26,1)+COUNTIF('Чадвар'!D26:Y26,1)+COUNTIF('Төлөвшил'!D26:G26,1)</f>
         <v/>
       </c>
       <c r="G26" s="12">
-        <f>IF((COUNT('Мэдлэг'!D27:N27)+COUNT('Чадвар'!D27:Y27)+COUNT('Төлөвшил'!D27:G27))=0,"",ROUND(F26/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D26:N26)+COUNT('Чадвар'!D26:Y26)+COUNT('Төлөвшил'!D26:G26))=0,"",ROUND(F26/37*100,1))</f>
         <v/>
       </c>
       <c r="H26" s="14">
@@ -1445,23 +1445,23 @@
         </is>
       </c>
       <c r="C27" s="12">
-        <f>IF(COUNT('Мэдлэг'!D28:N28)=0,"",ROUND(COUNTIF('Мэдлэг'!D28:N28,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D27:N27)=0,"",ROUND(COUNTIF('Мэдлэг'!D27:N27,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D27" s="12">
-        <f>IF(COUNT('Чадвар'!D28:Y28)=0,"",ROUND(COUNTIF('Чадвар'!D28:Y28,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D27:Y27)=0,"",ROUND(COUNTIF('Чадвар'!D27:Y27,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>IF(COUNT('Төлөвшил'!D28:G28)=0,"",ROUND(COUNTIF('Төлөвшил'!D28:G28,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D27:G27)=0,"",ROUND(COUNTIF('Төлөвшил'!D27:G27,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F27" s="12">
-        <f>COUNTIF('Мэдлэг'!D28:N28,1)+COUNTIF('Чадвар'!D28:Y28,1)+COUNTIF('Төлөвшил'!D28:G28,1)</f>
+        <f>COUNTIF('Мэдлэг'!D27:N27,1)+COUNTIF('Чадвар'!D27:Y27,1)+COUNTIF('Төлөвшил'!D27:G27,1)</f>
         <v/>
       </c>
       <c r="G27" s="12">
-        <f>IF((COUNT('Мэдлэг'!D28:N28)+COUNT('Чадвар'!D28:Y28)+COUNT('Төлөвшил'!D28:G28))=0,"",ROUND(F27/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D27:N27)+COUNT('Чадвар'!D27:Y27)+COUNT('Төлөвшил'!D27:G27))=0,"",ROUND(F27/37*100,1))</f>
         <v/>
       </c>
       <c r="H27" s="14">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="C28" s="12">
-        <f>IF(COUNT('Мэдлэг'!D29:N29)=0,"",ROUND(COUNTIF('Мэдлэг'!D29:N29,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D28:N28)=0,"",ROUND(COUNTIF('Мэдлэг'!D28:N28,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D28" s="12">
-        <f>IF(COUNT('Чадвар'!D29:Y29)=0,"",ROUND(COUNTIF('Чадвар'!D29:Y29,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D28:Y28)=0,"",ROUND(COUNTIF('Чадвар'!D28:Y28,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>IF(COUNT('Төлөвшил'!D29:G29)=0,"",ROUND(COUNTIF('Төлөвшил'!D29:G29,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D28:G28)=0,"",ROUND(COUNTIF('Төлөвшил'!D28:G28,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F28" s="12">
-        <f>COUNTIF('Мэдлэг'!D29:N29,1)+COUNTIF('Чадвар'!D29:Y29,1)+COUNTIF('Төлөвшил'!D29:G29,1)</f>
+        <f>COUNTIF('Мэдлэг'!D28:N28,1)+COUNTIF('Чадвар'!D28:Y28,1)+COUNTIF('Төлөвшил'!D28:G28,1)</f>
         <v/>
       </c>
       <c r="G28" s="12">
-        <f>IF((COUNT('Мэдлэг'!D29:N29)+COUNT('Чадвар'!D29:Y29)+COUNT('Төлөвшил'!D29:G29))=0,"",ROUND(F28/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D28:N28)+COUNT('Чадвар'!D28:Y28)+COUNT('Төлөвшил'!D28:G28))=0,"",ROUND(F28/37*100,1))</f>
         <v/>
       </c>
       <c r="H28" s="14">
@@ -1513,23 +1513,23 @@
         </is>
       </c>
       <c r="C29" s="12">
-        <f>IF(COUNT('Мэдлэг'!D30:N30)=0,"",ROUND(COUNTIF('Мэдлэг'!D30:N30,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D29:N29)=0,"",ROUND(COUNTIF('Мэдлэг'!D29:N29,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D29" s="12">
-        <f>IF(COUNT('Чадвар'!D30:Y30)=0,"",ROUND(COUNTIF('Чадвар'!D30:Y30,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D29:Y29)=0,"",ROUND(COUNTIF('Чадвар'!D29:Y29,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>IF(COUNT('Төлөвшил'!D30:G30)=0,"",ROUND(COUNTIF('Төлөвшил'!D30:G30,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D29:G29)=0,"",ROUND(COUNTIF('Төлөвшил'!D29:G29,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F29" s="12">
-        <f>COUNTIF('Мэдлэг'!D30:N30,1)+COUNTIF('Чадвар'!D30:Y30,1)+COUNTIF('Төлөвшил'!D30:G30,1)</f>
+        <f>COUNTIF('Мэдлэг'!D29:N29,1)+COUNTIF('Чадвар'!D29:Y29,1)+COUNTIF('Төлөвшил'!D29:G29,1)</f>
         <v/>
       </c>
       <c r="G29" s="12">
-        <f>IF((COUNT('Мэдлэг'!D30:N30)+COUNT('Чадвар'!D30:Y30)+COUNT('Төлөвшил'!D30:G30))=0,"",ROUND(F29/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D29:N29)+COUNT('Чадвар'!D29:Y29)+COUNT('Төлөвшил'!D29:G29))=0,"",ROUND(F29/37*100,1))</f>
         <v/>
       </c>
       <c r="H29" s="14">
@@ -1547,23 +1547,23 @@
         </is>
       </c>
       <c r="C30" s="12">
-        <f>IF(COUNT('Мэдлэг'!D31:N31)=0,"",ROUND(COUNTIF('Мэдлэг'!D31:N31,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D30:N30)=0,"",ROUND(COUNTIF('Мэдлэг'!D30:N30,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D30" s="12">
-        <f>IF(COUNT('Чадвар'!D31:Y31)=0,"",ROUND(COUNTIF('Чадвар'!D31:Y31,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D30:Y30)=0,"",ROUND(COUNTIF('Чадвар'!D30:Y30,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>IF(COUNT('Төлөвшил'!D31:G31)=0,"",ROUND(COUNTIF('Төлөвшил'!D31:G31,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D30:G30)=0,"",ROUND(COUNTIF('Төлөвшил'!D30:G30,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F30" s="12">
-        <f>COUNTIF('Мэдлэг'!D31:N31,1)+COUNTIF('Чадвар'!D31:Y31,1)+COUNTIF('Төлөвшил'!D31:G31,1)</f>
+        <f>COUNTIF('Мэдлэг'!D30:N30,1)+COUNTIF('Чадвар'!D30:Y30,1)+COUNTIF('Төлөвшил'!D30:G30,1)</f>
         <v/>
       </c>
       <c r="G30" s="12">
-        <f>IF((COUNT('Мэдлэг'!D31:N31)+COUNT('Чадвар'!D31:Y31)+COUNT('Төлөвшил'!D31:G31))=0,"",ROUND(F30/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D30:N30)+COUNT('Чадвар'!D30:Y30)+COUNT('Төлөвшил'!D30:G30))=0,"",ROUND(F30/37*100,1))</f>
         <v/>
       </c>
       <c r="H30" s="14">
@@ -1581,23 +1581,23 @@
         </is>
       </c>
       <c r="C31" s="12">
-        <f>IF(COUNT('Мэдлэг'!D32:N32)=0,"",ROUND(COUNTIF('Мэдлэг'!D32:N32,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D31:N31)=0,"",ROUND(COUNTIF('Мэдлэг'!D31:N31,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D31" s="12">
-        <f>IF(COUNT('Чадвар'!D32:Y32)=0,"",ROUND(COUNTIF('Чадвар'!D32:Y32,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D31:Y31)=0,"",ROUND(COUNTIF('Чадвар'!D31:Y31,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E31" s="12">
-        <f>IF(COUNT('Төлөвшил'!D32:G32)=0,"",ROUND(COUNTIF('Төлөвшил'!D32:G32,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D31:G31)=0,"",ROUND(COUNTIF('Төлөвшил'!D31:G31,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F31" s="12">
-        <f>COUNTIF('Мэдлэг'!D32:N32,1)+COUNTIF('Чадвар'!D32:Y32,1)+COUNTIF('Төлөвшил'!D32:G32,1)</f>
+        <f>COUNTIF('Мэдлэг'!D31:N31,1)+COUNTIF('Чадвар'!D31:Y31,1)+COUNTIF('Төлөвшил'!D31:G31,1)</f>
         <v/>
       </c>
       <c r="G31" s="12">
-        <f>IF((COUNT('Мэдлэг'!D32:N32)+COUNT('Чадвар'!D32:Y32)+COUNT('Төлөвшил'!D32:G32))=0,"",ROUND(F31/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D31:N31)+COUNT('Чадвар'!D31:Y31)+COUNT('Төлөвшил'!D31:G31))=0,"",ROUND(F31/37*100,1))</f>
         <v/>
       </c>
       <c r="H31" s="14">
@@ -1615,23 +1615,23 @@
         </is>
       </c>
       <c r="C32" s="12">
-        <f>IF(COUNT('Мэдлэг'!D33:N33)=0,"",ROUND(COUNTIF('Мэдлэг'!D33:N33,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D32:N32)=0,"",ROUND(COUNTIF('Мэдлэг'!D32:N32,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D32" s="12">
-        <f>IF(COUNT('Чадвар'!D33:Y33)=0,"",ROUND(COUNTIF('Чадвар'!D33:Y33,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D32:Y32)=0,"",ROUND(COUNTIF('Чадвар'!D32:Y32,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>IF(COUNT('Төлөвшил'!D33:G33)=0,"",ROUND(COUNTIF('Төлөвшил'!D33:G33,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D32:G32)=0,"",ROUND(COUNTIF('Төлөвшил'!D32:G32,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F32" s="12">
-        <f>COUNTIF('Мэдлэг'!D33:N33,1)+COUNTIF('Чадвар'!D33:Y33,1)+COUNTIF('Төлөвшил'!D33:G33,1)</f>
+        <f>COUNTIF('Мэдлэг'!D32:N32,1)+COUNTIF('Чадвар'!D32:Y32,1)+COUNTIF('Төлөвшил'!D32:G32,1)</f>
         <v/>
       </c>
       <c r="G32" s="12">
-        <f>IF((COUNT('Мэдлэг'!D33:N33)+COUNT('Чадвар'!D33:Y33)+COUNT('Төлөвшил'!D33:G33))=0,"",ROUND(F32/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D32:N32)+COUNT('Чадвар'!D32:Y32)+COUNT('Төлөвшил'!D32:G32))=0,"",ROUND(F32/37*100,1))</f>
         <v/>
       </c>
       <c r="H32" s="14">
@@ -1649,23 +1649,23 @@
         </is>
       </c>
       <c r="C33" s="12">
-        <f>IF(COUNT('Мэдлэг'!D34:N34)=0,"",ROUND(COUNTIF('Мэдлэг'!D34:N34,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D33:N33)=0,"",ROUND(COUNTIF('Мэдлэг'!D33:N33,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D33" s="12">
-        <f>IF(COUNT('Чадвар'!D34:Y34)=0,"",ROUND(COUNTIF('Чадвар'!D34:Y34,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D33:Y33)=0,"",ROUND(COUNTIF('Чадвар'!D33:Y33,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E33" s="12">
-        <f>IF(COUNT('Төлөвшил'!D34:G34)=0,"",ROUND(COUNTIF('Төлөвшил'!D34:G34,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D33:G33)=0,"",ROUND(COUNTIF('Төлөвшил'!D33:G33,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F33" s="12">
-        <f>COUNTIF('Мэдлэг'!D34:N34,1)+COUNTIF('Чадвар'!D34:Y34,1)+COUNTIF('Төлөвшил'!D34:G34,1)</f>
+        <f>COUNTIF('Мэдлэг'!D33:N33,1)+COUNTIF('Чадвар'!D33:Y33,1)+COUNTIF('Төлөвшил'!D33:G33,1)</f>
         <v/>
       </c>
       <c r="G33" s="12">
-        <f>IF((COUNT('Мэдлэг'!D34:N34)+COUNT('Чадвар'!D34:Y34)+COUNT('Төлөвшил'!D34:G34))=0,"",ROUND(F33/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D33:N33)+COUNT('Чадвар'!D33:Y33)+COUNT('Төлөвшил'!D33:G33))=0,"",ROUND(F33/37*100,1))</f>
         <v/>
       </c>
       <c r="H33" s="14">
@@ -1683,23 +1683,23 @@
         </is>
       </c>
       <c r="C34" s="12">
-        <f>IF(COUNT('Мэдлэг'!D35:N35)=0,"",ROUND(COUNTIF('Мэдлэг'!D35:N35,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D34:N34)=0,"",ROUND(COUNTIF('Мэдлэг'!D34:N34,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D34" s="12">
-        <f>IF(COUNT('Чадвар'!D35:Y35)=0,"",ROUND(COUNTIF('Чадвар'!D35:Y35,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D34:Y34)=0,"",ROUND(COUNTIF('Чадвар'!D34:Y34,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E34" s="12">
-        <f>IF(COUNT('Төлөвшил'!D35:G35)=0,"",ROUND(COUNTIF('Төлөвшил'!D35:G35,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D34:G34)=0,"",ROUND(COUNTIF('Төлөвшил'!D34:G34,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F34" s="12">
-        <f>COUNTIF('Мэдлэг'!D35:N35,1)+COUNTIF('Чадвар'!D35:Y35,1)+COUNTIF('Төлөвшил'!D35:G35,1)</f>
+        <f>COUNTIF('Мэдлэг'!D34:N34,1)+COUNTIF('Чадвар'!D34:Y34,1)+COUNTIF('Төлөвшил'!D34:G34,1)</f>
         <v/>
       </c>
       <c r="G34" s="12">
-        <f>IF((COUNT('Мэдлэг'!D35:N35)+COUNT('Чадвар'!D35:Y35)+COUNT('Төлөвшил'!D35:G35))=0,"",ROUND(F34/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D34:N34)+COUNT('Чадвар'!D34:Y34)+COUNT('Төлөвшил'!D34:G34))=0,"",ROUND(F34/37*100,1))</f>
         <v/>
       </c>
       <c r="H34" s="14">
@@ -1717,23 +1717,23 @@
         </is>
       </c>
       <c r="C35" s="12">
-        <f>IF(COUNT('Мэдлэг'!D36:N36)=0,"",ROUND(COUNTIF('Мэдлэг'!D36:N36,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D35:N35)=0,"",ROUND(COUNTIF('Мэдлэг'!D35:N35,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D35" s="12">
-        <f>IF(COUNT('Чадвар'!D36:Y36)=0,"",ROUND(COUNTIF('Чадвар'!D36:Y36,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D35:Y35)=0,"",ROUND(COUNTIF('Чадвар'!D35:Y35,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E35" s="12">
-        <f>IF(COUNT('Төлөвшил'!D36:G36)=0,"",ROUND(COUNTIF('Төлөвшил'!D36:G36,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D35:G35)=0,"",ROUND(COUNTIF('Төлөвшил'!D35:G35,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F35" s="12">
-        <f>COUNTIF('Мэдлэг'!D36:N36,1)+COUNTIF('Чадвар'!D36:Y36,1)+COUNTIF('Төлөвшил'!D36:G36,1)</f>
+        <f>COUNTIF('Мэдлэг'!D35:N35,1)+COUNTIF('Чадвар'!D35:Y35,1)+COUNTIF('Төлөвшил'!D35:G35,1)</f>
         <v/>
       </c>
       <c r="G35" s="12">
-        <f>IF((COUNT('Мэдлэг'!D36:N36)+COUNT('Чадвар'!D36:Y36)+COUNT('Төлөвшил'!D36:G36))=0,"",ROUND(F35/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D35:N35)+COUNT('Чадвар'!D35:Y35)+COUNT('Төлөвшил'!D35:G35))=0,"",ROUND(F35/37*100,1))</f>
         <v/>
       </c>
       <c r="H35" s="14">
@@ -1751,23 +1751,23 @@
         </is>
       </c>
       <c r="C36" s="12">
-        <f>IF(COUNT('Мэдлэг'!D37:N37)=0,"",ROUND(COUNTIF('Мэдлэг'!D37:N37,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D36:N36)=0,"",ROUND(COUNTIF('Мэдлэг'!D36:N36,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D36" s="12">
-        <f>IF(COUNT('Чадвар'!D37:Y37)=0,"",ROUND(COUNTIF('Чадвар'!D37:Y37,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D36:Y36)=0,"",ROUND(COUNTIF('Чадвар'!D36:Y36,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E36" s="12">
-        <f>IF(COUNT('Төлөвшил'!D37:G37)=0,"",ROUND(COUNTIF('Төлөвшил'!D37:G37,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D36:G36)=0,"",ROUND(COUNTIF('Төлөвшил'!D36:G36,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F36" s="12">
-        <f>COUNTIF('Мэдлэг'!D37:N37,1)+COUNTIF('Чадвар'!D37:Y37,1)+COUNTIF('Төлөвшил'!D37:G37,1)</f>
+        <f>COUNTIF('Мэдлэг'!D36:N36,1)+COUNTIF('Чадвар'!D36:Y36,1)+COUNTIF('Төлөвшил'!D36:G36,1)</f>
         <v/>
       </c>
       <c r="G36" s="12">
-        <f>IF((COUNT('Мэдлэг'!D37:N37)+COUNT('Чадвар'!D37:Y37)+COUNT('Төлөвшил'!D37:G37))=0,"",ROUND(F36/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D36:N36)+COUNT('Чадвар'!D36:Y36)+COUNT('Төлөвшил'!D36:G36))=0,"",ROUND(F36/37*100,1))</f>
         <v/>
       </c>
       <c r="H36" s="14">
@@ -1785,23 +1785,23 @@
         </is>
       </c>
       <c r="C37" s="12">
-        <f>IF(COUNT('Мэдлэг'!D38:N38)=0,"",ROUND(COUNTIF('Мэдлэг'!D38:N38,1)/11*100,1))</f>
+        <f>IF(COUNT('Мэдлэг'!D37:N37)=0,"",ROUND(COUNTIF('Мэдлэг'!D37:N37,1)/11*100,1))</f>
         <v/>
       </c>
       <c r="D37" s="12">
-        <f>IF(COUNT('Чадвар'!D38:Y38)=0,"",ROUND(COUNTIF('Чадвар'!D38:Y38,1)/22*100,1))</f>
+        <f>IF(COUNT('Чадвар'!D37:Y37)=0,"",ROUND(COUNTIF('Чадвар'!D37:Y37,1)/22*100,1))</f>
         <v/>
       </c>
       <c r="E37" s="12">
-        <f>IF(COUNT('Төлөвшил'!D38:G38)=0,"",ROUND(COUNTIF('Төлөвшил'!D38:G38,1)/4*100,1))</f>
+        <f>IF(COUNT('Төлөвшил'!D37:G37)=0,"",ROUND(COUNTIF('Төлөвшил'!D37:G37,1)/4*100,1))</f>
         <v/>
       </c>
       <c r="F37" s="12">
-        <f>COUNTIF('Мэдлэг'!D38:N38,1)+COUNTIF('Чадвар'!D38:Y38,1)+COUNTIF('Төлөвшил'!D38:G38,1)</f>
+        <f>COUNTIF('Мэдлэг'!D37:N37,1)+COUNTIF('Чадвар'!D37:Y37,1)+COUNTIF('Төлөвшил'!D37:G37,1)</f>
         <v/>
       </c>
       <c r="G37" s="12">
-        <f>IF((COUNT('Мэдлэг'!D38:N38)+COUNT('Чадвар'!D38:Y38)+COUNT('Төлөвшил'!D38:G38))=0,"",ROUND(F37/37*100,1))</f>
+        <f>IF((COUNT('Мэдлэг'!D37:N37)+COUNT('Чадвар'!D37:Y37)+COUNT('Төлөвшил'!D37:G37))=0,"",ROUND(F37/37*100,1))</f>
         <v/>
       </c>
       <c r="H37" s="14">
@@ -1951,7 +1951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -2173,42 +2173,64 @@
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>11</v>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
       </c>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
@@ -2216,91 +2238,89 @@
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
     </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="12">
+        <f>IF(Нэгтгэл!B7="","",Нэгтгэл!B7)</f>
+        <v/>
+      </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="4" t="n"/>
+      <c r="D7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12">
+        <f>COUNTIF(D7:N7,1)</f>
+        <v/>
+      </c>
+      <c r="P7" s="12">
+        <f>IF(COUNT(D7:N7)=0,"",ROUND(O7/11*100,1))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="12">
+        <f>COUNTIF(D7:N7,0)</f>
+        <v/>
+      </c>
+      <c r="R7" s="12">
+        <f>IF(COUNT(D7:N7)=0,"",ROUND(Q7/11*100,1))</f>
+        <v/>
+      </c>
+      <c r="S7" s="20">
+        <f>IF(P7="","",IF(P7&gt;=Нэгтгэл!$K$4,"Хангалттай эзэмшиж байна",IF(P7&gt;=Нэгтгэл!$K$5,"Ахиж байна","Хөгжиж байна")))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="12">
-        <f>IF(Нэгтгэл!B7="","",Нэгтгэл!B7)</f>
+        <f>IF(Нэгтгэл!B8="","",Нэгтгэл!B8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="13" t="n">
         <v>1</v>
@@ -2309,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="13" t="n">
         <v>1</v>
@@ -2321,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="12">
         <f>COUNTIF(D8:N8,1)</f>
@@ -2346,39 +2366,39 @@
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="12">
-        <f>IF(Нэгтгэл!B8="","",Нэгтгэл!B8)</f>
+        <f>IF(Нэгтгэл!B9="","",Нэгтгэл!B9)</f>
         <v/>
       </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>1</v>
@@ -2409,10 +2429,10 @@
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="12">
-        <f>IF(Нэгтгэл!B9="","",Нэгтгэл!B9)</f>
+        <f>IF(Нэгтгэл!B10="","",Нэгтгэл!B10)</f>
         <v/>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -2420,19 +2440,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="13" t="n">
         <v>1</v>
@@ -2472,10 +2492,10 @@
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="12">
-        <f>IF(Нэгтгэл!B10="","",Нэгтгэл!B10)</f>
+        <f>IF(Нэгтгэл!B11="","",Нэгтгэл!B11)</f>
         <v/>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -2483,10 +2503,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>1</v>
@@ -2495,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="13" t="n">
         <v>1</v>
@@ -2504,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>1</v>
@@ -2535,10 +2555,10 @@
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="12">
-        <f>IF(Нэгтгэл!B11="","",Нэгтгэл!B11)</f>
+        <f>IF(Нэгтгэл!B12="","",Нэгтгэл!B12)</f>
         <v/>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -2549,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>1</v>
@@ -2567,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>1</v>
@@ -2598,15 +2618,15 @@
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="12">
-        <f>IF(Нэгтгэл!B12="","",Нэгтгэл!B12)</f>
+        <f>IF(Нэгтгэл!B13="","",Нэгтгэл!B13)</f>
         <v/>
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>1</v>
@@ -2618,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="13" t="n">
         <v>0</v>
@@ -2636,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="12">
         <f>COUNTIF(D13:N13,1)</f>
@@ -2661,30 +2681,30 @@
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="12">
-        <f>IF(Нэгтгэл!B13="","",Нэгтгэл!B13)</f>
+        <f>IF(Нэгтгэл!B14="","",Нэгтгэл!B14)</f>
         <v/>
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="n">
         <v>1</v>
@@ -2699,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12">
         <f>COUNTIF(D14:N14,1)</f>
@@ -2724,10 +2744,10 @@
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="12">
-        <f>IF(Нэгтгэл!B14="","",Нэгтгэл!B14)</f>
+        <f>IF(Нэгтгэл!B15="","",Нэгтгэл!B15)</f>
         <v/>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -2735,10 +2755,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>1</v>
@@ -2747,19 +2767,19 @@
         <v>1</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>1</v>
@@ -2787,42 +2807,42 @@
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16" s="12">
-        <f>IF(Нэгтгэл!B15="","",Нэгтгэл!B15)</f>
+        <f>IF(Нэгтгэл!B16="","",Нэгтгэл!B16)</f>
         <v/>
       </c>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>1</v>
@@ -2850,15 +2870,15 @@
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="12">
-        <f>IF(Нэгтгэл!B16="","",Нэгтгэл!B16)</f>
+        <f>IF(Нэгтгэл!B17="","",Нэгтгэл!B17)</f>
         <v/>
       </c>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>1</v>
@@ -2876,16 +2896,16 @@
         <v>1</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>1</v>
@@ -2913,15 +2933,15 @@
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="12">
-        <f>IF(Нэгтгэл!B17="","",Нэгтгэл!B17)</f>
+        <f>IF(Нэгтгэл!B18="","",Нэгтгэл!B18)</f>
         <v/>
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>1</v>
@@ -2933,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="13" t="n">
         <v>1</v>
@@ -2948,10 +2968,10 @@
         <v>1</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="12">
         <f>COUNTIF(D18:N18,1)</f>
@@ -2976,10 +2996,10 @@
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="12">
-        <f>IF(Нэгтгэл!B18="","",Нэгтгэл!B18)</f>
+        <f>IF(Нэгтгэл!B19="","",Нэгтгэл!B19)</f>
         <v/>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -2990,22 +3010,22 @@
         <v>1</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="13" t="n">
         <v>1</v>
@@ -3014,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="12">
         <f>COUNTIF(D19:N19,1)</f>
@@ -3039,10 +3059,10 @@
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="12">
-        <f>IF(Нэгтгэл!B19="","",Нэгтгэл!B19)</f>
+        <f>IF(Нэгтгэл!B20="","",Нэгтгэл!B20)</f>
         <v/>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -3050,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>0</v>
@@ -3062,13 +3082,13 @@
         <v>1</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="13" t="n">
         <v>1</v>
@@ -3077,7 +3097,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="12">
         <f>COUNTIF(D20:N20,1)</f>
@@ -3102,30 +3122,30 @@
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="12">
-        <f>IF(Нэгтгэл!B20="","",Нэгтгэл!B20)</f>
+        <f>IF(Нэгтгэл!B21="","",Нэгтгэл!B21)</f>
         <v/>
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="13" t="n">
         <v>1</v>
@@ -3165,10 +3185,10 @@
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="12">
-        <f>IF(Нэгтгэл!B21="","",Нэгтгэл!B21)</f>
+        <f>IF(Нэгтгэл!B22="","",Нэгтгэл!B22)</f>
         <v/>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -3176,13 +3196,13 @@
         <v>1</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="13" t="n">
         <v>1</v>
@@ -3203,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="12">
         <f>COUNTIF(D22:N22,1)</f>
@@ -3228,30 +3248,30 @@
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="12">
-        <f>IF(Нэгтгэл!B22="","",Нэгтгэл!B22)</f>
+        <f>IF(Нэгтгэл!B23="","",Нэгтгэл!B23)</f>
         <v/>
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="13" t="n">
         <v>1</v>
@@ -3260,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>1</v>
@@ -3291,10 +3311,10 @@
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="12">
-        <f>IF(Нэгтгэл!B23="","",Нэгтгэл!B23)</f>
+        <f>IF(Нэгтгэл!B24="","",Нэгтгэл!B24)</f>
         <v/>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -3305,16 +3325,16 @@
         <v>1</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="13" t="n">
         <v>1</v>
@@ -3323,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="13" t="n">
         <v>1</v>
@@ -3354,15 +3374,15 @@
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="12">
-        <f>IF(Нэгтгэл!B24="","",Нэгтгэл!B24)</f>
+        <f>IF(Нэгтгэл!B25="","",Нэгтгэл!B25)</f>
         <v/>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>1</v>
@@ -3374,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>1</v>
@@ -3386,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="12">
         <f>COUNTIF(D25:N25,1)</f>
@@ -3417,15 +3437,15 @@
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="12">
-        <f>IF(Нэгтгэл!B25="","",Нэгтгэл!B25)</f>
+        <f>IF(Нэгтгэл!B26="","",Нэгтгэл!B26)</f>
         <v/>
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>1</v>
@@ -3434,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="13" t="n">
         <v>1</v>
@@ -3443,19 +3463,19 @@
         <v>1</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12">
         <f>COUNTIF(D26:N26,1)</f>
@@ -3480,24 +3500,24 @@
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="12">
-        <f>IF(Нэгтгэл!B26="","",Нэгтгэл!B26)</f>
+        <f>IF(Нэгтгэл!B27="","",Нэгтгэл!B27)</f>
         <v/>
       </c>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="13" t="n">
         <v>1</v>
@@ -3506,16 +3526,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="13" t="n">
         <v>1</v>
@@ -3543,10 +3563,10 @@
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="12">
-        <f>IF(Нэгтгэл!B27="","",Нэгтгэл!B27)</f>
+        <f>IF(Нэгтгэл!B28="","",Нэгтгэл!B28)</f>
         <v/>
       </c>
       <c r="C28" s="4" t="n"/>
@@ -3560,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="13" t="n">
         <v>1</v>
@@ -3569,10 +3589,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="13" t="n">
         <v>1</v>
@@ -3606,10 +3626,10 @@
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" s="12">
-        <f>IF(Нэгтгэл!B28="","",Нэгтгэл!B28)</f>
+        <f>IF(Нэгтгэл!B29="","",Нэгтгэл!B29)</f>
         <v/>
       </c>
       <c r="C29" s="4" t="n"/>
@@ -3617,13 +3637,13 @@
         <v>1</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="13" t="n">
         <v>1</v>
@@ -3632,13 +3652,13 @@
         <v>1</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="n">
         <v>1</v>
@@ -3669,10 +3689,10 @@
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="12">
-        <f>IF(Нэгтгэл!B29="","",Нэгтгэл!B29)</f>
+        <f>IF(Нэгтгэл!B30="","",Нэгтгэл!B30)</f>
         <v/>
       </c>
       <c r="C30" s="4" t="n"/>
@@ -3680,7 +3700,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="13" t="n">
         <v>1</v>
@@ -3692,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="13" t="n">
         <v>1</v>
@@ -3701,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="13" t="n">
         <v>1</v>
@@ -3732,15 +3752,15 @@
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="12">
-        <f>IF(Нэгтгэл!B30="","",Нэгтгэл!B30)</f>
+        <f>IF(Нэгтгэл!B31="","",Нэгтгэл!B31)</f>
         <v/>
       </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>1</v>
@@ -3752,7 +3772,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="13" t="n">
         <v>0</v>
@@ -3767,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="13" t="n">
         <v>1</v>
@@ -3795,10 +3815,10 @@
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="12">
-        <f>IF(Нэгтгэл!B31="","",Нэгтгэл!B31)</f>
+        <f>IF(Нэгтгэл!B32="","",Нэгтгэл!B32)</f>
         <v/>
       </c>
       <c r="C32" s="4" t="n"/>
@@ -3809,16 +3829,16 @@
         <v>1</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="13" t="n">
         <v>1</v>
@@ -3827,13 +3847,13 @@
         <v>0</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="12">
         <f>COUNTIF(D32:N32,1)</f>
@@ -3858,21 +3878,21 @@
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="12">
-        <f>IF(Нэгтгэл!B32="","",Нэгтгэл!B32)</f>
+        <f>IF(Нэгтгэл!B33="","",Нэгтгэл!B33)</f>
         <v/>
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>1</v>
@@ -3881,22 +3901,22 @@
         <v>1</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="13" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="12">
         <f>COUNTIF(D33:N33,1)</f>
@@ -3921,10 +3941,10 @@
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="12">
-        <f>IF(Нэгтгэл!B33="","",Нэгтгэл!B33)</f>
+        <f>IF(Нэгтгэл!B34="","",Нэгтгэл!B34)</f>
         <v/>
       </c>
       <c r="C34" s="4" t="n"/>
@@ -3932,7 +3952,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="13" t="n">
         <v>1</v>
@@ -3944,7 +3964,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="13" t="n">
         <v>1</v>
@@ -3984,10 +4004,10 @@
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="12">
-        <f>IF(Нэгтгэл!B34="","",Нэгтгэл!B34)</f>
+        <f>IF(Нэгтгэл!B35="","",Нэгтгэл!B35)</f>
         <v/>
       </c>
       <c r="C35" s="4" t="n"/>
@@ -3995,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="13" t="n">
         <v>1</v>
@@ -4047,21 +4067,21 @@
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" s="12">
-        <f>IF(Нэгтгэл!B35="","",Нэгтгэл!B35)</f>
+        <f>IF(Нэгтгэл!B36="","",Нэгтгэл!B36)</f>
         <v/>
       </c>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>1</v>
@@ -4070,7 +4090,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="13" t="n">
         <v>1</v>
@@ -4082,7 +4102,7 @@
         <v>1</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" s="13" t="n">
         <v>1</v>
@@ -4110,15 +4130,15 @@
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="12">
-        <f>IF(Нэгтгэл!B36="","",Нэгтгэл!B36)</f>
+        <f>IF(Нэгтгэл!B37="","",Нэгтгэл!B37)</f>
         <v/>
       </c>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>1</v>
@@ -4130,25 +4150,25 @@
         <v>1</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="12">
         <f>COUNTIF(D37:N37,1)</f>
@@ -4171,380 +4191,317 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B38" s="12">
-        <f>IF(Нэгтгэл!B37="","",Нэгтгэл!B37)</f>
-        <v/>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="12">
-        <f>COUNTIF(D38:N38,1)</f>
-        <v/>
-      </c>
-      <c r="P38" s="12">
-        <f>IF(COUNT(D38:N38)=0,"",ROUND(O38/11*100,1))</f>
-        <v/>
-      </c>
-      <c r="Q38" s="12">
-        <f>COUNTIF(D38:N38,0)</f>
-        <v/>
-      </c>
-      <c r="R38" s="12">
-        <f>IF(COUNT(D38:N38)=0,"",ROUND(Q38/11*100,1))</f>
-        <v/>
-      </c>
-      <c r="S38" s="20">
-        <f>IF(P38="","",IF(P38&gt;=Нэгтгэл!$K$4,"Хангалттай эзэмшиж байна",IF(P38&gt;=Нэгтгэл!$K$5,"Ахиж байна","Хөгжиж байна")))</f>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Чадна (1)</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="5">
+        <f>COUNTIF(D7:D37,1)</f>
+        <v/>
+      </c>
+      <c r="E38" s="5">
+        <f>COUNTIF(E7:E37,1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="5">
+        <f>COUNTIF(F7:F37,1)</f>
+        <v/>
+      </c>
+      <c r="G38" s="5">
+        <f>COUNTIF(G7:G37,1)</f>
+        <v/>
+      </c>
+      <c r="H38" s="5">
+        <f>COUNTIF(H7:H37,1)</f>
+        <v/>
+      </c>
+      <c r="I38" s="5">
+        <f>COUNTIF(I7:I37,1)</f>
+        <v/>
+      </c>
+      <c r="J38" s="5">
+        <f>COUNTIF(J7:J37,1)</f>
+        <v/>
+      </c>
+      <c r="K38" s="5">
+        <f>COUNTIF(K7:K37,1)</f>
+        <v/>
+      </c>
+      <c r="L38" s="5">
+        <f>COUNTIF(L7:L37,1)</f>
+        <v/>
+      </c>
+      <c r="M38" s="5">
+        <f>COUNTIF(M7:M37,1)</f>
+        <v/>
+      </c>
+      <c r="N38" s="5">
+        <f>COUNTIF(N7:N37,1)</f>
+        <v/>
+      </c>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t>Хангалттай эзэмшиж байна</t>
+        </is>
+      </c>
+      <c r="P38" s="22" t="n"/>
+      <c r="Q38" s="22" t="n"/>
+      <c r="R38" s="23" t="n"/>
+      <c r="S38" s="5">
+        <f>COUNTIF(S7:S37,"Хангалттай эзэмшиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Чадна (1)</t>
+          <t>Хувь</t>
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="15" t="n"/>
       <c r="D39" s="5">
-        <f>COUNTIF(D8:D38,1)</f>
+        <f>IF(COUNT(D7:D37)=0,"",ROUND(COUNTIF(D7:D37,1)/COUNT(D7:D37)*100,1))</f>
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>COUNTIF(E8:E38,1)</f>
+        <f>IF(COUNT(E7:E37)=0,"",ROUND(COUNTIF(E7:E37,1)/COUNT(E7:E37)*100,1))</f>
         <v/>
       </c>
       <c r="F39" s="5">
-        <f>COUNTIF(F8:F38,1)</f>
+        <f>IF(COUNT(F7:F37)=0,"",ROUND(COUNTIF(F7:F37,1)/COUNT(F7:F37)*100,1))</f>
         <v/>
       </c>
       <c r="G39" s="5">
-        <f>COUNTIF(G8:G38,1)</f>
+        <f>IF(COUNT(G7:G37)=0,"",ROUND(COUNTIF(G7:G37,1)/COUNT(G7:G37)*100,1))</f>
         <v/>
       </c>
       <c r="H39" s="5">
-        <f>COUNTIF(H8:H38,1)</f>
+        <f>IF(COUNT(H7:H37)=0,"",ROUND(COUNTIF(H7:H37,1)/COUNT(H7:H37)*100,1))</f>
         <v/>
       </c>
       <c r="I39" s="5">
-        <f>COUNTIF(I8:I38,1)</f>
+        <f>IF(COUNT(I7:I37)=0,"",ROUND(COUNTIF(I7:I37,1)/COUNT(I7:I37)*100,1))</f>
         <v/>
       </c>
       <c r="J39" s="5">
-        <f>COUNTIF(J8:J38,1)</f>
+        <f>IF(COUNT(J7:J37)=0,"",ROUND(COUNTIF(J7:J37,1)/COUNT(J7:J37)*100,1))</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>COUNTIF(K8:K38,1)</f>
+        <f>IF(COUNT(K7:K37)=0,"",ROUND(COUNTIF(K7:K37,1)/COUNT(K7:K37)*100,1))</f>
         <v/>
       </c>
       <c r="L39" s="5">
-        <f>COUNTIF(L8:L38,1)</f>
+        <f>IF(COUNT(L7:L37)=0,"",ROUND(COUNTIF(L7:L37,1)/COUNT(L7:L37)*100,1))</f>
         <v/>
       </c>
       <c r="M39" s="5">
-        <f>COUNTIF(M8:M38,1)</f>
+        <f>IF(COUNT(M7:M37)=0,"",ROUND(COUNTIF(M7:M37,1)/COUNT(M7:M37)*100,1))</f>
         <v/>
       </c>
       <c r="N39" s="5">
-        <f>COUNTIF(N8:N38,1)</f>
+        <f>IF(COUNT(N7:N37)=0,"",ROUND(COUNTIF(N7:N37,1)/COUNT(N7:N37)*100,1))</f>
         <v/>
       </c>
       <c r="O39" s="21" t="inlineStr">
         <is>
-          <t>Хангалттай эзэмшиж байна</t>
+          <t>Ахиж байна</t>
         </is>
       </c>
       <c r="P39" s="22" t="n"/>
       <c r="Q39" s="22" t="n"/>
       <c r="R39" s="23" t="n"/>
       <c r="S39" s="5">
-        <f>COUNTIF(S8:S38,"Хангалттай эзэмшиж байна")</f>
+        <f>COUNTIF(S7:S37,"Ахиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Хувь</t>
+          <t>Чадахгүй (0)</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="15" t="n"/>
       <c r="D40" s="5">
-        <f>IF(COUNT(D8:D38)=0,"",ROUND(COUNTIF(D8:D38,1)/COUNT(D8:D38)*100,1))</f>
+        <f>COUNTIF(D7:D37,0)</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>IF(COUNT(E8:E38)=0,"",ROUND(COUNTIF(E8:E38,1)/COUNT(E8:E38)*100,1))</f>
+        <f>COUNTIF(E7:E37,0)</f>
         <v/>
       </c>
       <c r="F40" s="5">
-        <f>IF(COUNT(F8:F38)=0,"",ROUND(COUNTIF(F8:F38,1)/COUNT(F8:F38)*100,1))</f>
+        <f>COUNTIF(F7:F37,0)</f>
         <v/>
       </c>
       <c r="G40" s="5">
-        <f>IF(COUNT(G8:G38)=0,"",ROUND(COUNTIF(G8:G38,1)/COUNT(G8:G38)*100,1))</f>
+        <f>COUNTIF(G7:G37,0)</f>
         <v/>
       </c>
       <c r="H40" s="5">
-        <f>IF(COUNT(H8:H38)=0,"",ROUND(COUNTIF(H8:H38,1)/COUNT(H8:H38)*100,1))</f>
+        <f>COUNTIF(H7:H37,0)</f>
         <v/>
       </c>
       <c r="I40" s="5">
-        <f>IF(COUNT(I8:I38)=0,"",ROUND(COUNTIF(I8:I38,1)/COUNT(I8:I38)*100,1))</f>
+        <f>COUNTIF(I7:I37,0)</f>
         <v/>
       </c>
       <c r="J40" s="5">
-        <f>IF(COUNT(J8:J38)=0,"",ROUND(COUNTIF(J8:J38,1)/COUNT(J8:J38)*100,1))</f>
+        <f>COUNTIF(J7:J37,0)</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IF(COUNT(K8:K38)=0,"",ROUND(COUNTIF(K8:K38,1)/COUNT(K8:K38)*100,1))</f>
+        <f>COUNTIF(K7:K37,0)</f>
         <v/>
       </c>
       <c r="L40" s="5">
-        <f>IF(COUNT(L8:L38)=0,"",ROUND(COUNTIF(L8:L38,1)/COUNT(L8:L38)*100,1))</f>
+        <f>COUNTIF(L7:L37,0)</f>
         <v/>
       </c>
       <c r="M40" s="5">
-        <f>IF(COUNT(M8:M38)=0,"",ROUND(COUNTIF(M8:M38,1)/COUNT(M8:M38)*100,1))</f>
+        <f>COUNTIF(M7:M37,0)</f>
         <v/>
       </c>
       <c r="N40" s="5">
-        <f>IF(COUNT(N8:N38)=0,"",ROUND(COUNTIF(N8:N38,1)/COUNT(N8:N38)*100,1))</f>
+        <f>COUNTIF(N7:N37,0)</f>
         <v/>
       </c>
       <c r="O40" s="21" t="inlineStr">
         <is>
-          <t>Ахиж байна</t>
+          <t>Хөгжиж байна</t>
         </is>
       </c>
       <c r="P40" s="22" t="n"/>
       <c r="Q40" s="22" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="5">
-        <f>COUNTIF(S8:S38,"Ахиж байна")</f>
+        <f>COUNTIF(S7:S37,"Хөгжиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Чадахгүй (0)</t>
+          <t>Хувь</t>
         </is>
       </c>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="15" t="n"/>
       <c r="D41" s="5">
-        <f>COUNTIF(D8:D38,0)</f>
+        <f>IF(COUNT(D7:D37)=0,"",ROUND(COUNTIF(D7:D37,0)/COUNT(D7:D37)*100,1))</f>
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>COUNTIF(E8:E38,0)</f>
+        <f>IF(COUNT(E7:E37)=0,"",ROUND(COUNTIF(E7:E37,0)/COUNT(E7:E37)*100,1))</f>
         <v/>
       </c>
       <c r="F41" s="5">
-        <f>COUNTIF(F8:F38,0)</f>
+        <f>IF(COUNT(F7:F37)=0,"",ROUND(COUNTIF(F7:F37,0)/COUNT(F7:F37)*100,1))</f>
         <v/>
       </c>
       <c r="G41" s="5">
-        <f>COUNTIF(G8:G38,0)</f>
+        <f>IF(COUNT(G7:G37)=0,"",ROUND(COUNTIF(G7:G37,0)/COUNT(G7:G37)*100,1))</f>
         <v/>
       </c>
       <c r="H41" s="5">
-        <f>COUNTIF(H8:H38,0)</f>
+        <f>IF(COUNT(H7:H37)=0,"",ROUND(COUNTIF(H7:H37,0)/COUNT(H7:H37)*100,1))</f>
         <v/>
       </c>
       <c r="I41" s="5">
-        <f>COUNTIF(I8:I38,0)</f>
+        <f>IF(COUNT(I7:I37)=0,"",ROUND(COUNTIF(I7:I37,0)/COUNT(I7:I37)*100,1))</f>
         <v/>
       </c>
       <c r="J41" s="5">
-        <f>COUNTIF(J8:J38,0)</f>
+        <f>IF(COUNT(J7:J37)=0,"",ROUND(COUNTIF(J7:J37,0)/COUNT(J7:J37)*100,1))</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>COUNTIF(K8:K38,0)</f>
+        <f>IF(COUNT(K7:K37)=0,"",ROUND(COUNTIF(K7:K37,0)/COUNT(K7:K37)*100,1))</f>
         <v/>
       </c>
       <c r="L41" s="5">
-        <f>COUNTIF(L8:L38,0)</f>
+        <f>IF(COUNT(L7:L37)=0,"",ROUND(COUNTIF(L7:L37,0)/COUNT(L7:L37)*100,1))</f>
         <v/>
       </c>
       <c r="M41" s="5">
-        <f>COUNTIF(M8:M38,0)</f>
+        <f>IF(COUNT(M7:M37)=0,"",ROUND(COUNTIF(M7:M37,0)/COUNT(M7:M37)*100,1))</f>
         <v/>
       </c>
       <c r="N41" s="5">
-        <f>COUNTIF(N8:N38,0)</f>
-        <v/>
-      </c>
-      <c r="O41" s="21" t="inlineStr">
-        <is>
-          <t>Хөгжиж байна</t>
-        </is>
-      </c>
-      <c r="P41" s="22" t="n"/>
-      <c r="Q41" s="22" t="n"/>
-      <c r="R41" s="23" t="n"/>
-      <c r="S41" s="5">
-        <f>COUNTIF(S8:S38,"Хөгжиж байна")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Хувь</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="5">
-        <f>IF(COUNT(D8:D38)=0,"",ROUND(COUNTIF(D8:D38,0)/COUNT(D8:D38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="E42" s="5">
-        <f>IF(COUNT(E8:E38)=0,"",ROUND(COUNTIF(E8:E38,0)/COUNT(E8:E38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="F42" s="5">
-        <f>IF(COUNT(F8:F38)=0,"",ROUND(COUNTIF(F8:F38,0)/COUNT(F8:F38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="G42" s="5">
-        <f>IF(COUNT(G8:G38)=0,"",ROUND(COUNTIF(G8:G38,0)/COUNT(G8:G38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="H42" s="5">
-        <f>IF(COUNT(H8:H38)=0,"",ROUND(COUNTIF(H8:H38,0)/COUNT(H8:H38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="I42" s="5">
-        <f>IF(COUNT(I8:I38)=0,"",ROUND(COUNTIF(I8:I38,0)/COUNT(I8:I38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="J42" s="5">
-        <f>IF(COUNT(J8:J38)=0,"",ROUND(COUNTIF(J8:J38,0)/COUNT(J8:J38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="K42" s="5">
-        <f>IF(COUNT(K8:K38)=0,"",ROUND(COUNTIF(K8:K38,0)/COUNT(K8:K38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="L42" s="5">
-        <f>IF(COUNT(L8:L38)=0,"",ROUND(COUNTIF(L8:L38,0)/COUNT(L8:L38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="M42" s="5">
-        <f>IF(COUNT(M8:M38)=0,"",ROUND(COUNTIF(M8:M38,0)/COUNT(M8:M38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="N42" s="5">
-        <f>IF(COUNT(N8:N38)=0,"",ROUND(COUNTIF(N8:N38,0)/COUNT(N8:N38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="O42" s="15" t="n"/>
-      <c r="P42" s="15" t="n"/>
-      <c r="Q42" s="15" t="n"/>
-      <c r="R42" s="15" t="n"/>
-      <c r="S42" s="15" t="n"/>
+        <f>IF(COUNT(N7:N37)=0,"",ROUND(COUNTIF(N7:N37,0)/COUNT(N7:N37)*100,1))</f>
+        <v/>
+      </c>
+      <c r="O41" s="15" t="n"/>
+      <c r="P41" s="15" t="n"/>
+      <c r="Q41" s="15" t="n"/>
+      <c r="R41" s="15" t="n"/>
+      <c r="S41" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="S3:S6"/>
+    <mergeCell ref="O3:O6"/>
+    <mergeCell ref="Q3:Q6"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="P3:P7"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="R3:R7"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B3:C7"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A3:A6"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="O3:O7"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="O39:R39"/>
-    <mergeCell ref="Q3:Q7"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="S3:S7"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A40:C40"/>
+    <mergeCell ref="P3:P6"/>
     <mergeCell ref="O40:R40"/>
+    <mergeCell ref="R3:R6"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D3:N3"/>
-    <mergeCell ref="O41:R41"/>
+    <mergeCell ref="B3:C6"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A3:A7"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="A2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:N38">
+  <conditionalFormatting sqref="D7:N37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="1 эсвэл 0" error="Чадна бол 1, чадахгүй бол 0 гэж бичнэ." promptTitle="Тэмдэглэх" prompt="Чадна = 1, Чадахгүй = 0" type="list">
+    <dataValidation sqref="D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="1 эсвэл 0" error="Чадна бол 1, чадахгүй бол 0 гэж бичнэ." promptTitle="Тэмдэглэх" prompt="Чадна = 1, Чадахгүй = 0" type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4560,7 +4517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD42"/>
+  <dimension ref="A1:AD41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -4915,75 +4872,119 @@
       <c r="AC5" s="4" t="n"/>
       <c r="AD5" s="4" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>33</v>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="U6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="V6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="W6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="X6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="Y6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
       </c>
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
@@ -4991,149 +4992,125 @@
       <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="n"/>
     </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="12">
+        <f>IF(Нэгтгэл!B7="","",Нэгтгэл!B7)</f>
+        <v/>
+      </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="R7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="T7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="U7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="V7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="X7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="Y7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="4" t="n"/>
-      <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="4" t="n"/>
+      <c r="D7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="12">
+        <f>COUNTIF(D7:Y7,1)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="12">
+        <f>IF(COUNT(D7:Y7)=0,"",ROUND(Z7/22*100,1))</f>
+        <v/>
+      </c>
+      <c r="AB7" s="12">
+        <f>COUNTIF(D7:Y7,0)</f>
+        <v/>
+      </c>
+      <c r="AC7" s="12">
+        <f>IF(COUNT(D7:Y7)=0,"",ROUND(AB7/22*100,1))</f>
+        <v/>
+      </c>
+      <c r="AD7" s="20">
+        <f>IF(AA7="","",IF(AA7&gt;=Нэгтгэл!$K$4,"Хангалттай эзэмшиж байна",IF(AA7&gt;=Нэгтгэл!$K$5,"Ахиж байна","Хөгжиж байна")))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="12">
-        <f>IF(Нэгтгэл!B7="","",Нэгтгэл!B7)</f>
+        <f>IF(Нэгтгэл!B8="","",Нэгтгэл!B8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="13" t="n">
         <v>1</v>
@@ -5142,43 +5119,43 @@
         <v>1</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="13" t="n">
         <v>1</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
         <v>1</v>
       </c>
       <c r="R8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" s="13" t="n">
         <v>1</v>
@@ -5209,10 +5186,10 @@
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="12">
-        <f>IF(Нэгтгэл!B8="","",Нэгтгэл!B8)</f>
+        <f>IF(Нэгтгэл!B9="","",Нэгтгэл!B9)</f>
         <v/>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -5226,52 +5203,52 @@
         <v>1</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="V9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="13" t="n">
         <v>1</v>
@@ -5305,21 +5282,21 @@
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="12">
-        <f>IF(Нэгтгэл!B9="","",Нэгтгэл!B9)</f>
+        <f>IF(Нэгтгэл!B10="","",Нэгтгэл!B10)</f>
         <v/>
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>1</v>
@@ -5331,13 +5308,13 @@
         <v>1</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="13" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>1</v>
@@ -5346,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="13" t="n">
         <v>1</v>
@@ -5358,10 +5335,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="13" t="n">
         <v>1</v>
@@ -5370,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" s="13" t="n">
         <v>1</v>
@@ -5401,10 +5378,10 @@
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="12">
-        <f>IF(Нэгтгэл!B10="","",Нэгтгэл!B10)</f>
+        <f>IF(Нэгтгэл!B11="","",Нэгтгэл!B11)</f>
         <v/>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -5415,7 +5392,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>1</v>
@@ -5424,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="13" t="n">
         <v>1</v>
@@ -5436,28 +5413,28 @@
         <v>1</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="13" t="n">
         <v>1</v>
@@ -5497,33 +5474,33 @@
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="12">
-        <f>IF(Нэгтгэл!B11="","",Нэгтгэл!B11)</f>
+        <f>IF(Нэгтгэл!B12="","",Нэгтгэл!B12)</f>
         <v/>
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="13" t="n">
         <v>1</v>
@@ -5532,37 +5509,37 @@
         <v>1</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="13" t="n">
         <v>1</v>
@@ -5593,10 +5570,10 @@
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="12">
-        <f>IF(Нэгтгэл!B12="","",Нэгтгэл!B12)</f>
+        <f>IF(Нэгтгэл!B13="","",Нэгтгэл!B13)</f>
         <v/>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -5604,13 +5581,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="13" t="n">
         <v>1</v>
@@ -5622,22 +5599,22 @@
         <v>0</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="13" t="n">
         <v>1</v>
@@ -5646,13 +5623,13 @@
         <v>1</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="13" t="n">
         <v>1</v>
@@ -5689,10 +5666,10 @@
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="12">
-        <f>IF(Нэгтгэл!B13="","",Нэгтгэл!B13)</f>
+        <f>IF(Нэгтгэл!B14="","",Нэгтгэл!B14)</f>
         <v/>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -5700,13 +5677,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="13" t="n">
         <v>1</v>
@@ -5715,16 +5692,16 @@
         <v>1</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>1</v>
@@ -5742,10 +5719,10 @@
         <v>1</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="13" t="n">
         <v>1</v>
@@ -5785,10 +5762,10 @@
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="12">
-        <f>IF(Нэгтгэл!B14="","",Нэгтгэл!B14)</f>
+        <f>IF(Нэгтгэл!B15="","",Нэгтгэл!B15)</f>
         <v/>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -5796,13 +5773,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>1</v>
@@ -5817,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>1</v>
@@ -5829,16 +5806,16 @@
         <v>1</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="13" t="n">
         <v>1</v>
@@ -5856,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="Y15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="12">
         <f>COUNTIF(D15:Y15,1)</f>
@@ -5881,15 +5858,15 @@
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16" s="12">
-        <f>IF(Нэгтгэл!B15="","",Нэгтгэл!B15)</f>
+        <f>IF(Нэгтгэл!B16="","",Нэгтгэл!B16)</f>
         <v/>
       </c>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>1</v>
@@ -5901,13 +5878,13 @@
         <v>1</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="13" t="n">
         <v>1</v>
@@ -5916,7 +5893,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>1</v>
@@ -5925,13 +5902,13 @@
         <v>1</v>
       </c>
       <c r="P16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="13" t="n">
         <v>0</v>
@@ -5943,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="V16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" s="13" t="n">
         <v>1</v>
@@ -5952,7 +5929,7 @@
         <v>1</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" s="12">
         <f>COUNTIF(D16:Y16,1)</f>
@@ -5977,15 +5954,15 @@
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="12">
-        <f>IF(Нэгтгэл!B16="","",Нэгтгэл!B16)</f>
+        <f>IF(Нэгтгэл!B17="","",Нэгтгэл!B17)</f>
         <v/>
       </c>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>1</v>
@@ -5997,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="13" t="n">
         <v>1</v>
@@ -6006,19 +5983,19 @@
         <v>0</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="13" t="n">
         <v>1</v>
@@ -6030,7 +6007,7 @@
         <v>1</v>
       </c>
       <c r="S17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="13" t="n">
         <v>1</v>
@@ -6039,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="13" t="n">
         <v>1</v>
@@ -6073,21 +6050,21 @@
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="12">
-        <f>IF(Нэгтгэл!B17="","",Нэгтгэл!B17)</f>
+        <f>IF(Нэгтгэл!B18="","",Нэгтгэл!B18)</f>
         <v/>
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>1</v>
@@ -6096,10 +6073,10 @@
         <v>1</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="13" t="n">
         <v>0</v>
@@ -6111,25 +6088,25 @@
         <v>1</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="T18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" s="13" t="n">
         <v>1</v>
@@ -6144,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="12">
         <f>COUNTIF(D18:Y18,1)</f>
@@ -6169,10 +6146,10 @@
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="12">
-        <f>IF(Нэгтгэл!B18="","",Нэгтгэл!B18)</f>
+        <f>IF(Нэгтгэл!B19="","",Нэгтгэл!B19)</f>
         <v/>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -6183,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>1</v>
@@ -6192,13 +6169,13 @@
         <v>1</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="13" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="13" t="n">
         <v>1</v>
@@ -6216,22 +6193,22 @@
         <v>1</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="13" t="n">
         <v>1</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" s="13" t="n">
         <v>1</v>
       </c>
       <c r="V19" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" s="13" t="n">
         <v>1</v>
@@ -6240,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="Y19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="12">
         <f>COUNTIF(D19:Y19,1)</f>
@@ -6265,15 +6242,15 @@
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="12">
-        <f>IF(Нэгтгэл!B19="","",Нэгтгэл!B19)</f>
+        <f>IF(Нэгтгэл!B20="","",Нэгтгэл!B20)</f>
         <v/>
       </c>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>1</v>
@@ -6288,13 +6265,13 @@
         <v>1</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="13" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="13" t="n">
         <v>1</v>
@@ -6303,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="13" t="n">
         <v>1</v>
@@ -6312,7 +6289,7 @@
         <v>1</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" s="13" t="n">
         <v>1</v>
@@ -6321,16 +6298,16 @@
         <v>1</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" s="13" t="n">
         <v>1</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" s="13" t="n">
         <v>1</v>
@@ -6361,21 +6338,21 @@
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="12">
-        <f>IF(Нэгтгэл!B20="","",Нэгтгэл!B20)</f>
+        <f>IF(Нэгтгэл!B21="","",Нэгтгэл!B21)</f>
         <v/>
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>1</v>
@@ -6390,16 +6367,16 @@
         <v>1</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="13" t="n">
         <v>1</v>
@@ -6408,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>1</v>
@@ -6417,13 +6394,13 @@
         <v>1</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" s="13" t="n">
         <v>0</v>
@@ -6432,7 +6409,7 @@
         <v>1</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="12">
         <f>COUNTIF(D21:Y21,1)</f>
@@ -6457,18 +6434,18 @@
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="12">
-        <f>IF(Нэгтгэл!B21="","",Нэгтгэл!B21)</f>
+        <f>IF(Нэгтгэл!B22="","",Нэгтгэл!B22)</f>
         <v/>
       </c>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="13" t="n">
         <v>0</v>
@@ -6480,31 +6457,31 @@
         <v>1</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="13" t="n">
         <v>1</v>
@@ -6516,19 +6493,19 @@
         <v>1</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="12">
         <f>COUNTIF(D22:Y22,1)</f>
@@ -6553,10 +6530,10 @@
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="12">
-        <f>IF(Нэгтгэл!B22="","",Нэгтгэл!B22)</f>
+        <f>IF(Нэгтгэл!B23="","",Нэгтгэл!B23)</f>
         <v/>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -6564,7 +6541,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>0</v>
@@ -6582,25 +6559,25 @@
         <v>1</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="13" t="n">
         <v>1</v>
@@ -6612,10 +6589,10 @@
         <v>1</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23" s="13" t="n">
         <v>1</v>
@@ -6649,10 +6626,10 @@
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="12">
-        <f>IF(Нэгтгэл!B23="","",Нэгтгэл!B23)</f>
+        <f>IF(Нэгтгэл!B24="","",Нэгтгэл!B24)</f>
         <v/>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -6666,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="13" t="n">
         <v>1</v>
@@ -6678,16 +6655,16 @@
         <v>1</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="13" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="13" t="n">
         <v>1</v>
@@ -6696,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" s="13" t="n">
         <v>1</v>
@@ -6708,10 +6685,10 @@
         <v>1</v>
       </c>
       <c r="U24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="13" t="n">
         <v>1</v>
@@ -6745,39 +6722,39 @@
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="12">
-        <f>IF(Нэгтгэл!B24="","",Нэгтгэл!B24)</f>
+        <f>IF(Нэгтгэл!B25="","",Нэгтгэл!B25)</f>
         <v/>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="13" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="13" t="n">
         <v>1</v>
@@ -6792,10 +6769,10 @@
         <v>1</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="13" t="n">
         <v>1</v>
@@ -6804,10 +6781,10 @@
         <v>1</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25" s="13" t="n">
         <v>1</v>
@@ -6841,15 +6818,15 @@
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="12">
-        <f>IF(Нэгтгэл!B25="","",Нэгтгэл!B25)</f>
+        <f>IF(Нэгтгэл!B26="","",Нэгтгэл!B26)</f>
         <v/>
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>1</v>
@@ -6879,28 +6856,28 @@
         <v>1</v>
       </c>
       <c r="N26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="13" t="n">
         <v>1</v>
       </c>
       <c r="P26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
         <v>1</v>
       </c>
       <c r="R26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="13" t="n">
         <v>0</v>
@@ -6909,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="X26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="13" t="n">
         <v>1</v>
@@ -6937,10 +6914,10 @@
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="12">
-        <f>IF(Нэгтгэл!B26="","",Нэгтгэл!B26)</f>
+        <f>IF(Нэгтгэл!B27="","",Нэгтгэл!B27)</f>
         <v/>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -6948,40 +6925,40 @@
         <v>1</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="13" t="n">
         <v>1</v>
@@ -6990,22 +6967,22 @@
         <v>1</v>
       </c>
       <c r="S27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" s="13" t="n">
         <v>1</v>
@@ -7033,10 +7010,10 @@
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="12">
-        <f>IF(Нэгтгэл!B27="","",Нэгтгэл!B27)</f>
+        <f>IF(Нэгтгэл!B28="","",Нэгтгэл!B28)</f>
         <v/>
       </c>
       <c r="C28" s="4" t="n"/>
@@ -7044,37 +7021,37 @@
         <v>1</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="13" t="n">
         <v>1</v>
@@ -7098,7 +7075,7 @@
         <v>1</v>
       </c>
       <c r="W28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="13" t="n">
         <v>1</v>
@@ -7129,10 +7106,10 @@
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" s="12">
-        <f>IF(Нэгтгэл!B28="","",Нэгтгэл!B28)</f>
+        <f>IF(Нэгтгэл!B29="","",Нэгтгэл!B29)</f>
         <v/>
       </c>
       <c r="C29" s="4" t="n"/>
@@ -7143,22 +7120,22 @@
         <v>1</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="n">
         <v>1</v>
@@ -7185,7 +7162,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" s="13" t="n">
         <v>1</v>
@@ -7225,36 +7202,36 @@
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="12">
-        <f>IF(Нэгтгэл!B29="","",Нэгтгэл!B29)</f>
+        <f>IF(Нэгтгэл!B30="","",Нэгтгэл!B30)</f>
         <v/>
       </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="13" t="n">
         <v>1</v>
@@ -7269,19 +7246,19 @@
         <v>1</v>
       </c>
       <c r="P30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
         <v>1</v>
       </c>
       <c r="R30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" s="13" t="n">
         <v>1</v>
       </c>
       <c r="T30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" s="13" t="n">
         <v>1</v>
@@ -7290,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="W30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" s="13" t="n">
         <v>1</v>
@@ -7321,15 +7298,15 @@
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="12">
-        <f>IF(Нэгтгэл!B30="","",Нэгтгэл!B30)</f>
+        <f>IF(Нэгтгэл!B31="","",Нэгтгэл!B31)</f>
         <v/>
       </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>1</v>
@@ -7365,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="13" t="n">
         <v>1</v>
@@ -7389,10 +7366,10 @@
         <v>0</v>
       </c>
       <c r="X31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="12">
         <f>COUNTIF(D31:Y31,1)</f>
@@ -7417,10 +7394,10 @@
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="12">
-        <f>IF(Нэгтгэл!B31="","",Нэгтгэл!B31)</f>
+        <f>IF(Нэгтгэл!B32="","",Нэгтгэл!B32)</f>
         <v/>
       </c>
       <c r="C32" s="4" t="n"/>
@@ -7428,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="13" t="n">
         <v>1</v>
@@ -7458,16 +7435,16 @@
         <v>1</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="13" t="n">
         <v>1</v>
@@ -7482,13 +7459,13 @@
         <v>1</v>
       </c>
       <c r="W32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="12">
         <f>COUNTIF(D32:Y32,1)</f>
@@ -7513,10 +7490,10 @@
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="12">
-        <f>IF(Нэгтгэл!B32="","",Нэгтгэл!B32)</f>
+        <f>IF(Нэгтгэл!B33="","",Нэгтгэл!B33)</f>
         <v/>
       </c>
       <c r="C33" s="4" t="n"/>
@@ -7524,10 +7501,10 @@
         <v>1</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>1</v>
@@ -7536,7 +7513,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="13" t="n">
         <v>1</v>
@@ -7554,13 +7531,13 @@
         <v>1</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="13" t="n">
         <v>1</v>
@@ -7609,10 +7586,10 @@
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="12">
-        <f>IF(Нэгтгэл!B33="","",Нэгтгэл!B33)</f>
+        <f>IF(Нэгтгэл!B34="","",Нэгтгэл!B34)</f>
         <v/>
       </c>
       <c r="C34" s="4" t="n"/>
@@ -7635,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="13" t="n">
         <v>1</v>
@@ -7644,13 +7621,13 @@
         <v>1</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="13" t="n">
         <v>1</v>
@@ -7671,13 +7648,13 @@
         <v>1</v>
       </c>
       <c r="V34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="13" t="n">
         <v>1</v>
@@ -7705,10 +7682,10 @@
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="12">
-        <f>IF(Нэгтгэл!B34="","",Нэгтгэл!B34)</f>
+        <f>IF(Нэгтгэл!B35="","",Нэгтгэл!B35)</f>
         <v/>
       </c>
       <c r="C35" s="4" t="n"/>
@@ -7716,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="13" t="n">
         <v>0</v>
@@ -7728,25 +7705,25 @@
         <v>1</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="13" t="n">
         <v>1</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="13" t="n">
         <v>1</v>
@@ -7770,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="W35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" s="13" t="n">
         <v>1</v>
@@ -7801,21 +7778,21 @@
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" s="12">
-        <f>IF(Нэгтгэл!B35="","",Нэгтгэл!B35)</f>
+        <f>IF(Нэгтгэл!B36="","",Нэгтгэл!B36)</f>
         <v/>
       </c>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>1</v>
@@ -7836,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" s="13" t="n">
         <v>1</v>
@@ -7860,16 +7837,16 @@
         <v>1</v>
       </c>
       <c r="U36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="13" t="n">
         <v>1</v>
@@ -7897,10 +7874,10 @@
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="12">
-        <f>IF(Нэгтгэл!B36="","",Нэгтгэл!B36)</f>
+        <f>IF(Нэгтгэл!B37="","",Нэгтгэл!B37)</f>
         <v/>
       </c>
       <c r="C37" s="4" t="n"/>
@@ -7917,7 +7894,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="13" t="n">
         <v>1</v>
@@ -7956,13 +7933,13 @@
         <v>1</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" s="13" t="n">
         <v>0</v>
@@ -7991,589 +7968,493 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B38" s="12">
-        <f>IF(Нэгтгэл!B37="","",Нэгтгэл!B37)</f>
-        <v/>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="12">
-        <f>COUNTIF(D38:Y38,1)</f>
-        <v/>
-      </c>
-      <c r="AA38" s="12">
-        <f>IF(COUNT(D38:Y38)=0,"",ROUND(Z38/22*100,1))</f>
-        <v/>
-      </c>
-      <c r="AB38" s="12">
-        <f>COUNTIF(D38:Y38,0)</f>
-        <v/>
-      </c>
-      <c r="AC38" s="12">
-        <f>IF(COUNT(D38:Y38)=0,"",ROUND(AB38/22*100,1))</f>
-        <v/>
-      </c>
-      <c r="AD38" s="20">
-        <f>IF(AA38="","",IF(AA38&gt;=Нэгтгэл!$K$4,"Хангалттай эзэмшиж байна",IF(AA38&gt;=Нэгтгэл!$K$5,"Ахиж байна","Хөгжиж байна")))</f>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Чадна (1)</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="5">
+        <f>COUNTIF(D7:D37,1)</f>
+        <v/>
+      </c>
+      <c r="E38" s="5">
+        <f>COUNTIF(E7:E37,1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="5">
+        <f>COUNTIF(F7:F37,1)</f>
+        <v/>
+      </c>
+      <c r="G38" s="5">
+        <f>COUNTIF(G7:G37,1)</f>
+        <v/>
+      </c>
+      <c r="H38" s="5">
+        <f>COUNTIF(H7:H37,1)</f>
+        <v/>
+      </c>
+      <c r="I38" s="5">
+        <f>COUNTIF(I7:I37,1)</f>
+        <v/>
+      </c>
+      <c r="J38" s="5">
+        <f>COUNTIF(J7:J37,1)</f>
+        <v/>
+      </c>
+      <c r="K38" s="5">
+        <f>COUNTIF(K7:K37,1)</f>
+        <v/>
+      </c>
+      <c r="L38" s="5">
+        <f>COUNTIF(L7:L37,1)</f>
+        <v/>
+      </c>
+      <c r="M38" s="5">
+        <f>COUNTIF(M7:M37,1)</f>
+        <v/>
+      </c>
+      <c r="N38" s="5">
+        <f>COUNTIF(N7:N37,1)</f>
+        <v/>
+      </c>
+      <c r="O38" s="5">
+        <f>COUNTIF(O7:O37,1)</f>
+        <v/>
+      </c>
+      <c r="P38" s="5">
+        <f>COUNTIF(P7:P37,1)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="5">
+        <f>COUNTIF(Q7:Q37,1)</f>
+        <v/>
+      </c>
+      <c r="R38" s="5">
+        <f>COUNTIF(R7:R37,1)</f>
+        <v/>
+      </c>
+      <c r="S38" s="5">
+        <f>COUNTIF(S7:S37,1)</f>
+        <v/>
+      </c>
+      <c r="T38" s="5">
+        <f>COUNTIF(T7:T37,1)</f>
+        <v/>
+      </c>
+      <c r="U38" s="5">
+        <f>COUNTIF(U7:U37,1)</f>
+        <v/>
+      </c>
+      <c r="V38" s="5">
+        <f>COUNTIF(V7:V37,1)</f>
+        <v/>
+      </c>
+      <c r="W38" s="5">
+        <f>COUNTIF(W7:W37,1)</f>
+        <v/>
+      </c>
+      <c r="X38" s="5">
+        <f>COUNTIF(X7:X37,1)</f>
+        <v/>
+      </c>
+      <c r="Y38" s="5">
+        <f>COUNTIF(Y7:Y37,1)</f>
+        <v/>
+      </c>
+      <c r="Z38" s="21" t="inlineStr">
+        <is>
+          <t>Хангалттай эзэмшиж байна</t>
+        </is>
+      </c>
+      <c r="AA38" s="22" t="n"/>
+      <c r="AB38" s="22" t="n"/>
+      <c r="AC38" s="23" t="n"/>
+      <c r="AD38" s="5">
+        <f>COUNTIF(AD7:AD37,"Хангалттай эзэмшиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Чадна (1)</t>
+          <t>Хувь</t>
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="15" t="n"/>
       <c r="D39" s="5">
-        <f>COUNTIF(D8:D38,1)</f>
+        <f>IF(COUNT(D7:D37)=0,"",ROUND(COUNTIF(D7:D37,1)/COUNT(D7:D37)*100,1))</f>
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>COUNTIF(E8:E38,1)</f>
+        <f>IF(COUNT(E7:E37)=0,"",ROUND(COUNTIF(E7:E37,1)/COUNT(E7:E37)*100,1))</f>
         <v/>
       </c>
       <c r="F39" s="5">
-        <f>COUNTIF(F8:F38,1)</f>
+        <f>IF(COUNT(F7:F37)=0,"",ROUND(COUNTIF(F7:F37,1)/COUNT(F7:F37)*100,1))</f>
         <v/>
       </c>
       <c r="G39" s="5">
-        <f>COUNTIF(G8:G38,1)</f>
+        <f>IF(COUNT(G7:G37)=0,"",ROUND(COUNTIF(G7:G37,1)/COUNT(G7:G37)*100,1))</f>
         <v/>
       </c>
       <c r="H39" s="5">
-        <f>COUNTIF(H8:H38,1)</f>
+        <f>IF(COUNT(H7:H37)=0,"",ROUND(COUNTIF(H7:H37,1)/COUNT(H7:H37)*100,1))</f>
         <v/>
       </c>
       <c r="I39" s="5">
-        <f>COUNTIF(I8:I38,1)</f>
+        <f>IF(COUNT(I7:I37)=0,"",ROUND(COUNTIF(I7:I37,1)/COUNT(I7:I37)*100,1))</f>
         <v/>
       </c>
       <c r="J39" s="5">
-        <f>COUNTIF(J8:J38,1)</f>
+        <f>IF(COUNT(J7:J37)=0,"",ROUND(COUNTIF(J7:J37,1)/COUNT(J7:J37)*100,1))</f>
         <v/>
       </c>
       <c r="K39" s="5">
-        <f>COUNTIF(K8:K38,1)</f>
+        <f>IF(COUNT(K7:K37)=0,"",ROUND(COUNTIF(K7:K37,1)/COUNT(K7:K37)*100,1))</f>
         <v/>
       </c>
       <c r="L39" s="5">
-        <f>COUNTIF(L8:L38,1)</f>
+        <f>IF(COUNT(L7:L37)=0,"",ROUND(COUNTIF(L7:L37,1)/COUNT(L7:L37)*100,1))</f>
         <v/>
       </c>
       <c r="M39" s="5">
-        <f>COUNTIF(M8:M38,1)</f>
+        <f>IF(COUNT(M7:M37)=0,"",ROUND(COUNTIF(M7:M37,1)/COUNT(M7:M37)*100,1))</f>
         <v/>
       </c>
       <c r="N39" s="5">
-        <f>COUNTIF(N8:N38,1)</f>
+        <f>IF(COUNT(N7:N37)=0,"",ROUND(COUNTIF(N7:N37,1)/COUNT(N7:N37)*100,1))</f>
         <v/>
       </c>
       <c r="O39" s="5">
-        <f>COUNTIF(O8:O38,1)</f>
+        <f>IF(COUNT(O7:O37)=0,"",ROUND(COUNTIF(O7:O37,1)/COUNT(O7:O37)*100,1))</f>
         <v/>
       </c>
       <c r="P39" s="5">
-        <f>COUNTIF(P8:P38,1)</f>
+        <f>IF(COUNT(P7:P37)=0,"",ROUND(COUNTIF(P7:P37,1)/COUNT(P7:P37)*100,1))</f>
         <v/>
       </c>
       <c r="Q39" s="5">
-        <f>COUNTIF(Q8:Q38,1)</f>
+        <f>IF(COUNT(Q7:Q37)=0,"",ROUND(COUNTIF(Q7:Q37,1)/COUNT(Q7:Q37)*100,1))</f>
         <v/>
       </c>
       <c r="R39" s="5">
-        <f>COUNTIF(R8:R38,1)</f>
+        <f>IF(COUNT(R7:R37)=0,"",ROUND(COUNTIF(R7:R37,1)/COUNT(R7:R37)*100,1))</f>
         <v/>
       </c>
       <c r="S39" s="5">
-        <f>COUNTIF(S8:S38,1)</f>
+        <f>IF(COUNT(S7:S37)=0,"",ROUND(COUNTIF(S7:S37,1)/COUNT(S7:S37)*100,1))</f>
         <v/>
       </c>
       <c r="T39" s="5">
-        <f>COUNTIF(T8:T38,1)</f>
+        <f>IF(COUNT(T7:T37)=0,"",ROUND(COUNTIF(T7:T37,1)/COUNT(T7:T37)*100,1))</f>
         <v/>
       </c>
       <c r="U39" s="5">
-        <f>COUNTIF(U8:U38,1)</f>
+        <f>IF(COUNT(U7:U37)=0,"",ROUND(COUNTIF(U7:U37,1)/COUNT(U7:U37)*100,1))</f>
         <v/>
       </c>
       <c r="V39" s="5">
-        <f>COUNTIF(V8:V38,1)</f>
+        <f>IF(COUNT(V7:V37)=0,"",ROUND(COUNTIF(V7:V37,1)/COUNT(V7:V37)*100,1))</f>
         <v/>
       </c>
       <c r="W39" s="5">
-        <f>COUNTIF(W8:W38,1)</f>
+        <f>IF(COUNT(W7:W37)=0,"",ROUND(COUNTIF(W7:W37,1)/COUNT(W7:W37)*100,1))</f>
         <v/>
       </c>
       <c r="X39" s="5">
-        <f>COUNTIF(X8:X38,1)</f>
+        <f>IF(COUNT(X7:X37)=0,"",ROUND(COUNTIF(X7:X37,1)/COUNT(X7:X37)*100,1))</f>
         <v/>
       </c>
       <c r="Y39" s="5">
-        <f>COUNTIF(Y8:Y38,1)</f>
+        <f>IF(COUNT(Y7:Y37)=0,"",ROUND(COUNTIF(Y7:Y37,1)/COUNT(Y7:Y37)*100,1))</f>
         <v/>
       </c>
       <c r="Z39" s="21" t="inlineStr">
         <is>
-          <t>Хангалттай эзэмшиж байна</t>
+          <t>Ахиж байна</t>
         </is>
       </c>
       <c r="AA39" s="22" t="n"/>
       <c r="AB39" s="22" t="n"/>
       <c r="AC39" s="23" t="n"/>
       <c r="AD39" s="5">
-        <f>COUNTIF(AD8:AD38,"Хангалттай эзэмшиж байна")</f>
+        <f>COUNTIF(AD7:AD37,"Ахиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Хувь</t>
+          <t>Чадахгүй (0)</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="15" t="n"/>
       <c r="D40" s="5">
-        <f>IF(COUNT(D8:D38)=0,"",ROUND(COUNTIF(D8:D38,1)/COUNT(D8:D38)*100,1))</f>
+        <f>COUNTIF(D7:D37,0)</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>IF(COUNT(E8:E38)=0,"",ROUND(COUNTIF(E8:E38,1)/COUNT(E8:E38)*100,1))</f>
+        <f>COUNTIF(E7:E37,0)</f>
         <v/>
       </c>
       <c r="F40" s="5">
-        <f>IF(COUNT(F8:F38)=0,"",ROUND(COUNTIF(F8:F38,1)/COUNT(F8:F38)*100,1))</f>
+        <f>COUNTIF(F7:F37,0)</f>
         <v/>
       </c>
       <c r="G40" s="5">
-        <f>IF(COUNT(G8:G38)=0,"",ROUND(COUNTIF(G8:G38,1)/COUNT(G8:G38)*100,1))</f>
+        <f>COUNTIF(G7:G37,0)</f>
         <v/>
       </c>
       <c r="H40" s="5">
-        <f>IF(COUNT(H8:H38)=0,"",ROUND(COUNTIF(H8:H38,1)/COUNT(H8:H38)*100,1))</f>
+        <f>COUNTIF(H7:H37,0)</f>
         <v/>
       </c>
       <c r="I40" s="5">
-        <f>IF(COUNT(I8:I38)=0,"",ROUND(COUNTIF(I8:I38,1)/COUNT(I8:I38)*100,1))</f>
+        <f>COUNTIF(I7:I37,0)</f>
         <v/>
       </c>
       <c r="J40" s="5">
-        <f>IF(COUNT(J8:J38)=0,"",ROUND(COUNTIF(J8:J38,1)/COUNT(J8:J38)*100,1))</f>
+        <f>COUNTIF(J7:J37,0)</f>
         <v/>
       </c>
       <c r="K40" s="5">
-        <f>IF(COUNT(K8:K38)=0,"",ROUND(COUNTIF(K8:K38,1)/COUNT(K8:K38)*100,1))</f>
+        <f>COUNTIF(K7:K37,0)</f>
         <v/>
       </c>
       <c r="L40" s="5">
-        <f>IF(COUNT(L8:L38)=0,"",ROUND(COUNTIF(L8:L38,1)/COUNT(L8:L38)*100,1))</f>
+        <f>COUNTIF(L7:L37,0)</f>
         <v/>
       </c>
       <c r="M40" s="5">
-        <f>IF(COUNT(M8:M38)=0,"",ROUND(COUNTIF(M8:M38,1)/COUNT(M8:M38)*100,1))</f>
+        <f>COUNTIF(M7:M37,0)</f>
         <v/>
       </c>
       <c r="N40" s="5">
-        <f>IF(COUNT(N8:N38)=0,"",ROUND(COUNTIF(N8:N38,1)/COUNT(N8:N38)*100,1))</f>
+        <f>COUNTIF(N7:N37,0)</f>
         <v/>
       </c>
       <c r="O40" s="5">
-        <f>IF(COUNT(O8:O38)=0,"",ROUND(COUNTIF(O8:O38,1)/COUNT(O8:O38)*100,1))</f>
+        <f>COUNTIF(O7:O37,0)</f>
         <v/>
       </c>
       <c r="P40" s="5">
-        <f>IF(COUNT(P8:P38)=0,"",ROUND(COUNTIF(P8:P38,1)/COUNT(P8:P38)*100,1))</f>
+        <f>COUNTIF(P7:P37,0)</f>
         <v/>
       </c>
       <c r="Q40" s="5">
-        <f>IF(COUNT(Q8:Q38)=0,"",ROUND(COUNTIF(Q8:Q38,1)/COUNT(Q8:Q38)*100,1))</f>
+        <f>COUNTIF(Q7:Q37,0)</f>
         <v/>
       </c>
       <c r="R40" s="5">
-        <f>IF(COUNT(R8:R38)=0,"",ROUND(COUNTIF(R8:R38,1)/COUNT(R8:R38)*100,1))</f>
+        <f>COUNTIF(R7:R37,0)</f>
         <v/>
       </c>
       <c r="S40" s="5">
-        <f>IF(COUNT(S8:S38)=0,"",ROUND(COUNTIF(S8:S38,1)/COUNT(S8:S38)*100,1))</f>
+        <f>COUNTIF(S7:S37,0)</f>
         <v/>
       </c>
       <c r="T40" s="5">
-        <f>IF(COUNT(T8:T38)=0,"",ROUND(COUNTIF(T8:T38,1)/COUNT(T8:T38)*100,1))</f>
+        <f>COUNTIF(T7:T37,0)</f>
         <v/>
       </c>
       <c r="U40" s="5">
-        <f>IF(COUNT(U8:U38)=0,"",ROUND(COUNTIF(U8:U38,1)/COUNT(U8:U38)*100,1))</f>
+        <f>COUNTIF(U7:U37,0)</f>
         <v/>
       </c>
       <c r="V40" s="5">
-        <f>IF(COUNT(V8:V38)=0,"",ROUND(COUNTIF(V8:V38,1)/COUNT(V8:V38)*100,1))</f>
+        <f>COUNTIF(V7:V37,0)</f>
         <v/>
       </c>
       <c r="W40" s="5">
-        <f>IF(COUNT(W8:W38)=0,"",ROUND(COUNTIF(W8:W38,1)/COUNT(W8:W38)*100,1))</f>
+        <f>COUNTIF(W7:W37,0)</f>
         <v/>
       </c>
       <c r="X40" s="5">
-        <f>IF(COUNT(X8:X38)=0,"",ROUND(COUNTIF(X8:X38,1)/COUNT(X8:X38)*100,1))</f>
+        <f>COUNTIF(X7:X37,0)</f>
         <v/>
       </c>
       <c r="Y40" s="5">
-        <f>IF(COUNT(Y8:Y38)=0,"",ROUND(COUNTIF(Y8:Y38,1)/COUNT(Y8:Y38)*100,1))</f>
+        <f>COUNTIF(Y7:Y37,0)</f>
         <v/>
       </c>
       <c r="Z40" s="21" t="inlineStr">
         <is>
-          <t>Ахиж байна</t>
+          <t>Хөгжиж байна</t>
         </is>
       </c>
       <c r="AA40" s="22" t="n"/>
       <c r="AB40" s="22" t="n"/>
       <c r="AC40" s="23" t="n"/>
       <c r="AD40" s="5">
-        <f>COUNTIF(AD8:AD38,"Ахиж байна")</f>
+        <f>COUNTIF(AD7:AD37,"Хөгжиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Чадахгүй (0)</t>
+          <t>Хувь</t>
         </is>
       </c>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="15" t="n"/>
       <c r="D41" s="5">
-        <f>COUNTIF(D8:D38,0)</f>
+        <f>IF(COUNT(D7:D37)=0,"",ROUND(COUNTIF(D7:D37,0)/COUNT(D7:D37)*100,1))</f>
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>COUNTIF(E8:E38,0)</f>
+        <f>IF(COUNT(E7:E37)=0,"",ROUND(COUNTIF(E7:E37,0)/COUNT(E7:E37)*100,1))</f>
         <v/>
       </c>
       <c r="F41" s="5">
-        <f>COUNTIF(F8:F38,0)</f>
+        <f>IF(COUNT(F7:F37)=0,"",ROUND(COUNTIF(F7:F37,0)/COUNT(F7:F37)*100,1))</f>
         <v/>
       </c>
       <c r="G41" s="5">
-        <f>COUNTIF(G8:G38,0)</f>
+        <f>IF(COUNT(G7:G37)=0,"",ROUND(COUNTIF(G7:G37,0)/COUNT(G7:G37)*100,1))</f>
         <v/>
       </c>
       <c r="H41" s="5">
-        <f>COUNTIF(H8:H38,0)</f>
+        <f>IF(COUNT(H7:H37)=0,"",ROUND(COUNTIF(H7:H37,0)/COUNT(H7:H37)*100,1))</f>
         <v/>
       </c>
       <c r="I41" s="5">
-        <f>COUNTIF(I8:I38,0)</f>
+        <f>IF(COUNT(I7:I37)=0,"",ROUND(COUNTIF(I7:I37,0)/COUNT(I7:I37)*100,1))</f>
         <v/>
       </c>
       <c r="J41" s="5">
-        <f>COUNTIF(J8:J38,0)</f>
+        <f>IF(COUNT(J7:J37)=0,"",ROUND(COUNTIF(J7:J37,0)/COUNT(J7:J37)*100,1))</f>
         <v/>
       </c>
       <c r="K41" s="5">
-        <f>COUNTIF(K8:K38,0)</f>
+        <f>IF(COUNT(K7:K37)=0,"",ROUND(COUNTIF(K7:K37,0)/COUNT(K7:K37)*100,1))</f>
         <v/>
       </c>
       <c r="L41" s="5">
-        <f>COUNTIF(L8:L38,0)</f>
+        <f>IF(COUNT(L7:L37)=0,"",ROUND(COUNTIF(L7:L37,0)/COUNT(L7:L37)*100,1))</f>
         <v/>
       </c>
       <c r="M41" s="5">
-        <f>COUNTIF(M8:M38,0)</f>
+        <f>IF(COUNT(M7:M37)=0,"",ROUND(COUNTIF(M7:M37,0)/COUNT(M7:M37)*100,1))</f>
         <v/>
       </c>
       <c r="N41" s="5">
-        <f>COUNTIF(N8:N38,0)</f>
+        <f>IF(COUNT(N7:N37)=0,"",ROUND(COUNTIF(N7:N37,0)/COUNT(N7:N37)*100,1))</f>
         <v/>
       </c>
       <c r="O41" s="5">
-        <f>COUNTIF(O8:O38,0)</f>
+        <f>IF(COUNT(O7:O37)=0,"",ROUND(COUNTIF(O7:O37,0)/COUNT(O7:O37)*100,1))</f>
         <v/>
       </c>
       <c r="P41" s="5">
-        <f>COUNTIF(P8:P38,0)</f>
+        <f>IF(COUNT(P7:P37)=0,"",ROUND(COUNTIF(P7:P37,0)/COUNT(P7:P37)*100,1))</f>
         <v/>
       </c>
       <c r="Q41" s="5">
-        <f>COUNTIF(Q8:Q38,0)</f>
+        <f>IF(COUNT(Q7:Q37)=0,"",ROUND(COUNTIF(Q7:Q37,0)/COUNT(Q7:Q37)*100,1))</f>
         <v/>
       </c>
       <c r="R41" s="5">
-        <f>COUNTIF(R8:R38,0)</f>
+        <f>IF(COUNT(R7:R37)=0,"",ROUND(COUNTIF(R7:R37,0)/COUNT(R7:R37)*100,1))</f>
         <v/>
       </c>
       <c r="S41" s="5">
-        <f>COUNTIF(S8:S38,0)</f>
+        <f>IF(COUNT(S7:S37)=0,"",ROUND(COUNTIF(S7:S37,0)/COUNT(S7:S37)*100,1))</f>
         <v/>
       </c>
       <c r="T41" s="5">
-        <f>COUNTIF(T8:T38,0)</f>
+        <f>IF(COUNT(T7:T37)=0,"",ROUND(COUNTIF(T7:T37,0)/COUNT(T7:T37)*100,1))</f>
         <v/>
       </c>
       <c r="U41" s="5">
-        <f>COUNTIF(U8:U38,0)</f>
+        <f>IF(COUNT(U7:U37)=0,"",ROUND(COUNTIF(U7:U37,0)/COUNT(U7:U37)*100,1))</f>
         <v/>
       </c>
       <c r="V41" s="5">
-        <f>COUNTIF(V8:V38,0)</f>
+        <f>IF(COUNT(V7:V37)=0,"",ROUND(COUNTIF(V7:V37,0)/COUNT(V7:V37)*100,1))</f>
         <v/>
       </c>
       <c r="W41" s="5">
-        <f>COUNTIF(W8:W38,0)</f>
+        <f>IF(COUNT(W7:W37)=0,"",ROUND(COUNTIF(W7:W37,0)/COUNT(W7:W37)*100,1))</f>
         <v/>
       </c>
       <c r="X41" s="5">
-        <f>COUNTIF(X8:X38,0)</f>
+        <f>IF(COUNT(X7:X37)=0,"",ROUND(COUNTIF(X7:X37,0)/COUNT(X7:X37)*100,1))</f>
         <v/>
       </c>
       <c r="Y41" s="5">
-        <f>COUNTIF(Y8:Y38,0)</f>
-        <v/>
-      </c>
-      <c r="Z41" s="21" t="inlineStr">
-        <is>
-          <t>Хөгжиж байна</t>
-        </is>
-      </c>
-      <c r="AA41" s="22" t="n"/>
-      <c r="AB41" s="22" t="n"/>
-      <c r="AC41" s="23" t="n"/>
-      <c r="AD41" s="5">
-        <f>COUNTIF(AD8:AD38,"Хөгжиж байна")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Хувь</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="5">
-        <f>IF(COUNT(D8:D38)=0,"",ROUND(COUNTIF(D8:D38,0)/COUNT(D8:D38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="E42" s="5">
-        <f>IF(COUNT(E8:E38)=0,"",ROUND(COUNTIF(E8:E38,0)/COUNT(E8:E38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="F42" s="5">
-        <f>IF(COUNT(F8:F38)=0,"",ROUND(COUNTIF(F8:F38,0)/COUNT(F8:F38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="G42" s="5">
-        <f>IF(COUNT(G8:G38)=0,"",ROUND(COUNTIF(G8:G38,0)/COUNT(G8:G38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="H42" s="5">
-        <f>IF(COUNT(H8:H38)=0,"",ROUND(COUNTIF(H8:H38,0)/COUNT(H8:H38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="I42" s="5">
-        <f>IF(COUNT(I8:I38)=0,"",ROUND(COUNTIF(I8:I38,0)/COUNT(I8:I38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="J42" s="5">
-        <f>IF(COUNT(J8:J38)=0,"",ROUND(COUNTIF(J8:J38,0)/COUNT(J8:J38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="K42" s="5">
-        <f>IF(COUNT(K8:K38)=0,"",ROUND(COUNTIF(K8:K38,0)/COUNT(K8:K38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="L42" s="5">
-        <f>IF(COUNT(L8:L38)=0,"",ROUND(COUNTIF(L8:L38,0)/COUNT(L8:L38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="M42" s="5">
-        <f>IF(COUNT(M8:M38)=0,"",ROUND(COUNTIF(M8:M38,0)/COUNT(M8:M38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="N42" s="5">
-        <f>IF(COUNT(N8:N38)=0,"",ROUND(COUNTIF(N8:N38,0)/COUNT(N8:N38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="O42" s="5">
-        <f>IF(COUNT(O8:O38)=0,"",ROUND(COUNTIF(O8:O38,0)/COUNT(O8:O38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="P42" s="5">
-        <f>IF(COUNT(P8:P38)=0,"",ROUND(COUNTIF(P8:P38,0)/COUNT(P8:P38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="Q42" s="5">
-        <f>IF(COUNT(Q8:Q38)=0,"",ROUND(COUNTIF(Q8:Q38,0)/COUNT(Q8:Q38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="R42" s="5">
-        <f>IF(COUNT(R8:R38)=0,"",ROUND(COUNTIF(R8:R38,0)/COUNT(R8:R38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="S42" s="5">
-        <f>IF(COUNT(S8:S38)=0,"",ROUND(COUNTIF(S8:S38,0)/COUNT(S8:S38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="T42" s="5">
-        <f>IF(COUNT(T8:T38)=0,"",ROUND(COUNTIF(T8:T38,0)/COUNT(T8:T38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="U42" s="5">
-        <f>IF(COUNT(U8:U38)=0,"",ROUND(COUNTIF(U8:U38,0)/COUNT(U8:U38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="V42" s="5">
-        <f>IF(COUNT(V8:V38)=0,"",ROUND(COUNTIF(V8:V38,0)/COUNT(V8:V38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="W42" s="5">
-        <f>IF(COUNT(W8:W38)=0,"",ROUND(COUNTIF(W8:W38,0)/COUNT(W8:W38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="X42" s="5">
-        <f>IF(COUNT(X8:X38)=0,"",ROUND(COUNTIF(X8:X38,0)/COUNT(X8:X38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="Y42" s="5">
-        <f>IF(COUNT(Y8:Y38)=0,"",ROUND(COUNTIF(Y8:Y38,0)/COUNT(Y8:Y38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="Z42" s="15" t="n"/>
-      <c r="AA42" s="15" t="n"/>
-      <c r="AB42" s="15" t="n"/>
-      <c r="AC42" s="15" t="n"/>
-      <c r="AD42" s="15" t="n"/>
+        <f>IF(COUNT(Y7:Y37)=0,"",ROUND(COUNTIF(Y7:Y37,0)/COUNT(Y7:Y37)*100,1))</f>
+        <v/>
+      </c>
+      <c r="Z41" s="15" t="n"/>
+      <c r="AA41" s="15" t="n"/>
+      <c r="AB41" s="15" t="n"/>
+      <c r="AC41" s="15" t="n"/>
+      <c r="AD41" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="Z38:AC38"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="AC3:AC6"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="AA3:AA7"/>
     <mergeCell ref="D3:Y3"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B3:C7"/>
     <mergeCell ref="Z40:AC40"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="AB3:AB7"/>
+    <mergeCell ref="Z3:Z6"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A3:A6"/>
     <mergeCell ref="A2:AD2"/>
-    <mergeCell ref="AD3:AD7"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="Z41:AC41"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="AC3:AC7"/>
+    <mergeCell ref="AA3:AA6"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C6"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="AB3:AB6"/>
     <mergeCell ref="Z39:AC39"/>
-    <mergeCell ref="Z3:Z7"/>
+    <mergeCell ref="AD3:AD6"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A3:A7"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="A1:AD1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:Y38">
+  <conditionalFormatting sqref="D7:Y37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S35 S36 S37 S38 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V35 V36 V37 V38 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W35 W36 W37 W38 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X35 X36 X37 X38 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Y34 Y35 Y36 Y37 Y38" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="1 эсвэл 0" error="Чадна бол 1, чадахгүй бол 0 гэж бичнэ." promptTitle="Тэмдэглэх" prompt="Чадна = 1, Чадахгүй = 0" type="list">
+    <dataValidation sqref="D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 S31 S32 S33 S34 S35 S36 S37 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V35 V36 V37 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 W31 W32 W33 W34 W35 W36 W37 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 X31 X32 X33 X34 X35 X36 X37 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Y31 Y32 Y33 Y34 Y35 Y36 Y37" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="1 эсвэл 0" error="Чадна бол 1, чадахгүй бол 0 гэж бичнэ." promptTitle="Тэмдэглэх" prompt="Чадна = 1, Чадахгүй = 0" type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8589,7 +8470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -8726,21 +8607,29 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>37</v>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>1 / 0</t>
+        </is>
       </c>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
@@ -8748,42 +8637,54 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
     </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="12">
+        <f>IF(Нэгтгэл!B7="","",Нэгтгэл!B7)</f>
+        <v/>
+      </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>1 / 0</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
+      <c r="D7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12">
+        <f>COUNTIF(D7:G7,1)</f>
+        <v/>
+      </c>
+      <c r="I7" s="12">
+        <f>IF(COUNT(D7:G7)=0,"",ROUND(H7/4*100,1))</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>COUNTIF(D7:G7,0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>IF(COUNT(D7:G7)=0,"",ROUND(J7/4*100,1))</f>
+        <v/>
+      </c>
+      <c r="L7" s="20">
+        <f>IF(I7="","",IF(I7&gt;=Нэгтгэл!$K$4,"Хангалттай эзэмшиж байна",IF(I7&gt;=Нэгтгэл!$K$5,"Ахиж байна","Хөгжиж байна")))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="12">
-        <f>IF(Нэгтгэл!B7="","",Нэгтгэл!B7)</f>
+        <f>IF(Нэгтгэл!B8="","",Нэгтгэл!B8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -8791,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>1</v>
@@ -8822,24 +8723,24 @@
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="12">
-        <f>IF(Нэгтгэл!B8="","",Нэгтгэл!B8)</f>
+        <f>IF(Нэгтгэл!B9="","",Нэгтгэл!B9)</f>
         <v/>
       </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="12">
         <f>COUNTIF(D9:G9,1)</f>
@@ -8864,10 +8765,10 @@
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="12">
-        <f>IF(Нэгтгэл!B9="","",Нэгтгэл!B9)</f>
+        <f>IF(Нэгтгэл!B10="","",Нэгтгэл!B10)</f>
         <v/>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -8875,13 +8776,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="12">
         <f>COUNTIF(D10:G10,1)</f>
@@ -8906,10 +8807,10 @@
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="12">
-        <f>IF(Нэгтгэл!B10="","",Нэгтгэл!B10)</f>
+        <f>IF(Нэгтгэл!B11="","",Нэгтгэл!B11)</f>
         <v/>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -8917,7 +8818,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>1</v>
@@ -8948,10 +8849,10 @@
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="12">
-        <f>IF(Нэгтгэл!B11="","",Нэгтгэл!B11)</f>
+        <f>IF(Нэгтгэл!B12="","",Нэгтгэл!B12)</f>
         <v/>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -8959,10 +8860,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>1</v>
@@ -8990,21 +8891,21 @@
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="12">
-        <f>IF(Нэгтгэл!B12="","",Нэгтгэл!B12)</f>
+        <f>IF(Нэгтгэл!B13="","",Нэгтгэл!B13)</f>
         <v/>
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>1</v>
@@ -9032,15 +8933,15 @@
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="12">
-        <f>IF(Нэгтгэл!B13="","",Нэгтгэл!B13)</f>
+        <f>IF(Нэгтгэл!B14="","",Нэгтгэл!B14)</f>
         <v/>
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>0</v>
@@ -9049,7 +8950,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="12">
         <f>COUNTIF(D14:G14,1)</f>
@@ -9074,10 +8975,10 @@
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="12">
-        <f>IF(Нэгтгэл!B14="","",Нэгтгэл!B14)</f>
+        <f>IF(Нэгтгэл!B15="","",Нэгтгэл!B15)</f>
         <v/>
       </c>
       <c r="C15" s="4" t="n"/>
@@ -9091,7 +8992,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="12">
         <f>COUNTIF(D15:G15,1)</f>
@@ -9116,10 +9017,10 @@
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16" s="12">
-        <f>IF(Нэгтгэл!B15="","",Нэгтгэл!B15)</f>
+        <f>IF(Нэгтгэл!B16="","",Нэгтгэл!B16)</f>
         <v/>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -9158,10 +9059,10 @@
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="12">
-        <f>IF(Нэгтгэл!B16="","",Нэгтгэл!B16)</f>
+        <f>IF(Нэгтгэл!B17="","",Нэгтгэл!B17)</f>
         <v/>
       </c>
       <c r="C17" s="4" t="n"/>
@@ -9169,7 +9070,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>1</v>
@@ -9200,10 +9101,10 @@
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="12">
-        <f>IF(Нэгтгэл!B17="","",Нэгтгэл!B17)</f>
+        <f>IF(Нэгтгэл!B18="","",Нэгтгэл!B18)</f>
         <v/>
       </c>
       <c r="C18" s="4" t="n"/>
@@ -9214,7 +9115,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>1</v>
@@ -9242,10 +9143,10 @@
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="12">
-        <f>IF(Нэгтгэл!B18="","",Нэгтгэл!B18)</f>
+        <f>IF(Нэгтгэл!B19="","",Нэгтгэл!B19)</f>
         <v/>
       </c>
       <c r="C19" s="4" t="n"/>
@@ -9256,7 +9157,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>1</v>
@@ -9284,15 +9185,15 @@
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="12">
-        <f>IF(Нэгтгэл!B19="","",Нэгтгэл!B19)</f>
+        <f>IF(Нэгтгэл!B20="","",Нэгтгэл!B20)</f>
         <v/>
       </c>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>1</v>
@@ -9326,15 +9227,15 @@
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="12">
-        <f>IF(Нэгтгэл!B20="","",Нэгтгэл!B20)</f>
+        <f>IF(Нэгтгэл!B21="","",Нэгтгэл!B21)</f>
         <v/>
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>1</v>
@@ -9368,24 +9269,24 @@
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="12">
-        <f>IF(Нэгтгэл!B21="","",Нэгтгэл!B21)</f>
+        <f>IF(Нэгтгэл!B22="","",Нэгтгэл!B22)</f>
         <v/>
       </c>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="12">
         <f>COUNTIF(D22:G22,1)</f>
@@ -9410,24 +9311,24 @@
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="12">
-        <f>IF(Нэгтгэл!B22="","",Нэгтгэл!B22)</f>
+        <f>IF(Нэгтгэл!B23="","",Нэгтгэл!B23)</f>
         <v/>
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="12">
         <f>COUNTIF(D23:G23,1)</f>
@@ -9452,15 +9353,15 @@
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="12">
-        <f>IF(Нэгтгэл!B23="","",Нэгтгэл!B23)</f>
+        <f>IF(Нэгтгэл!B24="","",Нэгтгэл!B24)</f>
         <v/>
       </c>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>1</v>
@@ -9494,15 +9395,15 @@
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="12">
-        <f>IF(Нэгтгэл!B24="","",Нэгтгэл!B24)</f>
+        <f>IF(Нэгтгэл!B25="","",Нэгтгэл!B25)</f>
         <v/>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>1</v>
@@ -9511,7 +9412,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="12">
         <f>COUNTIF(D25:G25,1)</f>
@@ -9536,15 +9437,15 @@
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="12">
-        <f>IF(Нэгтгэл!B25="","",Нэгтгэл!B25)</f>
+        <f>IF(Нэгтгэл!B26="","",Нэгтгэл!B26)</f>
         <v/>
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>1</v>
@@ -9553,7 +9454,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="12">
         <f>COUNTIF(D26:G26,1)</f>
@@ -9578,15 +9479,15 @@
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="12">
-        <f>IF(Нэгтгэл!B26="","",Нэгтгэл!B26)</f>
+        <f>IF(Нэгтгэл!B27="","",Нэгтгэл!B27)</f>
         <v/>
       </c>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>1</v>
@@ -9620,10 +9521,10 @@
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="12">
-        <f>IF(Нэгтгэл!B27="","",Нэгтгэл!B27)</f>
+        <f>IF(Нэгтгэл!B28="","",Нэгтгэл!B28)</f>
         <v/>
       </c>
       <c r="C28" s="4" t="n"/>
@@ -9634,10 +9535,10 @@
         <v>1</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12">
         <f>COUNTIF(D28:G28,1)</f>
@@ -9662,21 +9563,21 @@
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" s="12">
-        <f>IF(Нэгтгэл!B28="","",Нэгтгэл!B28)</f>
+        <f>IF(Нэгтгэл!B29="","",Нэгтгэл!B29)</f>
         <v/>
       </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>0</v>
@@ -9704,24 +9605,24 @@
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="12">
-        <f>IF(Нэгтгэл!B29="","",Нэгтгэл!B29)</f>
+        <f>IF(Нэгтгэл!B30="","",Нэгтгэл!B30)</f>
         <v/>
       </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12">
         <f>COUNTIF(D30:G30,1)</f>
@@ -9746,10 +9647,10 @@
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="12">
-        <f>IF(Нэгтгэл!B30="","",Нэгтгэл!B30)</f>
+        <f>IF(Нэгтгэл!B31="","",Нэгтгэл!B31)</f>
         <v/>
       </c>
       <c r="C31" s="4" t="n"/>
@@ -9757,13 +9658,13 @@
         <v>1</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="12">
         <f>COUNTIF(D31:G31,1)</f>
@@ -9788,10 +9689,10 @@
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="12">
-        <f>IF(Нэгтгэл!B31="","",Нэгтгэл!B31)</f>
+        <f>IF(Нэгтгэл!B32="","",Нэгтгэл!B32)</f>
         <v/>
       </c>
       <c r="C32" s="4" t="n"/>
@@ -9830,10 +9731,10 @@
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="12">
-        <f>IF(Нэгтгэл!B32="","",Нэгтгэл!B32)</f>
+        <f>IF(Нэгтгэл!B33="","",Нэгтгэл!B33)</f>
         <v/>
       </c>
       <c r="C33" s="4" t="n"/>
@@ -9841,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="13" t="n">
         <v>1</v>
@@ -9872,10 +9773,10 @@
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="12">
-        <f>IF(Нэгтгэл!B33="","",Нэгтгэл!B33)</f>
+        <f>IF(Нэгтгэл!B34="","",Нэгтгэл!B34)</f>
         <v/>
       </c>
       <c r="C34" s="4" t="n"/>
@@ -9889,7 +9790,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12">
         <f>COUNTIF(D34:G34,1)</f>
@@ -9914,10 +9815,10 @@
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="12">
-        <f>IF(Нэгтгэл!B34="","",Нэгтгэл!B34)</f>
+        <f>IF(Нэгтгэл!B35="","",Нэгтгэл!B35)</f>
         <v/>
       </c>
       <c r="C35" s="4" t="n"/>
@@ -9925,7 +9826,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="13" t="n">
         <v>1</v>
@@ -9956,24 +9857,24 @@
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" s="12">
-        <f>IF(Нэгтгэл!B35="","",Нэгтгэл!B35)</f>
+        <f>IF(Нэгтгэл!B36="","",Нэгтгэл!B36)</f>
         <v/>
       </c>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12">
         <f>COUNTIF(D36:G36,1)</f>
@@ -9998,15 +9899,15 @@
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="12">
-        <f>IF(Нэгтгэл!B36="","",Нэгтгэл!B36)</f>
+        <f>IF(Нэгтгэл!B37="","",Нэгтгэл!B37)</f>
         <v/>
       </c>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>1</v>
@@ -10015,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="12">
         <f>COUNTIF(D37:G37,1)</f>
@@ -10038,215 +9939,172 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B38" s="12">
-        <f>IF(Нэгтгэл!B37="","",Нэгтгэл!B37)</f>
-        <v/>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="12">
-        <f>COUNTIF(D38:G38,1)</f>
-        <v/>
-      </c>
-      <c r="I38" s="12">
-        <f>IF(COUNT(D38:G38)=0,"",ROUND(H38/4*100,1))</f>
-        <v/>
-      </c>
-      <c r="J38" s="12">
-        <f>COUNTIF(D38:G38,0)</f>
-        <v/>
-      </c>
-      <c r="K38" s="12">
-        <f>IF(COUNT(D38:G38)=0,"",ROUND(J38/4*100,1))</f>
-        <v/>
-      </c>
-      <c r="L38" s="20">
-        <f>IF(I38="","",IF(I38&gt;=Нэгтгэл!$K$4,"Хангалттай эзэмшиж байна",IF(I38&gt;=Нэгтгэл!$K$5,"Ахиж байна","Хөгжиж байна")))</f>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Чадна (1)</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="5">
+        <f>COUNTIF(D7:D37,1)</f>
+        <v/>
+      </c>
+      <c r="E38" s="5">
+        <f>COUNTIF(E7:E37,1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="5">
+        <f>COUNTIF(F7:F37,1)</f>
+        <v/>
+      </c>
+      <c r="G38" s="5">
+        <f>COUNTIF(G7:G37,1)</f>
+        <v/>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>Хангалттай эзэмшиж байна</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="22" t="n"/>
+      <c r="K38" s="23" t="n"/>
+      <c r="L38" s="5">
+        <f>COUNTIF(L7:L37,"Хангалттай эзэмшиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Чадна (1)</t>
+          <t>Хувь</t>
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="15" t="n"/>
       <c r="D39" s="5">
-        <f>COUNTIF(D8:D38,1)</f>
+        <f>IF(COUNT(D7:D37)=0,"",ROUND(COUNTIF(D7:D37,1)/COUNT(D7:D37)*100,1))</f>
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>COUNTIF(E8:E38,1)</f>
+        <f>IF(COUNT(E7:E37)=0,"",ROUND(COUNTIF(E7:E37,1)/COUNT(E7:E37)*100,1))</f>
         <v/>
       </c>
       <c r="F39" s="5">
-        <f>COUNTIF(F8:F38,1)</f>
+        <f>IF(COUNT(F7:F37)=0,"",ROUND(COUNTIF(F7:F37,1)/COUNT(F7:F37)*100,1))</f>
         <v/>
       </c>
       <c r="G39" s="5">
-        <f>COUNTIF(G8:G38,1)</f>
+        <f>IF(COUNT(G7:G37)=0,"",ROUND(COUNTIF(G7:G37,1)/COUNT(G7:G37)*100,1))</f>
         <v/>
       </c>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t>Хангалттай эзэмшиж байна</t>
+          <t>Ахиж байна</t>
         </is>
       </c>
       <c r="I39" s="22" t="n"/>
       <c r="J39" s="22" t="n"/>
       <c r="K39" s="23" t="n"/>
       <c r="L39" s="5">
-        <f>COUNTIF(L8:L38,"Хангалттай эзэмшиж байна")</f>
+        <f>COUNTIF(L7:L37,"Ахиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Хувь</t>
+          <t>Чадахгүй (0)</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="15" t="n"/>
       <c r="D40" s="5">
-        <f>IF(COUNT(D8:D38)=0,"",ROUND(COUNTIF(D8:D38,1)/COUNT(D8:D38)*100,1))</f>
+        <f>COUNTIF(D7:D37,0)</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>IF(COUNT(E8:E38)=0,"",ROUND(COUNTIF(E8:E38,1)/COUNT(E8:E38)*100,1))</f>
+        <f>COUNTIF(E7:E37,0)</f>
         <v/>
       </c>
       <c r="F40" s="5">
-        <f>IF(COUNT(F8:F38)=0,"",ROUND(COUNTIF(F8:F38,1)/COUNT(F8:F38)*100,1))</f>
+        <f>COUNTIF(F7:F37,0)</f>
         <v/>
       </c>
       <c r="G40" s="5">
-        <f>IF(COUNT(G8:G38)=0,"",ROUND(COUNTIF(G8:G38,1)/COUNT(G8:G38)*100,1))</f>
+        <f>COUNTIF(G7:G37,0)</f>
         <v/>
       </c>
       <c r="H40" s="21" t="inlineStr">
         <is>
-          <t>Ахиж байна</t>
+          <t>Хөгжиж байна</t>
         </is>
       </c>
       <c r="I40" s="22" t="n"/>
       <c r="J40" s="22" t="n"/>
       <c r="K40" s="23" t="n"/>
       <c r="L40" s="5">
-        <f>COUNTIF(L8:L38,"Ахиж байна")</f>
+        <f>COUNTIF(L7:L37,"Хөгжиж байна")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Чадахгүй (0)</t>
+          <t>Хувь</t>
         </is>
       </c>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="15" t="n"/>
       <c r="D41" s="5">
-        <f>COUNTIF(D8:D38,0)</f>
+        <f>IF(COUNT(D7:D37)=0,"",ROUND(COUNTIF(D7:D37,0)/COUNT(D7:D37)*100,1))</f>
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>COUNTIF(E8:E38,0)</f>
+        <f>IF(COUNT(E7:E37)=0,"",ROUND(COUNTIF(E7:E37,0)/COUNT(E7:E37)*100,1))</f>
         <v/>
       </c>
       <c r="F41" s="5">
-        <f>COUNTIF(F8:F38,0)</f>
+        <f>IF(COUNT(F7:F37)=0,"",ROUND(COUNTIF(F7:F37,0)/COUNT(F7:F37)*100,1))</f>
         <v/>
       </c>
       <c r="G41" s="5">
-        <f>COUNTIF(G8:G38,0)</f>
-        <v/>
-      </c>
-      <c r="H41" s="21" t="inlineStr">
-        <is>
-          <t>Хөгжиж байна</t>
-        </is>
-      </c>
-      <c r="I41" s="22" t="n"/>
-      <c r="J41" s="22" t="n"/>
-      <c r="K41" s="23" t="n"/>
-      <c r="L41" s="5">
-        <f>COUNTIF(L8:L38,"Хөгжиж байна")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Хувь</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="5">
-        <f>IF(COUNT(D8:D38)=0,"",ROUND(COUNTIF(D8:D38,0)/COUNT(D8:D38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="E42" s="5">
-        <f>IF(COUNT(E8:E38)=0,"",ROUND(COUNTIF(E8:E38,0)/COUNT(E8:E38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="F42" s="5">
-        <f>IF(COUNT(F8:F38)=0,"",ROUND(COUNTIF(F8:F38,0)/COUNT(F8:F38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="G42" s="5">
-        <f>IF(COUNT(G8:G38)=0,"",ROUND(COUNTIF(G8:G38,0)/COUNT(G8:G38)*100,1))</f>
-        <v/>
-      </c>
-      <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
-      <c r="K42" s="15" t="n"/>
-      <c r="L42" s="15" t="n"/>
+        <f>IF(COUNT(G7:G37)=0,"",ROUND(COUNTIF(G7:G37,0)/COUNT(G7:G37)*100,1))</f>
+        <v/>
+      </c>
+      <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="15" t="n"/>
+      <c r="K41" s="15" t="n"/>
+      <c r="L41" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D3:G3"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="L3:L6"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="J3:J7"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B3:C7"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="I3:I6"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="H38:K38"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="B19:C19"/>
@@ -10256,29 +10114,30 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="H39:K39"/>
-    <mergeCell ref="L3:L7"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C6"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="H3:H6"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="J3:J6"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="K3:K6"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A3:A7"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B35:C35"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:G38">
+  <conditionalFormatting sqref="D7:G37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="1 эсвэл 0" error="Чадна бол 1, чадахгүй бол 0 гэж бичнэ." promptTitle="Тэмдэглэх" prompt="Чадна = 1, Чадахгүй = 0" type="list">
+    <dataValidation sqref="D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="1 эсвэл 0" error="Чадна бол 1, чадахгүй бол 0 гэж бичнэ." promptTitle="Тэмдэглэх" prompt="Чадна = 1, Чадахгүй = 0" type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
